--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 5 position(s) left CURRENT on a STOP BREACH (R1 4 · R2 1) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>⚠ lifecycle dataset is dated 2026-09-11, not this report's as-of · rerun the pipeline</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -103,10 +103,10 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="3" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="5" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -480,7 +480,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:W61"/>
+  <dimension ref="A1:W49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -518,14 +518,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>35 investable · NEW 12 · ACTIVE+ 12 · ACTIVE 11   ·   R2 20 · MOMENTUM 0 · R1 15 (advisory)</t>
+          <t>23 investable · NEW 0 · ACTIVE+ 12 · ACTIVE 11   ·   R2 8 · MOMENTUM 0 · R1 15 (advisory)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>🛡 DOWNSIDE · 35 position(s) with an INTACT stop · if all of them fired today the average outcome is -6.65% from entry, worst single -17.17%</t>
+          <t>🛡 DOWNSIDE · 23 position(s) with an INTACT stop · if all of them fired today the average outcome is -7.23% from entry, worst single -17.17%</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=12 · 516 scored · 30 already in CURRENT · biggest blocker: model disagreement (410) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 2</t>
+          <t>🔎 WHY NEW=0 · 516 scored · 20 already in CURRENT · biggest blocker: model disagreement (427) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 20 candidate(s) reviewed today.</t>
+          <t>🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 8 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -675,7 +675,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>AMGN</t>
+          <t>TRV</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -685,7 +685,7 @@
       </c>
       <c r="D8" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E8" s="4" t="inlineStr">
@@ -695,51 +695,53 @@
       </c>
       <c r="F8" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G8" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H8" s="4" t="n">
+        <v>374.34</v>
+      </c>
+      <c r="I8" s="4" t="n">
+        <v>378.05</v>
+      </c>
+      <c r="J8" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K8" s="5" t="n">
+        <v>0.99</v>
+      </c>
+      <c r="L8" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M8" s="4" t="inlineStr">
+        <is>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N8" s="6" t="n">
+        <v>78849691774.53787</v>
+      </c>
+      <c r="O8" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H8" s="4" t="n">
-        <v>381.5</v>
-      </c>
-      <c r="I8" s="4" t="n">
-        <v>381.5</v>
-      </c>
-      <c r="J8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K8" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M8" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N8" s="5" t="n">
-        <v>236374160811.6292</v>
-      </c>
-      <c r="O8" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n">
-        <v>359.8657</v>
+        <v>365.5859</v>
       </c>
       <c r="R8" s="4" t="inlineStr">
         <is>
@@ -747,22 +749,22 @@
         </is>
       </c>
       <c r="S8" s="4" t="n">
-        <v>5.67</v>
+        <v>3.3</v>
       </c>
       <c r="T8" s="4" t="n">
-        <v>-5.67</v>
+        <v>-2.34</v>
       </c>
       <c r="U8" s="4" t="n">
-        <v>413.95</v>
+        <v>400.86</v>
       </c>
       <c r="V8" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-AMGN-20260915-97fabb</t>
+          <t>USA-R2-TRV-20260810-9cd25d</t>
         </is>
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -774,7 +776,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>CF</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -784,7 +786,7 @@
       </c>
       <c r="D9" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E9" s="4" t="inlineStr">
@@ -794,51 +796,53 @@
       </c>
       <c r="F9" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G9" s="4" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H9" s="4" t="n">
+        <v>382.85</v>
+      </c>
+      <c r="I9" s="4" t="n">
+        <v>382.95</v>
+      </c>
+      <c r="J9" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K9" s="5" t="n">
+        <v>0.03</v>
+      </c>
+      <c r="L9" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M9" s="4" t="inlineStr">
+        <is>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N9" s="6" t="n">
+        <v>110255433210.2225</v>
+      </c>
+      <c r="O9" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H9" s="4" t="n">
-        <v>131.24</v>
-      </c>
-      <c r="I9" s="4" t="n">
-        <v>131.24</v>
-      </c>
-      <c r="J9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K9" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M9" s="4" t="inlineStr">
-        <is>
-          <t>Basic Materials</t>
-        </is>
-      </c>
-      <c r="N9" s="5" t="n">
-        <v>20179016711.53197</v>
-      </c>
-      <c r="O9" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n">
-        <v>122.8507</v>
+        <v>364.9789</v>
       </c>
       <c r="R9" s="4" t="inlineStr">
         <is>
@@ -846,22 +850,22 @@
         </is>
       </c>
       <c r="S9" s="4" t="n">
-        <v>6.39</v>
+        <v>4.69</v>
       </c>
       <c r="T9" s="4" t="n">
-        <v>-6.39</v>
+        <v>-4.67</v>
       </c>
       <c r="U9" s="4" t="n">
-        <v>148.02</v>
+        <v>414.08</v>
       </c>
       <c r="V9" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-CF-20260915-4b01a2</t>
+          <t>USA-R2-VLO-20260908-e69cee</t>
         </is>
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -873,7 +877,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>CRM</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -883,7 +887,7 @@
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
@@ -893,51 +897,53 @@
       </c>
       <c r="F10" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G10" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H10" s="4" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="I10" s="4" t="n">
+        <v>173.31</v>
+      </c>
+      <c r="J10" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K10" s="7" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="L10" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M10" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N10" s="6" t="n">
+        <v>416485609340.7415</v>
+      </c>
+      <c r="O10" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H10" s="4" t="n">
-        <v>259.43</v>
-      </c>
-      <c r="I10" s="4" t="n">
-        <v>259.43</v>
-      </c>
-      <c r="J10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K10" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M10" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N10" s="5" t="n">
-        <v>213353612143.8822</v>
-      </c>
-      <c r="O10" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n">
-        <v>240.8171</v>
+        <v>161.9314</v>
       </c>
       <c r="R10" s="4" t="inlineStr">
         <is>
@@ -945,22 +951,22 @@
         </is>
       </c>
       <c r="S10" s="4" t="n">
-        <v>7.17</v>
+        <v>6.57</v>
       </c>
       <c r="T10" s="4" t="n">
-        <v>-7.17</v>
+        <v>-7.59</v>
       </c>
       <c r="U10" s="4" t="n">
-        <v>296.66</v>
+        <v>204.13</v>
       </c>
       <c r="V10" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-CRM-20260915-1cd445</t>
+          <t>USA-R2-PLTR-20260810-f9e975</t>
         </is>
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +978,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>EIX</t>
+          <t>INCY</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -982,7 +988,7 @@
       </c>
       <c r="D11" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E11" s="4" t="inlineStr">
@@ -992,51 +998,53 @@
       </c>
       <c r="F11" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-09</t>
         </is>
       </c>
       <c r="G11" s="4" t="inlineStr">
         <is>
+          <t>2026-09-09</t>
+        </is>
+      </c>
+      <c r="H11" s="4" t="n">
+        <v>126.01</v>
+      </c>
+      <c r="I11" s="4" t="n">
+        <v>122.19</v>
+      </c>
+      <c r="J11" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K11" s="7" t="n">
+        <v>-3.03</v>
+      </c>
+      <c r="L11" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M11" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N11" s="6" t="n">
+        <v>24768516757.93547</v>
+      </c>
+      <c r="O11" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H11" s="4" t="n">
-        <v>56.13</v>
-      </c>
-      <c r="I11" s="4" t="n">
-        <v>56.13</v>
-      </c>
-      <c r="J11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K11" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="4" t="n">
-        <v>62.3</v>
-      </c>
-      <c r="M11" s="4" t="inlineStr">
-        <is>
-          <t>Utilities</t>
-        </is>
-      </c>
-      <c r="N11" s="5" t="n">
-        <v>21847412064.79042</v>
-      </c>
-      <c r="O11" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n">
-        <v>50.1118</v>
+        <v>115.7257</v>
       </c>
       <c r="R11" s="4" t="inlineStr">
         <is>
@@ -1044,22 +1052,22 @@
         </is>
       </c>
       <c r="S11" s="4" t="n">
-        <v>10.72</v>
+        <v>5.29</v>
       </c>
       <c r="T11" s="4" t="n">
-        <v>-10.72</v>
+        <v>-8.16</v>
       </c>
       <c r="U11" s="4" t="n">
-        <v>68.17</v>
+        <v>135.86</v>
       </c>
       <c r="V11" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-EIX-20260915-0d2d3d</t>
+          <t>USA-R2-INCY-20260909-bb0ff1</t>
         </is>
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1079,7 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>GDDY</t>
+          <t>SMCI</t>
         </is>
       </c>
       <c r="C12" s="4" t="inlineStr">
@@ -1081,7 +1089,7 @@
       </c>
       <c r="D12" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E12" s="4" t="inlineStr">
@@ -1091,51 +1099,53 @@
       </c>
       <c r="F12" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-08</t>
         </is>
       </c>
       <c r="G12" s="4" t="inlineStr">
         <is>
+          <t>2026-09-08</t>
+        </is>
+      </c>
+      <c r="H12" s="4" t="n">
+        <v>40.26</v>
+      </c>
+      <c r="I12" s="4" t="n">
+        <v>36.74</v>
+      </c>
+      <c r="J12" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K12" s="7" t="n">
+        <v>-8.74</v>
+      </c>
+      <c r="L12" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M12" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N12" s="6" t="n">
+        <v>23768402866.24873</v>
+      </c>
+      <c r="O12" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H12" s="4" t="n">
-        <v>104.47</v>
-      </c>
-      <c r="I12" s="4" t="n">
-        <v>104.47</v>
-      </c>
-      <c r="J12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K12" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="4" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="M12" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N12" s="5" t="n">
-        <v>12829212537.09402</v>
-      </c>
-      <c r="O12" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n">
-        <v>98.3323</v>
+        <v>33.3468</v>
       </c>
       <c r="R12" s="4" t="inlineStr">
         <is>
@@ -1143,22 +1153,22 @@
         </is>
       </c>
       <c r="S12" s="4" t="n">
-        <v>5.88</v>
+        <v>9.24</v>
       </c>
       <c r="T12" s="4" t="n">
-        <v>-5.88</v>
+        <v>-17.17</v>
       </c>
       <c r="U12" s="4" t="n">
-        <v>116.75</v>
+        <v>46.92</v>
       </c>
       <c r="V12" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-GDDY-20260915-4ff869</t>
+          <t>USA-R2-SMCI-20260908-c2c66b</t>
         </is>
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1170,71 +1180,73 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>GOOG</t>
+          <t>GRMN</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D13" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G13" s="4" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="H13" s="4" t="n">
+        <v>274.11</v>
+      </c>
+      <c r="I13" s="4" t="n">
+        <v>280.38</v>
+      </c>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K13" s="5" t="n">
+        <v>2.29</v>
+      </c>
+      <c r="L13" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M13" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N13" s="6" t="n">
+        <v>54075432294.55815</v>
+      </c>
+      <c r="O13" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H13" s="4" t="n">
-        <v>345.71</v>
-      </c>
-      <c r="I13" s="4" t="n">
-        <v>345.71</v>
-      </c>
-      <c r="J13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K13" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M13" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="N13" s="5" t="n">
-        <v>4101096608748.116</v>
-      </c>
-      <c r="O13" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n">
-        <v>331.3671</v>
+        <v>260.921</v>
       </c>
       <c r="R13" s="4" t="inlineStr">
         <is>
@@ -1242,22 +1254,22 @@
         </is>
       </c>
       <c r="S13" s="4" t="n">
-        <v>4.15</v>
+        <v>6.94</v>
       </c>
       <c r="T13" s="4" t="n">
-        <v>-4.15</v>
+        <v>-4.81</v>
       </c>
       <c r="U13" s="4" t="n">
-        <v>367.22</v>
+        <v>293.89</v>
       </c>
       <c r="V13" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-GOOG-20260915-111a59</t>
+          <t>USA-R1-GRMN-20260901-4c77f2</t>
         </is>
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1269,71 +1281,73 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>IT</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D14" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G14" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H14" s="4" t="n">
+        <v>193.17</v>
+      </c>
+      <c r="I14" s="4" t="n">
+        <v>197.07</v>
+      </c>
+      <c r="J14" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K14" s="5" t="n">
+        <v>2.02</v>
+      </c>
+      <c r="L14" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M14" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N14" s="6" t="n">
+        <v>12445146117.71387</v>
+      </c>
+      <c r="O14" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H14" s="4" t="n">
-        <v>280.38</v>
-      </c>
-      <c r="I14" s="4" t="n">
-        <v>280.38</v>
-      </c>
-      <c r="J14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K14" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M14" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N14" s="5" t="n">
-        <v>53431824008.73483</v>
-      </c>
-      <c r="O14" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n">
-        <v>268.7507</v>
+        <v>170.3286</v>
       </c>
       <c r="R14" s="4" t="inlineStr">
         <is>
@@ -1341,22 +1355,22 @@
         </is>
       </c>
       <c r="S14" s="4" t="n">
-        <v>4.15</v>
+        <v>13.57</v>
       </c>
       <c r="T14" s="4" t="n">
-        <v>-4.15</v>
+        <v>-11.82</v>
       </c>
       <c r="U14" s="4" t="n">
-        <v>297.82</v>
+        <v>227.43</v>
       </c>
       <c r="V14" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-GRMN-20260915-78ebe3</t>
+          <t>USA-R1-IT-20260810-04dfbc</t>
         </is>
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1368,71 +1382,73 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>IDXX</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-14</t>
         </is>
       </c>
       <c r="G15" s="4" t="inlineStr">
         <is>
+          <t>2026-08-14</t>
+        </is>
+      </c>
+      <c r="H15" s="4" t="n">
+        <v>63.83</v>
+      </c>
+      <c r="I15" s="4" t="n">
+        <v>64.09999999999999</v>
+      </c>
+      <c r="J15" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K15" s="5" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="L15" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M15" s="4" t="inlineStr">
+        <is>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N15" s="6" t="n">
+        <v>130948340798.581</v>
+      </c>
+      <c r="O15" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H15" s="4" t="n">
-        <v>509.56</v>
-      </c>
-      <c r="I15" s="4" t="n">
-        <v>509.56</v>
-      </c>
-      <c r="J15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K15" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="4" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="M15" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N15" s="5" t="n">
-        <v>42227950130.60567</v>
-      </c>
-      <c r="O15" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n">
-        <v>482.07</v>
+        <v>60.0271</v>
       </c>
       <c r="R15" s="4" t="inlineStr">
         <is>
@@ -1440,22 +1456,22 @@
         </is>
       </c>
       <c r="S15" s="4" t="n">
-        <v>5.39</v>
+        <v>6.35</v>
       </c>
       <c r="T15" s="4" t="n">
-        <v>-5.39</v>
+        <v>-5.96</v>
       </c>
       <c r="U15" s="4" t="n">
-        <v>550.8</v>
+        <v>69.53</v>
       </c>
       <c r="V15" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-IDXX-20260915-1e7aa1</t>
+          <t>USA-R1-BMY-20260814-a3b600</t>
         </is>
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1467,71 +1483,73 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>NCLH</t>
+          <t>MSFT</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D16" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G16" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H16" s="4" t="n">
+        <v>505.11</v>
+      </c>
+      <c r="I16" s="4" t="n">
+        <v>505.41</v>
+      </c>
+      <c r="J16" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K16" s="5" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="L16" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M16" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N16" s="6" t="n">
+        <v>3753185242379.146</v>
+      </c>
+      <c r="O16" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H16" s="4" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="I16" s="4" t="n">
-        <v>14.72</v>
-      </c>
-      <c r="J16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K16" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="4" t="n">
-        <v>59.4</v>
-      </c>
-      <c r="M16" s="4" t="inlineStr">
-        <is>
-          <t>Consumer Cyclical</t>
-        </is>
-      </c>
-      <c r="N16" s="5" t="n">
-        <v>7149900531.60001</v>
-      </c>
-      <c r="O16" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n">
-        <v>13.9625</v>
+        <v>469.0698</v>
       </c>
       <c r="R16" s="4" t="inlineStr">
         <is>
@@ -1539,22 +1557,22 @@
         </is>
       </c>
       <c r="S16" s="4" t="n">
-        <v>5.15</v>
+        <v>7.19</v>
       </c>
       <c r="T16" s="4" t="n">
-        <v>-5.15</v>
+        <v>-7.13</v>
       </c>
       <c r="U16" s="4" t="n">
-        <v>16.24</v>
+        <v>559.17</v>
       </c>
       <c r="V16" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-NCLH-20260915-9c865d</t>
+          <t>USA-R1-MSFT-20260810-6110fc</t>
         </is>
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1566,71 +1584,73 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>PLD</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D17" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H17" s="4" t="n">
+        <v>175.23</v>
+      </c>
+      <c r="I17" s="4" t="n">
+        <v>173.31</v>
+      </c>
+      <c r="J17" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K17" s="7" t="n">
+        <v>-1.1</v>
+      </c>
+      <c r="L17" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M17" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N17" s="6" t="n">
+        <v>416485609340.7415</v>
+      </c>
+      <c r="O17" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H17" s="4" t="n">
-        <v>135.19</v>
-      </c>
-      <c r="I17" s="4" t="n">
-        <v>135.19</v>
-      </c>
-      <c r="J17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K17" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="4" t="n">
-        <v>56.2</v>
-      </c>
-      <c r="M17" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="N17" s="5" t="n">
-        <v>133505758956.2373</v>
-      </c>
-      <c r="O17" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n">
-        <v>130.9443</v>
+        <v>155.965</v>
       </c>
       <c r="R17" s="4" t="inlineStr">
         <is>
@@ -1638,22 +1658,22 @@
         </is>
       </c>
       <c r="S17" s="4" t="n">
-        <v>3.14</v>
+        <v>10.01</v>
       </c>
       <c r="T17" s="4" t="n">
-        <v>-3.14</v>
+        <v>-10.99</v>
       </c>
       <c r="U17" s="4" t="n">
-        <v>141.56</v>
+        <v>204.13</v>
       </c>
       <c r="V17" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-PLD-20260915-4969bb</t>
+          <t>USA-R1-PLTR-20260810-5c4552</t>
         </is>
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1665,71 +1685,73 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>TPL</t>
+          <t>ADBE</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D18" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G18" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H18" s="4" t="n">
+        <v>272.96</v>
+      </c>
+      <c r="I18" s="4" t="n">
+        <v>265.6</v>
+      </c>
+      <c r="J18" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K18" s="7" t="n">
+        <v>-2.7</v>
+      </c>
+      <c r="L18" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M18" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N18" s="6" t="n">
+        <v>105584459243.008</v>
+      </c>
+      <c r="O18" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H18" s="4" t="n">
-        <v>365.27</v>
-      </c>
-      <c r="I18" s="4" t="n">
-        <v>365.27</v>
-      </c>
-      <c r="J18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K18" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="4" t="n">
-        <v>61.9</v>
-      </c>
-      <c r="M18" s="4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N18" s="5" t="n">
-        <v>24997697021.78508</v>
-      </c>
-      <c r="O18" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n">
-        <v>346.2808</v>
+        <v>247.1386</v>
       </c>
       <c r="R18" s="4" t="inlineStr">
         <is>
@@ -1737,22 +1759,22 @@
         </is>
       </c>
       <c r="S18" s="4" t="n">
-        <v>5.2</v>
+        <v>6.95</v>
       </c>
       <c r="T18" s="4" t="n">
-        <v>-5.2</v>
+        <v>-9.460000000000001</v>
       </c>
       <c r="U18" s="4" t="n">
-        <v>403.25</v>
+        <v>311.69</v>
       </c>
       <c r="V18" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-TPL-20260915-ace2a8</t>
+          <t>USA-R1-ADBE-20260810-4ad164</t>
         </is>
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1764,71 +1786,73 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>UDR</t>
+          <t>UBER</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D19" s="4" t="inlineStr">
         <is>
-          <t>NEW</t>
+          <t>ACTIVE+</t>
         </is>
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
         <is>
-          <t>NEW today</t>
+          <t>Admitted 2026-08-10</t>
         </is>
       </c>
       <c r="G19" s="4" t="inlineStr">
         <is>
+          <t>2026-08-10</t>
+        </is>
+      </c>
+      <c r="H19" s="4" t="n">
+        <v>78.03</v>
+      </c>
+      <c r="I19" s="4" t="n">
+        <v>72.63</v>
+      </c>
+      <c r="J19" s="4" t="inlineStr">
+        <is>
+          <t>2026-09-14</t>
+        </is>
+      </c>
+      <c r="K19" s="7" t="n">
+        <v>-6.92</v>
+      </c>
+      <c r="L19" s="4" t="inlineStr">
+        <is>
+          <t>Historical score unavailable</t>
+        </is>
+      </c>
+      <c r="M19" s="4" t="inlineStr">
+        <is>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N19" s="6" t="n">
+        <v>148354252614.7491</v>
+      </c>
+      <c r="O19" s="4" t="inlineStr">
+        <is>
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="H19" s="4" t="n">
-        <v>35.37</v>
-      </c>
-      <c r="I19" s="4" t="n">
-        <v>35.37</v>
-      </c>
-      <c r="J19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K19" s="4" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="4" t="n">
-        <v>59.1</v>
-      </c>
-      <c r="M19" s="4" t="inlineStr">
-        <is>
-          <t>Real Estate</t>
-        </is>
-      </c>
-      <c r="N19" s="5" t="n">
-        <v>13480313738.1309</v>
-      </c>
-      <c r="O19" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
           <t>Large</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n">
-        <v>34.22</v>
+        <v>72.40940000000001</v>
       </c>
       <c r="R19" s="4" t="inlineStr">
         <is>
@@ -1836,22 +1860,22 @@
         </is>
       </c>
       <c r="S19" s="4" t="n">
-        <v>3.25</v>
+        <v>0.3</v>
       </c>
       <c r="T19" s="4" t="n">
-        <v>-3.25</v>
+        <v>-7.2</v>
       </c>
       <c r="U19" s="4" t="n">
-        <v>37.09</v>
+        <v>86.45999999999999</v>
       </c>
       <c r="V19" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-UDR-20260915-44e67d</t>
+          <t>USA-R1-UBER-20260810-3f4c24</t>
         </is>
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 0d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -1863,7 +1887,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>TRV</t>
+          <t>V</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1873,7 +1897,7 @@
       </c>
       <c r="D20" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E20" s="4" t="inlineStr">
@@ -1892,18 +1916,18 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>374.34</v>
+        <v>360.65</v>
       </c>
       <c r="I20" s="4" t="n">
-        <v>378.05</v>
+        <v>375.28</v>
       </c>
       <c r="J20" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K20" s="6" t="n">
-        <v>0.99</v>
+      <c r="K20" s="5" t="n">
+        <v>4.06</v>
       </c>
       <c r="L20" s="4" t="inlineStr">
         <is>
@@ -1915,8 +1939,8 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N20" s="5" t="n">
-        <v>77037113169.76082</v>
+      <c r="N20" s="6" t="n">
+        <v>700648182865.4106</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
@@ -1929,7 +1953,7 @@
         </is>
       </c>
       <c r="Q20" s="4" t="n">
-        <v>365.5859</v>
+        <v>364.7557</v>
       </c>
       <c r="R20" s="4" t="inlineStr">
         <is>
@@ -1937,22 +1961,22 @@
         </is>
       </c>
       <c r="S20" s="4" t="n">
-        <v>3.3</v>
+        <v>2.8</v>
       </c>
       <c r="T20" s="4" t="n">
-        <v>-2.34</v>
+        <v>1.14</v>
       </c>
       <c r="U20" s="4" t="n">
-        <v>400.86</v>
+        <v>384</v>
       </c>
       <c r="V20" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-TRV-20260810-9cd25d</t>
+          <t>USA-R2-V-20260810-69160d</t>
         </is>
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1964,7 +1988,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>VLO</t>
+          <t>BMY</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1974,7 +1998,7 @@
       </c>
       <c r="D21" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E21" s="4" t="inlineStr">
@@ -1984,27 +2008,27 @@
       </c>
       <c r="F21" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-08-11</t>
         </is>
       </c>
       <c r="G21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H21" s="4" t="n">
-        <v>382.85</v>
+        <v>63.61</v>
       </c>
       <c r="I21" s="4" t="n">
-        <v>382.95</v>
+        <v>64.09999999999999</v>
       </c>
       <c r="J21" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K21" s="6" t="n">
-        <v>0.03</v>
+      <c r="K21" s="5" t="n">
+        <v>0.77</v>
       </c>
       <c r="L21" s="4" t="inlineStr">
         <is>
@@ -2013,11 +2037,11 @@
       </c>
       <c r="M21" s="4" t="inlineStr">
         <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N21" s="5" t="n">
-        <v>106733315426.1837</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N21" s="6" t="n">
+        <v>130948340798.581</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
@@ -2030,7 +2054,7 @@
         </is>
       </c>
       <c r="Q21" s="4" t="n">
-        <v>364.9789</v>
+        <v>61.4986</v>
       </c>
       <c r="R21" s="4" t="inlineStr">
         <is>
@@ -2038,22 +2062,22 @@
         </is>
       </c>
       <c r="S21" s="4" t="n">
-        <v>4.69</v>
+        <v>4.06</v>
       </c>
       <c r="T21" s="4" t="n">
-        <v>-4.67</v>
+        <v>-3.32</v>
       </c>
       <c r="U21" s="4" t="n">
-        <v>414.08</v>
+        <v>69.45</v>
       </c>
       <c r="V21" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-VLO-20260908-e69cee</t>
+          <t>USA-R2-BMY-20260811-c99117</t>
         </is>
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2065,7 +2089,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>DXCM</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -2075,7 +2099,7 @@
       </c>
       <c r="D22" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E22" s="4" t="inlineStr">
@@ -2085,19 +2109,19 @@
       </c>
       <c r="F22" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-08-11</t>
         </is>
       </c>
       <c r="G22" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="H22" s="4" t="n">
-        <v>175.23</v>
+        <v>89.53</v>
       </c>
       <c r="I22" s="4" t="n">
-        <v>173.31</v>
+        <v>84.68000000000001</v>
       </c>
       <c r="J22" s="4" t="inlineStr">
         <is>
@@ -2105,7 +2129,7 @@
         </is>
       </c>
       <c r="K22" s="7" t="n">
-        <v>-1.1</v>
+        <v>-5.42</v>
       </c>
       <c r="L22" s="4" t="inlineStr">
         <is>
@@ -2114,11 +2138,11 @@
       </c>
       <c r="M22" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N22" s="5" t="n">
-        <v>418890007002.7825</v>
+          <t>Healthcare</t>
+        </is>
+      </c>
+      <c r="N22" s="6" t="n">
+        <v>31952143648.08222</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
@@ -2131,7 +2155,7 @@
         </is>
       </c>
       <c r="Q22" s="4" t="n">
-        <v>161.9314</v>
+        <v>79.8471</v>
       </c>
       <c r="R22" s="4" t="inlineStr">
         <is>
@@ -2139,22 +2163,22 @@
         </is>
       </c>
       <c r="S22" s="4" t="n">
-        <v>6.57</v>
+        <v>5.71</v>
       </c>
       <c r="T22" s="4" t="n">
-        <v>-7.59</v>
+        <v>-10.82</v>
       </c>
       <c r="U22" s="4" t="n">
-        <v>204.13</v>
+        <v>99.06</v>
       </c>
       <c r="V22" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-PLTR-20260810-f9e975</t>
+          <t>USA-R2-DXCM-20260811-b3de8c</t>
         </is>
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2166,47 +2190,47 @@
       </c>
       <c r="B23" s="4" t="inlineStr">
         <is>
-          <t>INCY</t>
+          <t>CRM</t>
         </is>
       </c>
       <c r="C23" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D23" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-09</t>
+          <t>Admitted 2026-08-14</t>
         </is>
       </c>
       <c r="G23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-09</t>
+          <t>2026-08-14</t>
         </is>
       </c>
       <c r="H23" s="4" t="n">
-        <v>126.01</v>
+        <v>196.21</v>
       </c>
       <c r="I23" s="4" t="n">
-        <v>122.19</v>
+        <v>259.43</v>
       </c>
       <c r="J23" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K23" s="7" t="n">
-        <v>-3.03</v>
+      <c r="K23" s="5" t="n">
+        <v>32.22</v>
       </c>
       <c r="L23" s="4" t="inlineStr">
         <is>
@@ -2215,11 +2239,11 @@
       </c>
       <c r="M23" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N23" s="5" t="n">
-        <v>25692123442.84064</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N23" s="6" t="n">
+        <v>213501042512.7226</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
@@ -2232,7 +2256,7 @@
         </is>
       </c>
       <c r="Q23" s="4" t="n">
-        <v>115.7257</v>
+        <v>179.3029</v>
       </c>
       <c r="R23" s="4" t="inlineStr">
         <is>
@@ -2240,22 +2264,24 @@
         </is>
       </c>
       <c r="S23" s="4" t="n">
-        <v>5.29</v>
+        <v>30.89</v>
       </c>
       <c r="T23" s="4" t="n">
-        <v>-8.16</v>
-      </c>
-      <c r="U23" s="4" t="n">
-        <v>135.86</v>
+        <v>-8.619999999999999</v>
+      </c>
+      <c r="U23" s="4" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
       </c>
       <c r="V23" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-INCY-20260909-bb0ff1</t>
+          <t>USA-R1-CRM-20260814-be7c1c</t>
         </is>
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -2267,47 +2293,47 @@
       </c>
       <c r="B24" s="4" t="inlineStr">
         <is>
-          <t>SMCI</t>
+          <t>HOOD</t>
         </is>
       </c>
       <c r="C24" s="4" t="inlineStr">
         <is>
-          <t>R2</t>
+          <t>R1</t>
         </is>
       </c>
       <c r="D24" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not reviewed · R3 covers R2 candidates only</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-09-08</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-08</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H24" s="4" t="n">
-        <v>40.26</v>
+        <v>103.51</v>
       </c>
       <c r="I24" s="4" t="n">
-        <v>36.74</v>
+        <v>114.33</v>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K24" s="7" t="n">
-        <v>-8.74</v>
+      <c r="K24" s="5" t="n">
+        <v>10.45</v>
       </c>
       <c r="L24" s="4" t="inlineStr">
         <is>
@@ -2316,11 +2342,11 @@
       </c>
       <c r="M24" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N24" s="5" t="n">
-        <v>25609435171.5677</v>
+          <t>Financial Services</t>
+        </is>
+      </c>
+      <c r="N24" s="6" t="n">
+        <v>102801629812.6475</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
@@ -2333,7 +2359,7 @@
         </is>
       </c>
       <c r="Q24" s="4" t="n">
-        <v>33.3468</v>
+        <v>91.0157</v>
       </c>
       <c r="R24" s="4" t="inlineStr">
         <is>
@@ -2341,22 +2367,22 @@
         </is>
       </c>
       <c r="S24" s="4" t="n">
-        <v>9.24</v>
+        <v>20.39</v>
       </c>
       <c r="T24" s="4" t="n">
-        <v>-17.17</v>
+        <v>-12.07</v>
       </c>
       <c r="U24" s="4" t="n">
-        <v>46.92</v>
+        <v>122.25</v>
       </c>
       <c r="V24" s="4" t="inlineStr">
         <is>
-          <t>USA-R2-SMCI-20260908-c2c66b</t>
+          <t>USA-R1-HOOD-20260901-b8d64b</t>
         </is>
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2394,7 @@
       </c>
       <c r="B25" s="4" t="inlineStr">
         <is>
-          <t>GRMN</t>
+          <t>VLO</t>
         </is>
       </c>
       <c r="C25" s="4" t="inlineStr">
@@ -2378,7 +2404,7 @@
       </c>
       <c r="D25" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E25" s="4" t="inlineStr">
@@ -2397,18 +2423,18 @@
         </is>
       </c>
       <c r="H25" s="4" t="n">
-        <v>274.11</v>
+        <v>361.99</v>
       </c>
       <c r="I25" s="4" t="n">
-        <v>280.38</v>
+        <v>382.95</v>
       </c>
       <c r="J25" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K25" s="6" t="n">
-        <v>2.29</v>
+      <c r="K25" s="5" t="n">
+        <v>5.79</v>
       </c>
       <c r="L25" s="4" t="inlineStr">
         <is>
@@ -2417,11 +2443,11 @@
       </c>
       <c r="M25" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N25" s="5" t="n">
-        <v>53431824008.73483</v>
+          <t>Energy</t>
+        </is>
+      </c>
+      <c r="N25" s="6" t="n">
+        <v>110255433210.2225</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
@@ -2434,7 +2460,7 @@
         </is>
       </c>
       <c r="Q25" s="4" t="n">
-        <v>260.921</v>
+        <v>342.2271</v>
       </c>
       <c r="R25" s="4" t="inlineStr">
         <is>
@@ -2442,17 +2468,17 @@
         </is>
       </c>
       <c r="S25" s="4" t="n">
-        <v>6.94</v>
+        <v>10.63</v>
       </c>
       <c r="T25" s="4" t="n">
-        <v>-4.81</v>
+        <v>-5.46</v>
       </c>
       <c r="U25" s="4" t="n">
-        <v>293.89</v>
+        <v>391.63</v>
       </c>
       <c r="V25" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-GRMN-20260901-4c77f2</t>
+          <t>USA-R1-VLO-20260901-3c6acd</t>
         </is>
       </c>
       <c r="W25" s="4" t="inlineStr">
@@ -2469,7 +2495,7 @@
       </c>
       <c r="B26" s="4" t="inlineStr">
         <is>
-          <t>IT</t>
+          <t>FTNT</t>
         </is>
       </c>
       <c r="C26" s="4" t="inlineStr">
@@ -2479,7 +2505,7 @@
       </c>
       <c r="D26" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E26" s="4" t="inlineStr">
@@ -2489,27 +2515,27 @@
       </c>
       <c r="F26" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G26" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H26" s="4" t="n">
-        <v>193.17</v>
+        <v>161.85</v>
       </c>
       <c r="I26" s="4" t="n">
-        <v>197.07</v>
+        <v>170.18</v>
       </c>
       <c r="J26" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K26" s="6" t="n">
-        <v>2.02</v>
+      <c r="K26" s="5" t="n">
+        <v>5.15</v>
       </c>
       <c r="L26" s="4" t="inlineStr">
         <is>
@@ -2521,8 +2547,8 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N26" s="5" t="n">
-        <v>11773348509.40141</v>
+      <c r="N26" s="6" t="n">
+        <v>124853292615.9492</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
@@ -2535,7 +2561,7 @@
         </is>
       </c>
       <c r="Q26" s="4" t="n">
-        <v>170.3286</v>
+        <v>147.9529</v>
       </c>
       <c r="R26" s="4" t="inlineStr">
         <is>
@@ -2543,17 +2569,17 @@
         </is>
       </c>
       <c r="S26" s="4" t="n">
-        <v>13.57</v>
+        <v>13.06</v>
       </c>
       <c r="T26" s="4" t="n">
-        <v>-11.82</v>
+        <v>-8.59</v>
       </c>
       <c r="U26" s="4" t="n">
-        <v>227.43</v>
+        <v>182.7</v>
       </c>
       <c r="V26" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-IT-20260810-04dfbc</t>
+          <t>USA-R1-FTNT-20260901-30d75e</t>
         </is>
       </c>
       <c r="W26" s="4" t="inlineStr">
@@ -2570,7 +2596,7 @@
       </c>
       <c r="B27" s="4" t="inlineStr">
         <is>
-          <t>BMY</t>
+          <t>SAIC</t>
         </is>
       </c>
       <c r="C27" s="4" t="inlineStr">
@@ -2580,7 +2606,7 @@
       </c>
       <c r="D27" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E27" s="4" t="inlineStr">
@@ -2599,18 +2625,18 @@
         </is>
       </c>
       <c r="H27" s="4" t="n">
-        <v>63.83</v>
+        <v>126.68</v>
       </c>
       <c r="I27" s="4" t="n">
-        <v>64.09999999999999</v>
+        <v>132.01</v>
       </c>
       <c r="J27" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K27" s="6" t="n">
-        <v>0.42</v>
+      <c r="K27" s="5" t="n">
+        <v>4.21</v>
       </c>
       <c r="L27" s="4" t="inlineStr">
         <is>
@@ -2619,11 +2645,11 @@
       </c>
       <c r="M27" s="4" t="inlineStr">
         <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N27" s="5" t="n">
-        <v>136489737964.495</v>
+          <t>Technology</t>
+        </is>
+      </c>
+      <c r="N27" s="6" t="n">
+        <v>5530953407.403122</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
@@ -2632,11 +2658,11 @@
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n">
-        <v>60.0271</v>
+        <v>119.43</v>
       </c>
       <c r="R27" s="4" t="inlineStr">
         <is>
@@ -2644,17 +2670,17 @@
         </is>
       </c>
       <c r="S27" s="4" t="n">
-        <v>6.35</v>
+        <v>9.529999999999999</v>
       </c>
       <c r="T27" s="4" t="n">
-        <v>-5.96</v>
+        <v>-5.72</v>
       </c>
       <c r="U27" s="4" t="n">
-        <v>69.53</v>
+        <v>137.55</v>
       </c>
       <c r="V27" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-BMY-20260814-a3b600</t>
+          <t>USA-R1-SAIC-20260814-889ae8</t>
         </is>
       </c>
       <c r="W27" s="4" t="inlineStr">
@@ -2671,7 +2697,7 @@
       </c>
       <c r="B28" s="4" t="inlineStr">
         <is>
-          <t>MSFT</t>
+          <t>EXPD</t>
         </is>
       </c>
       <c r="C28" s="4" t="inlineStr">
@@ -2681,7 +2707,7 @@
       </c>
       <c r="D28" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E28" s="4" t="inlineStr">
@@ -2691,27 +2717,27 @@
       </c>
       <c r="F28" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-09-01</t>
         </is>
       </c>
       <c r="G28" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="H28" s="4" t="n">
-        <v>505.11</v>
+        <v>187.7</v>
       </c>
       <c r="I28" s="4" t="n">
-        <v>505.41</v>
+        <v>193.61</v>
       </c>
       <c r="J28" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K28" s="6" t="n">
-        <v>0.06</v>
+      <c r="K28" s="5" t="n">
+        <v>3.15</v>
       </c>
       <c r="L28" s="4" t="inlineStr">
         <is>
@@ -2720,11 +2746,11 @@
       </c>
       <c r="M28" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N28" s="5" t="n">
-        <v>3710222886174.651</v>
+          <t>Industrials</t>
+        </is>
+      </c>
+      <c r="N28" s="6" t="n">
+        <v>25165177616.14645</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
@@ -2737,7 +2763,7 @@
         </is>
       </c>
       <c r="Q28" s="4" t="n">
-        <v>469.0698</v>
+        <v>180.8543</v>
       </c>
       <c r="R28" s="4" t="inlineStr">
         <is>
@@ -2745,17 +2771,17 @@
         </is>
       </c>
       <c r="S28" s="4" t="n">
-        <v>7.19</v>
+        <v>6.59</v>
       </c>
       <c r="T28" s="4" t="n">
-        <v>-7.13</v>
+        <v>-3.65</v>
       </c>
       <c r="U28" s="4" t="n">
-        <v>559.17</v>
+        <v>197.97</v>
       </c>
       <c r="V28" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-MSFT-20260810-6110fc</t>
+          <t>USA-R1-EXPD-20260901-065905</t>
         </is>
       </c>
       <c r="W28" s="4" t="inlineStr">
@@ -2772,7 +2798,7 @@
       </c>
       <c r="B29" s="4" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>FOX</t>
         </is>
       </c>
       <c r="C29" s="4" t="inlineStr">
@@ -2782,7 +2808,7 @@
       </c>
       <c r="D29" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E29" s="4" t="inlineStr">
@@ -2792,27 +2818,27 @@
       </c>
       <c r="F29" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-08-19</t>
         </is>
       </c>
       <c r="G29" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H29" s="4" t="n">
-        <v>175.23</v>
+        <v>60.09</v>
       </c>
       <c r="I29" s="4" t="n">
-        <v>173.31</v>
+        <v>61.14</v>
       </c>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K29" s="7" t="n">
-        <v>-1.1</v>
+      <c r="K29" s="5" t="n">
+        <v>1.74</v>
       </c>
       <c r="L29" s="4" t="inlineStr">
         <is>
@@ -2821,11 +2847,11 @@
       </c>
       <c r="M29" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N29" s="5" t="n">
-        <v>418890007002.7825</v>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="N29" s="6" t="n">
+        <v>25703957827.68865</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
@@ -2838,7 +2864,7 @@
         </is>
       </c>
       <c r="Q29" s="4" t="n">
-        <v>155.965</v>
+        <v>56.6217</v>
       </c>
       <c r="R29" s="4" t="inlineStr">
         <is>
@@ -2846,17 +2872,17 @@
         </is>
       </c>
       <c r="S29" s="4" t="n">
-        <v>10.01</v>
+        <v>7.39</v>
       </c>
       <c r="T29" s="4" t="n">
-        <v>-10.99</v>
+        <v>-5.78</v>
       </c>
       <c r="U29" s="4" t="n">
-        <v>204.13</v>
+        <v>65.3</v>
       </c>
       <c r="V29" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-PLTR-20260810-5c4552</t>
+          <t>USA-R1-FOX-20260819-7b9e84</t>
         </is>
       </c>
       <c r="W29" s="4" t="inlineStr">
@@ -2873,7 +2899,7 @@
       </c>
       <c r="B30" s="4" t="inlineStr">
         <is>
-          <t>ADBE</t>
+          <t>GOOGL</t>
         </is>
       </c>
       <c r="C30" s="4" t="inlineStr">
@@ -2883,7 +2909,7 @@
       </c>
       <c r="D30" s="4" t="inlineStr">
         <is>
-          <t>ACTIVE+</t>
+          <t>ACTIVE</t>
         </is>
       </c>
       <c r="E30" s="4" t="inlineStr">
@@ -2893,27 +2919,27 @@
       </c>
       <c r="F30" s="4" t="inlineStr">
         <is>
-          <t>Admitted 2026-08-10</t>
+          <t>Admitted 2026-08-19</t>
         </is>
       </c>
       <c r="G30" s="4" t="inlineStr">
         <is>
-          <t>2026-08-10</t>
+          <t>2026-08-19</t>
         </is>
       </c>
       <c r="H30" s="4" t="n">
-        <v>272.96</v>
+        <v>344.5</v>
       </c>
       <c r="I30" s="4" t="n">
-        <v>265.6</v>
+        <v>349.39</v>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="K30" s="7" t="n">
-        <v>-2.7</v>
+      <c r="K30" s="5" t="n">
+        <v>1.42</v>
       </c>
       <c r="L30" s="4" t="inlineStr">
         <is>
@@ -2922,11 +2948,11 @@
       </c>
       <c r="M30" s="4" t="inlineStr">
         <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N30" s="5" t="n">
-        <v>105949765544.345</v>
+          <t>Communication Services</t>
+        </is>
+      </c>
+      <c r="N30" s="6" t="n">
+        <v>4272676381599.783</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
@@ -2939,7 +2965,7 @@
         </is>
       </c>
       <c r="Q30" s="4" t="n">
-        <v>247.1386</v>
+        <v>323.138</v>
       </c>
       <c r="R30" s="4" t="inlineStr">
         <is>
@@ -2947,17 +2973,17 @@
         </is>
       </c>
       <c r="S30" s="4" t="n">
-        <v>6.95</v>
+        <v>7.51</v>
       </c>
       <c r="T30" s="4" t="n">
-        <v>-9.460000000000001</v>
+        <v>-6.2</v>
       </c>
       <c r="U30" s="4" t="n">
-        <v>311.69</v>
+        <v>376.54</v>
       </c>
       <c r="V30" s="4" t="inlineStr">
         <is>
-          <t>USA-R1-ADBE-20260810-4ad164</t>
+          <t>USA-R1-GOOGL-20260819-1fce1a</t>
         </is>
       </c>
       <c r="W30" s="4" t="inlineStr">
@@ -2966,1364 +2992,150 @@
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B31" s="4" t="inlineStr">
-        <is>
-          <t>UBER</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D31" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE+</t>
-        </is>
-      </c>
-      <c r="E31" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F31" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-10</t>
-        </is>
-      </c>
-      <c r="G31" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H31" s="4" t="n">
-        <v>78.03</v>
-      </c>
-      <c r="I31" s="4" t="n">
-        <v>72.63</v>
-      </c>
-      <c r="J31" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K31" s="7" t="n">
-        <v>-6.92</v>
-      </c>
-      <c r="L31" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M31" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N31" s="5" t="n">
-        <v>154739076282.088</v>
-      </c>
-      <c r="O31" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P31" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q31" s="4" t="n">
-        <v>72.40940000000001</v>
-      </c>
-      <c r="R31" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S31" s="4" t="n">
-        <v>0.3</v>
-      </c>
-      <c r="T31" s="4" t="n">
-        <v>-7.2</v>
-      </c>
-      <c r="U31" s="4" t="n">
-        <v>86.45999999999999</v>
-      </c>
-      <c r="V31" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-UBER-20260810-3f4c24</t>
-        </is>
-      </c>
-      <c r="W31" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B32" s="4" t="inlineStr">
-        <is>
-          <t>V</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D32" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E32" s="4" t="inlineStr">
-        <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
-        </is>
-      </c>
-      <c r="F32" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-10</t>
-        </is>
-      </c>
-      <c r="G32" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-10</t>
-        </is>
-      </c>
-      <c r="H32" s="4" t="n">
-        <v>360.65</v>
-      </c>
-      <c r="I32" s="4" t="n">
-        <v>375.28</v>
-      </c>
-      <c r="J32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K32" s="6" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="L32" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M32" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="N32" s="5" t="n">
-        <v>700325596737.0536</v>
-      </c>
-      <c r="O32" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P32" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q32" s="4" t="n">
-        <v>364.7557</v>
-      </c>
-      <c r="R32" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S32" s="4" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="T32" s="4" t="n">
-        <v>1.14</v>
-      </c>
-      <c r="U32" s="4" t="n">
-        <v>384</v>
-      </c>
-      <c r="V32" s="4" t="inlineStr">
-        <is>
-          <t>USA-R2-V-20260810-69160d</t>
-        </is>
-      </c>
-      <c r="W32" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
-        </is>
-      </c>
-    </row>
     <row r="33">
-      <c r="A33" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B33" s="4" t="inlineStr">
-        <is>
-          <t>BMY</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D33" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E33" s="4" t="inlineStr">
-        <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
-        </is>
-      </c>
-      <c r="F33" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-11</t>
-        </is>
-      </c>
-      <c r="G33" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H33" s="4" t="n">
-        <v>63.61</v>
-      </c>
-      <c r="I33" s="4" t="n">
-        <v>64.09999999999999</v>
-      </c>
-      <c r="J33" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K33" s="6" t="n">
-        <v>0.77</v>
-      </c>
-      <c r="L33" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M33" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N33" s="5" t="n">
-        <v>136489737964.495</v>
-      </c>
-      <c r="O33" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P33" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q33" s="4" t="n">
-        <v>61.4986</v>
-      </c>
-      <c r="R33" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S33" s="4" t="n">
-        <v>4.06</v>
-      </c>
-      <c r="T33" s="4" t="n">
-        <v>-3.32</v>
-      </c>
-      <c r="U33" s="4" t="n">
-        <v>69.45</v>
-      </c>
-      <c r="V33" s="4" t="inlineStr">
-        <is>
-          <t>USA-R2-BMY-20260811-c99117</t>
-        </is>
-      </c>
-      <c r="W33" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
         </is>
       </c>
     </row>
     <row r="34">
-      <c r="A34" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B34" s="4" t="inlineStr">
-        <is>
-          <t>DXCM</t>
-        </is>
-      </c>
-      <c r="C34" s="4" t="inlineStr">
-        <is>
-          <t>R2</t>
-        </is>
-      </c>
-      <c r="D34" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E34" s="4" t="inlineStr">
-        <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
-        </is>
-      </c>
-      <c r="F34" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-11</t>
-        </is>
-      </c>
-      <c r="G34" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-11</t>
-        </is>
-      </c>
-      <c r="H34" s="4" t="n">
-        <v>89.53</v>
-      </c>
-      <c r="I34" s="4" t="n">
-        <v>84.68000000000001</v>
-      </c>
-      <c r="J34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K34" s="7" t="n">
-        <v>-5.42</v>
-      </c>
-      <c r="L34" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M34" s="4" t="inlineStr">
-        <is>
-          <t>Healthcare</t>
-        </is>
-      </c>
-      <c r="N34" s="5" t="n">
-        <v>33166527215.04348</v>
-      </c>
-      <c r="O34" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P34" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q34" s="4" t="n">
-        <v>79.8471</v>
-      </c>
-      <c r="R34" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S34" s="4" t="n">
-        <v>5.71</v>
-      </c>
-      <c r="T34" s="4" t="n">
-        <v>-10.82</v>
-      </c>
-      <c r="U34" s="4" t="n">
-        <v>99.06</v>
-      </c>
-      <c r="V34" s="4" t="inlineStr">
-        <is>
-          <t>USA-R2-DXCM-20260811-b3de8c</t>
-        </is>
-      </c>
-      <c r="W34" s="4" t="inlineStr">
-        <is>
-          <t>HOLD · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
         </is>
       </c>
     </row>
     <row r="35">
-      <c r="A35" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B35" s="4" t="inlineStr">
-        <is>
-          <t>CRM</t>
-        </is>
-      </c>
-      <c r="C35" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D35" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E35" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F35" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-14</t>
-        </is>
-      </c>
-      <c r="G35" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="H35" s="4" t="n">
-        <v>196.21</v>
-      </c>
-      <c r="I35" s="4" t="n">
-        <v>259.43</v>
-      </c>
-      <c r="J35" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K35" s="6" t="n">
-        <v>32.22</v>
-      </c>
-      <c r="L35" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M35" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N35" s="5" t="n">
-        <v>213353612143.8822</v>
-      </c>
-      <c r="O35" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P35" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q35" s="4" t="n">
-        <v>179.3029</v>
-      </c>
-      <c r="R35" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S35" s="4" t="n">
-        <v>30.89</v>
-      </c>
-      <c r="T35" s="4" t="n">
-        <v>-8.619999999999999</v>
-      </c>
-      <c r="U35" s="4" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="V35" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-CRM-20260814-be7c1c</t>
-        </is>
-      </c>
-      <c r="W35" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
         </is>
       </c>
     </row>
     <row r="36">
-      <c r="A36" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B36" s="4" t="inlineStr">
-        <is>
-          <t>HOOD</t>
-        </is>
-      </c>
-      <c r="C36" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D36" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E36" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F36" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-09-01</t>
-        </is>
-      </c>
-      <c r="G36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H36" s="4" t="n">
-        <v>103.51</v>
-      </c>
-      <c r="I36" s="4" t="n">
-        <v>114.33</v>
-      </c>
-      <c r="J36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K36" s="6" t="n">
-        <v>10.45</v>
-      </c>
-      <c r="L36" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M36" s="4" t="inlineStr">
-        <is>
-          <t>Financial Services</t>
-        </is>
-      </c>
-      <c r="N36" s="5" t="n">
-        <v>109799408364.9603</v>
-      </c>
-      <c r="O36" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P36" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q36" s="4" t="n">
-        <v>91.0157</v>
-      </c>
-      <c r="R36" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S36" s="4" t="n">
-        <v>20.39</v>
-      </c>
-      <c r="T36" s="4" t="n">
-        <v>-12.07</v>
-      </c>
-      <c r="U36" s="4" t="n">
-        <v>122.25</v>
-      </c>
-      <c r="V36" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-HOOD-20260901-b8d64b</t>
-        </is>
-      </c>
-      <c r="W36" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
         </is>
       </c>
     </row>
     <row r="37">
-      <c r="A37" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B37" s="4" t="inlineStr">
-        <is>
-          <t>VLO</t>
-        </is>
-      </c>
-      <c r="C37" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D37" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E37" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F37" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-09-01</t>
-        </is>
-      </c>
-      <c r="G37" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H37" s="4" t="n">
-        <v>361.99</v>
-      </c>
-      <c r="I37" s="4" t="n">
-        <v>382.95</v>
-      </c>
-      <c r="J37" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K37" s="6" t="n">
-        <v>5.79</v>
-      </c>
-      <c r="L37" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M37" s="4" t="inlineStr">
-        <is>
-          <t>Energy</t>
-        </is>
-      </c>
-      <c r="N37" s="5" t="n">
-        <v>106733315426.1837</v>
-      </c>
-      <c r="O37" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P37" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q37" s="4" t="n">
-        <v>342.2271</v>
-      </c>
-      <c r="R37" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S37" s="4" t="n">
-        <v>10.63</v>
-      </c>
-      <c r="T37" s="4" t="n">
-        <v>-5.46</v>
-      </c>
-      <c r="U37" s="4" t="n">
-        <v>391.63</v>
-      </c>
-      <c r="V37" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-VLO-20260901-3c6acd</t>
-        </is>
-      </c>
-      <c r="W37" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A37" s="8" t="inlineStr">
+        <is>
+          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
         </is>
       </c>
     </row>
     <row r="38">
-      <c r="A38" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B38" s="4" t="inlineStr">
-        <is>
-          <t>FTNT</t>
-        </is>
-      </c>
-      <c r="C38" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D38" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E38" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F38" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-09-01</t>
-        </is>
-      </c>
-      <c r="G38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H38" s="4" t="n">
-        <v>161.85</v>
-      </c>
-      <c r="I38" s="4" t="n">
-        <v>170.18</v>
-      </c>
-      <c r="J38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K38" s="6" t="n">
-        <v>5.15</v>
-      </c>
-      <c r="L38" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M38" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N38" s="5" t="n">
-        <v>114683252142.2478</v>
-      </c>
-      <c r="O38" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P38" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q38" s="4" t="n">
-        <v>147.9529</v>
-      </c>
-      <c r="R38" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S38" s="4" t="n">
-        <v>13.06</v>
-      </c>
-      <c r="T38" s="4" t="n">
-        <v>-8.59</v>
-      </c>
-      <c r="U38" s="4" t="n">
-        <v>182.7</v>
-      </c>
-      <c r="V38" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-FTNT-20260901-30d75e</t>
-        </is>
-      </c>
-      <c r="W38" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A38" s="8" t="inlineStr">
+        <is>
+          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
         </is>
       </c>
     </row>
     <row r="39">
-      <c r="A39" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B39" s="4" t="inlineStr">
-        <is>
-          <t>SAIC</t>
-        </is>
-      </c>
-      <c r="C39" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D39" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E39" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F39" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-14</t>
-        </is>
-      </c>
-      <c r="G39" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-14</t>
-        </is>
-      </c>
-      <c r="H39" s="4" t="n">
-        <v>126.68</v>
-      </c>
-      <c r="I39" s="4" t="n">
-        <v>132.01</v>
-      </c>
-      <c r="J39" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K39" s="6" t="n">
-        <v>4.21</v>
-      </c>
-      <c r="L39" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M39" s="4" t="inlineStr">
-        <is>
-          <t>Technology</t>
-        </is>
-      </c>
-      <c r="N39" s="5" t="n">
-        <v>5310066989.662829</v>
-      </c>
-      <c r="O39" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P39" s="4" t="inlineStr">
-        <is>
-          <t>Mid</t>
-        </is>
-      </c>
-      <c r="Q39" s="4" t="n">
-        <v>119.43</v>
-      </c>
-      <c r="R39" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S39" s="4" t="n">
-        <v>9.529999999999999</v>
-      </c>
-      <c r="T39" s="4" t="n">
-        <v>-5.72</v>
-      </c>
-      <c r="U39" s="4" t="n">
-        <v>137.55</v>
-      </c>
-      <c r="V39" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-SAIC-20260814-889ae8</t>
-        </is>
-      </c>
-      <c r="W39" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A39" s="8" t="inlineStr">
+        <is>
+          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
         </is>
       </c>
     </row>
     <row r="40">
-      <c r="A40" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B40" s="4" t="inlineStr">
-        <is>
-          <t>EXPD</t>
-        </is>
-      </c>
-      <c r="C40" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D40" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E40" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F40" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-09-01</t>
-        </is>
-      </c>
-      <c r="G40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-01</t>
-        </is>
-      </c>
-      <c r="H40" s="4" t="n">
-        <v>187.7</v>
-      </c>
-      <c r="I40" s="4" t="n">
-        <v>193.61</v>
-      </c>
-      <c r="J40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K40" s="6" t="n">
-        <v>3.15</v>
-      </c>
-      <c r="L40" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M40" s="4" t="inlineStr">
-        <is>
-          <t>Industrials</t>
-        </is>
-      </c>
-      <c r="N40" s="5" t="n">
-        <v>24541437631.37434</v>
-      </c>
-      <c r="O40" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P40" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q40" s="4" t="n">
-        <v>180.8543</v>
-      </c>
-      <c r="R40" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S40" s="4" t="n">
-        <v>6.59</v>
-      </c>
-      <c r="T40" s="4" t="n">
-        <v>-3.65</v>
-      </c>
-      <c r="U40" s="4" t="n">
-        <v>197.97</v>
-      </c>
-      <c r="V40" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-EXPD-20260901-065905</t>
-        </is>
-      </c>
-      <c r="W40" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A40" s="8" t="inlineStr">
+        <is>
+          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
         </is>
       </c>
     </row>
     <row r="41">
-      <c r="A41" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B41" s="4" t="inlineStr">
-        <is>
-          <t>FOX</t>
-        </is>
-      </c>
-      <c r="C41" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D41" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E41" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F41" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-19</t>
-        </is>
-      </c>
-      <c r="G41" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="H41" s="4" t="n">
-        <v>60.09</v>
-      </c>
-      <c r="I41" s="4" t="n">
-        <v>61.14</v>
-      </c>
-      <c r="J41" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K41" s="6" t="n">
-        <v>1.74</v>
-      </c>
-      <c r="L41" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M41" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="N41" s="5" t="n">
-        <v>24564051543.2472</v>
-      </c>
-      <c r="O41" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P41" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q41" s="4" t="n">
-        <v>56.6217</v>
-      </c>
-      <c r="R41" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S41" s="4" t="n">
-        <v>7.39</v>
-      </c>
-      <c r="T41" s="4" t="n">
-        <v>-5.78</v>
-      </c>
-      <c r="U41" s="4" t="n">
-        <v>65.3</v>
-      </c>
-      <c r="V41" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-FOX-20260819-7b9e84</t>
-        </is>
-      </c>
-      <c r="W41" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A41" s="8" t="inlineStr">
+        <is>
+          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
         </is>
       </c>
     </row>
     <row r="42">
-      <c r="A42" s="4" t="inlineStr">
-        <is>
-          <t>USA</t>
-        </is>
-      </c>
-      <c r="B42" s="4" t="inlineStr">
-        <is>
-          <t>GOOGL</t>
-        </is>
-      </c>
-      <c r="C42" s="4" t="inlineStr">
-        <is>
-          <t>R1</t>
-        </is>
-      </c>
-      <c r="D42" s="4" t="inlineStr">
-        <is>
-          <t>ACTIVE</t>
-        </is>
-      </c>
-      <c r="E42" s="4" t="inlineStr">
-        <is>
-          <t>Not reviewed · R3 covers R2 candidates only</t>
-        </is>
-      </c>
-      <c r="F42" s="4" t="inlineStr">
-        <is>
-          <t>Admitted 2026-08-19</t>
-        </is>
-      </c>
-      <c r="G42" s="4" t="inlineStr">
-        <is>
-          <t>2026-08-19</t>
-        </is>
-      </c>
-      <c r="H42" s="4" t="n">
-        <v>344.5</v>
-      </c>
-      <c r="I42" s="4" t="n">
-        <v>349.39</v>
-      </c>
-      <c r="J42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-14</t>
-        </is>
-      </c>
-      <c r="K42" s="6" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="L42" s="4" t="inlineStr">
-        <is>
-          <t>Historical score unavailable</t>
-        </is>
-      </c>
-      <c r="M42" s="4" t="inlineStr">
-        <is>
-          <t>Communication Services</t>
-        </is>
-      </c>
-      <c r="N42" s="5" t="n">
-        <v>4139043588458.335</v>
-      </c>
-      <c r="O42" s="4" t="inlineStr">
-        <is>
-          <t>2026-09-15</t>
-        </is>
-      </c>
-      <c r="P42" s="4" t="inlineStr">
-        <is>
-          <t>Large</t>
-        </is>
-      </c>
-      <c r="Q42" s="4" t="n">
-        <v>323.138</v>
-      </c>
-      <c r="R42" s="4" t="inlineStr">
-        <is>
-          <t>INTACT</t>
-        </is>
-      </c>
-      <c r="S42" s="4" t="n">
-        <v>7.51</v>
-      </c>
-      <c r="T42" s="4" t="n">
-        <v>-6.2</v>
-      </c>
-      <c r="U42" s="4" t="n">
-        <v>376.54</v>
-      </c>
-      <c r="V42" s="4" t="inlineStr">
-        <is>
-          <t>USA-R1-GOOGL-20260819-1fce1a</t>
-        </is>
-      </c>
-      <c r="W42" s="4" t="inlineStr">
-        <is>
-          <t>R1 ADVISORY · suggested stop only · never auto-exited</t>
+      <c r="A42" s="8" t="inlineStr">
+        <is>
+          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="8" t="inlineStr">
+        <is>
+          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="8" t="inlineStr">
+        <is>
+          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="8" t="inlineStr">
         <is>
-          <t>Stop distance % · the DOWNSIDE from the current price to the stop. It is not a profit target and no target is implied by it.</t>
+          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="8" t="inlineStr">
         <is>
-          <t>Target · withheld (—) when the stored target sits at or below the current price · a target already passed is not a target.</t>
+          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="8" t="inlineStr">
         <is>
-          <t>R3 SHADOW is RESEARCH ONLY. It describes an R2 candidate and never changes one · R2 Action, Confidence and Stop in this row were decided without reading any R3 value.</t>
+          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="8" t="inlineStr">
         <is>
-          <t>ABSTAIN = insufficient validated evidence. It is NOT Hold, Buy, Avoid, or a 50/50 probability. Every row reads ABSTAIN today because no R3 specialist has passed its evidence gate.</t>
+          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" s="8" t="inlineStr">
         <is>
-          <t>A future AVOID is a research annotation · it never implies an R2 EXIT. Only explicit authorisation can make R3 actionable.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="8" t="inlineStr">
-        <is>
-          <t>No probability is shown. An uncalibrated model can always produce a number; months later nobody could tell it apart from one that meant something.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="8" t="inlineStr">
-        <is>
-          <t>The full specialist decomposition (fundamental · statistical · temporal · sector · risk · uncertainty · model version · evidence tier · OOS · calibration · provenance) is kept in the R3 shadow ledger and research artifacts · it belongs in the audit trail, not beside a Stop price.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="8" t="inlineStr">
-        <is>
-          <t>CURRENT is the daily recommendation · everything AEGIS considers investable right now. Non-investable states (WATCH, REVIEW, AVOID, research-only) are filtered from this VIEW · they remain in the backend research artifacts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="8" t="inlineStr">
-        <is>
-          <t>Every value here is rendered from the canonical lifecycle dataset produced upstream in the same pipeline run. This sheet computes nothing, so it cannot disagree with the engines.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="8" t="inlineStr">
-        <is>
-          <t>Engine · R2 production · MOMENTUM upstream (never bypasses R2 governance) · R1 ADVISORY, which carries no dynamic-exit protection and is never auto-exited.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="8" t="inlineStr">
-        <is>
-          <t>Action · NEW (became investable today) · ACTIVE+ (already active, on a BUY-family signal) · ACTIVE. EXIT never appears here · an exit moves the row to EXIT HISTORY.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="8" t="inlineStr">
-        <is>
-          <t>Stop · R2 uses the canonical dynamic_risk_v2 value, ENFORCED. R1 shows an ATR-14 SUGGESTED level that is advisory and NOT enforced.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="8" t="inlineStr">
-        <is>
-          <t>Stop State · INTACT (price above the stop) · NO STOP (no stop could be derived). BREACHED never appears here: a position trading below its stop is not investable, so it transitions to EXIT HISTORY the day the breach is first observed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="8" t="inlineStr">
-        <is>
-          <t>Dist to Stop % · how far price must fall before the stop fires. Max Loss if Stop % · worst case FROM ENTRY if the stop fires today.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="8" t="inlineStr">
-        <is>
-          <t>The breach transition is a DELIVERY rule, not a trading rule. No engine changed: R1 remains advisory and is still never auto-exited, R2 keeps its enforced dynamic_risk_v2 stop, and no position was closed in the registry. Only the investor view moved.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="8" t="inlineStr">
-        <is>
-          <t>A losing position that is still active stays visible with its negative P&amp;L. Losses are never hidden or restated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="8" t="inlineStr">
-        <is>
           <t>The 🔎 line answers "why is NEW zero today?" from the lifecycle reconciler · every scored name gets exactly one verdict (reports/context/why_not_current_{market}.json). A zero here is never presented without its reason.</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="23">
-    <mergeCell ref="A58:W58"/>
+    <mergeCell ref="A44:W44"/>
+    <mergeCell ref="A40:W40"/>
+    <mergeCell ref="A34:W34"/>
     <mergeCell ref="A48:W48"/>
-    <mergeCell ref="A59:W59"/>
+    <mergeCell ref="A39:W39"/>
     <mergeCell ref="A49:W49"/>
-    <mergeCell ref="A51:W51"/>
-    <mergeCell ref="A60:W60"/>
+    <mergeCell ref="A36:W36"/>
     <mergeCell ref="A1:W1"/>
     <mergeCell ref="A45:W45"/>
-    <mergeCell ref="A61:W61"/>
     <mergeCell ref="A6:W6"/>
-    <mergeCell ref="A54:W54"/>
+    <mergeCell ref="A41:W41"/>
     <mergeCell ref="A46:W46"/>
-    <mergeCell ref="A56:W56"/>
-    <mergeCell ref="A50:W50"/>
+    <mergeCell ref="A37:W37"/>
     <mergeCell ref="A3:W3"/>
-    <mergeCell ref="A55:W55"/>
-    <mergeCell ref="A57:W57"/>
     <mergeCell ref="A2:W2"/>
+    <mergeCell ref="A33:W33"/>
     <mergeCell ref="A47:W47"/>
+    <mergeCell ref="A42:W42"/>
     <mergeCell ref="A5:W5"/>
-    <mergeCell ref="A53:W53"/>
+    <mergeCell ref="A35:W35"/>
     <mergeCell ref="A4:W4"/>
-    <mergeCell ref="A52:W52"/>
+    <mergeCell ref="A38:W38"/>
+    <mergeCell ref="A43:W43"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4501,7 +3313,7 @@
       <c r="I5" s="4" t="n">
         <v>197.07</v>
       </c>
-      <c r="J5" s="6" t="n">
+      <c r="J5" s="5" t="n">
         <v>2.02</v>
       </c>
       <c r="K5" s="4" t="n">
@@ -5759,7 +4571,7 @@
       <c r="I22" s="4" t="n">
         <v>77.52</v>
       </c>
-      <c r="J22" s="6" t="n">
+      <c r="J22" s="5" t="n">
         <v>2.88</v>
       </c>
       <c r="K22" s="4" t="n">
@@ -5907,7 +4719,7 @@
       <c r="I24" s="4" t="n">
         <v>101.38</v>
       </c>
-      <c r="J24" s="6" t="n">
+      <c r="J24" s="5" t="n">
         <v>4.27</v>
       </c>
       <c r="K24" s="4" t="n">
@@ -5981,7 +4793,7 @@
       <c r="I25" s="4" t="n">
         <v>153.64</v>
       </c>
-      <c r="J25" s="6" t="n">
+      <c r="J25" s="5" t="n">
         <v>6.67</v>
       </c>
       <c r="K25" s="4" t="n">
@@ -6055,7 +4867,7 @@
       <c r="I26" s="4" t="n">
         <v>83.09999999999999</v>
       </c>
-      <c r="J26" s="6" t="n">
+      <c r="J26" s="5" t="n">
         <v>5.1</v>
       </c>
       <c r="K26" s="4" t="n">
@@ -6277,7 +5089,7 @@
       <c r="I29" s="4" t="n">
         <v>77.68000000000001</v>
       </c>
-      <c r="J29" s="6" t="n">
+      <c r="J29" s="5" t="n">
         <v>0.03</v>
       </c>
       <c r="K29" s="4" t="n">
@@ -6499,7 +5311,7 @@
       <c r="I32" s="4" t="n">
         <v>343.12</v>
       </c>
-      <c r="J32" s="6" t="n">
+      <c r="J32" s="5" t="n">
         <v>0.21</v>
       </c>
       <c r="K32" s="4" t="n">
@@ -6573,7 +5385,7 @@
       <c r="I33" s="4" t="n">
         <v>343.12</v>
       </c>
-      <c r="J33" s="6" t="n">
+      <c r="J33" s="5" t="n">
         <v>0.21</v>
       </c>
       <c r="K33" s="4" t="n">
@@ -6943,7 +5755,7 @@
       <c r="I38" s="4" t="n">
         <v>73.87</v>
       </c>
-      <c r="J38" s="6" t="n">
+      <c r="J38" s="5" t="n">
         <v>2.9</v>
       </c>
       <c r="K38" s="4" t="n">
@@ -7165,7 +5977,7 @@
       <c r="I41" s="4" t="n">
         <v>241.56</v>
       </c>
-      <c r="J41" s="6" t="n">
+      <c r="J41" s="5" t="n">
         <v>7.28</v>
       </c>
       <c r="K41" s="4" t="n">
@@ -7239,7 +6051,7 @@
       <c r="I42" s="4" t="n">
         <v>107.52</v>
       </c>
-      <c r="J42" s="6" t="n">
+      <c r="J42" s="5" t="n">
         <v>1.67</v>
       </c>
       <c r="K42" s="4" t="n">
@@ -7313,7 +6125,7 @@
       <c r="I43" s="4" t="n">
         <v>468.73</v>
       </c>
-      <c r="J43" s="6" t="n">
+      <c r="J43" s="5" t="n">
         <v>7.07</v>
       </c>
       <c r="K43" s="4" t="n">
@@ -7387,7 +6199,7 @@
       <c r="I44" s="4" t="n">
         <v>190.75</v>
       </c>
-      <c r="J44" s="6" t="n">
+      <c r="J44" s="5" t="n">
         <v>5.23</v>
       </c>
       <c r="K44" s="4" t="n">
@@ -7461,7 +6273,7 @@
       <c r="I45" s="4" t="n">
         <v>28.75</v>
       </c>
-      <c r="J45" s="6" t="n">
+      <c r="J45" s="5" t="n">
         <v>6.21</v>
       </c>
       <c r="K45" s="4" t="n">
@@ -7609,7 +6421,7 @@
       <c r="I47" s="4" t="n">
         <v>300.54</v>
       </c>
-      <c r="J47" s="6" t="n">
+      <c r="J47" s="5" t="n">
         <v>0.9399999999999999</v>
       </c>
       <c r="K47" s="4" t="n">
@@ -7683,7 +6495,7 @@
       <c r="I48" s="4" t="n">
         <v>50.19</v>
       </c>
-      <c r="J48" s="6" t="n">
+      <c r="J48" s="5" t="n">
         <v>6.18</v>
       </c>
       <c r="K48" s="4" t="n">
@@ -7757,7 +6569,7 @@
       <c r="I49" s="4" t="n">
         <v>16.85</v>
       </c>
-      <c r="J49" s="6" t="n">
+      <c r="J49" s="5" t="n">
         <v>4.28</v>
       </c>
       <c r="K49" s="4" t="n">
@@ -7831,7 +6643,7 @@
       <c r="I50" s="4" t="n">
         <v>93.5</v>
       </c>
-      <c r="J50" s="6" t="n">
+      <c r="J50" s="5" t="n">
         <v>7.52</v>
       </c>
       <c r="K50" s="4" t="n">
@@ -7979,7 +6791,7 @@
       <c r="I52" s="4" t="n">
         <v>547.29</v>
       </c>
-      <c r="J52" s="6" t="n">
+      <c r="J52" s="5" t="n">
         <v>3.33</v>
       </c>
       <c r="K52" s="4" t="n">
@@ -8127,7 +6939,7 @@
       <c r="I54" s="4" t="n">
         <v>292.99</v>
       </c>
-      <c r="J54" s="6" t="n">
+      <c r="J54" s="5" t="n">
         <v>2.16</v>
       </c>
       <c r="K54" s="4" t="n">
@@ -8201,7 +7013,7 @@
       <c r="I55" s="4" t="n">
         <v>187.87</v>
       </c>
-      <c r="J55" s="6" t="n">
+      <c r="J55" s="5" t="n">
         <v>3.81</v>
       </c>
       <c r="K55" s="4" t="n">
@@ -8349,7 +7161,7 @@
       <c r="I57" s="4" t="n">
         <v>98.69</v>
       </c>
-      <c r="J57" s="6" t="n">
+      <c r="J57" s="5" t="n">
         <v>0.73</v>
       </c>
       <c r="K57" s="4" t="n">
@@ -8423,7 +7235,7 @@
       <c r="I58" s="4" t="n">
         <v>348.03</v>
       </c>
-      <c r="J58" s="6" t="n">
+      <c r="J58" s="5" t="n">
         <v>7.44</v>
       </c>
       <c r="K58" s="4" t="n">
@@ -8497,7 +7309,7 @@
       <c r="I59" s="4" t="n">
         <v>26</v>
       </c>
-      <c r="J59" s="6" t="n">
+      <c r="J59" s="5" t="n">
         <v>0.08</v>
       </c>
       <c r="K59" s="4" t="n">
@@ -8571,7 +7383,7 @@
       <c r="I60" s="4" t="n">
         <v>244.91</v>
       </c>
-      <c r="J60" s="6" t="n">
+      <c r="J60" s="5" t="n">
         <v>3.52</v>
       </c>
       <c r="K60" s="4" t="n">
@@ -8645,7 +7457,7 @@
       <c r="I61" s="4" t="n">
         <v>383.9</v>
       </c>
-      <c r="J61" s="6" t="n">
+      <c r="J61" s="5" t="n">
         <v>6.45</v>
       </c>
       <c r="K61" s="4" t="n">
@@ -8867,7 +7679,7 @@
       <c r="I64" s="4" t="n">
         <v>105.65</v>
       </c>
-      <c r="J64" s="6" t="n">
+      <c r="J64" s="5" t="n">
         <v>2.78</v>
       </c>
       <c r="K64" s="4" t="n">
@@ -8941,7 +7753,7 @@
       <c r="I65" s="4" t="n">
         <v>309.19</v>
       </c>
-      <c r="J65" s="6" t="n">
+      <c r="J65" s="5" t="n">
         <v>6.06</v>
       </c>
       <c r="K65" s="4" t="n">
@@ -9089,7 +7901,7 @@
       <c r="I67" s="4" t="n">
         <v>543.1900000000001</v>
       </c>
-      <c r="J67" s="6" t="n">
+      <c r="J67" s="5" t="n">
         <v>0.34</v>
       </c>
       <c r="K67" s="4" t="n">
@@ -9163,7 +7975,7 @@
       <c r="I68" s="4" t="n">
         <v>178.48</v>
       </c>
-      <c r="J68" s="6" t="n">
+      <c r="J68" s="5" t="n">
         <v>5.91</v>
       </c>
       <c r="K68" s="4" t="n">
@@ -9237,7 +8049,7 @@
       <c r="I69" s="4" t="n">
         <v>37.93</v>
       </c>
-      <c r="J69" s="6" t="n">
+      <c r="J69" s="5" t="n">
         <v>2.08</v>
       </c>
       <c r="K69" s="4" t="n">
@@ -9385,7 +8197,7 @@
       <c r="I71" s="4" t="n">
         <v>352.65</v>
       </c>
-      <c r="J71" s="6" t="n">
+      <c r="J71" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K71" s="4" t="n">
@@ -9755,7 +8567,7 @@
       <c r="I76" s="4" t="n">
         <v>56.03</v>
       </c>
-      <c r="J76" s="6" t="n">
+      <c r="J76" s="5" t="n">
         <v>0.21</v>
       </c>
       <c r="K76" s="4" t="n">
@@ -9829,7 +8641,7 @@
       <c r="I77" s="4" t="n">
         <v>345.82</v>
       </c>
-      <c r="J77" s="6" t="n">
+      <c r="J77" s="5" t="n">
         <v>3.91</v>
       </c>
       <c r="K77" s="4" t="n">
@@ -10125,7 +8937,7 @@
       <c r="I81" s="4" t="n">
         <v>59.68</v>
       </c>
-      <c r="J81" s="6" t="n">
+      <c r="J81" s="5" t="n">
         <v>2.93</v>
       </c>
       <c r="K81" s="4" t="n">
@@ -10199,7 +9011,7 @@
       <c r="I82" s="4" t="n">
         <v>294.03</v>
       </c>
-      <c r="J82" s="6" t="n">
+      <c r="J82" s="5" t="n">
         <v>10.77</v>
       </c>
       <c r="K82" s="4" t="n">
@@ -10347,7 +9159,7 @@
       <c r="I84" s="4" t="n">
         <v>368.81</v>
       </c>
-      <c r="J84" s="6" t="n">
+      <c r="J84" s="5" t="n">
         <v>1.21</v>
       </c>
       <c r="K84" s="4" t="n">
@@ -10421,7 +9233,7 @@
       <c r="I85" s="4" t="n">
         <v>178.58</v>
       </c>
-      <c r="J85" s="6" t="n">
+      <c r="J85" s="5" t="n">
         <v>0.58</v>
       </c>
       <c r="K85" s="4" t="n">
@@ -10495,7 +9307,7 @@
       <c r="I86" s="4" t="n">
         <v>633.71</v>
       </c>
-      <c r="J86" s="6" t="n">
+      <c r="J86" s="5" t="n">
         <v>4.75</v>
       </c>
       <c r="K86" s="4" t="n">
@@ -10717,7 +9529,7 @@
       <c r="I89" s="4" t="n">
         <v>164.04</v>
       </c>
-      <c r="J89" s="6" t="n">
+      <c r="J89" s="5" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="K89" s="4" t="n">
@@ -10791,7 +9603,7 @@
       <c r="I90" s="4" t="n">
         <v>164.04</v>
       </c>
-      <c r="J90" s="6" t="n">
+      <c r="J90" s="5" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="K90" s="4" t="n">
@@ -11161,7 +9973,7 @@
       <c r="I95" s="4" t="n">
         <v>72.38</v>
       </c>
-      <c r="J95" s="6" t="n">
+      <c r="J95" s="5" t="n">
         <v>0.43</v>
       </c>
       <c r="K95" s="4" t="n">
@@ -11383,7 +10195,7 @@
       <c r="I98" s="4" t="n">
         <v>41.61</v>
       </c>
-      <c r="J98" s="6" t="n">
+      <c r="J98" s="5" t="n">
         <v>0.26</v>
       </c>
       <c r="K98" s="4" t="n">
@@ -11457,7 +10269,7 @@
       <c r="I99" s="4" t="n">
         <v>25.87</v>
       </c>
-      <c r="J99" s="6" t="n">
+      <c r="J99" s="5" t="n">
         <v>5.59</v>
       </c>
       <c r="K99" s="4" t="n">
@@ -11679,7 +10491,7 @@
       <c r="I102" s="4" t="n">
         <v>79.78</v>
       </c>
-      <c r="J102" s="6" t="n">
+      <c r="J102" s="5" t="n">
         <v>1.67</v>
       </c>
       <c r="K102" s="4" t="n">
@@ -11901,7 +10713,7 @@
       <c r="I105" s="4" t="n">
         <v>49.56</v>
       </c>
-      <c r="J105" s="6" t="n">
+      <c r="J105" s="5" t="n">
         <v>0.79</v>
       </c>
       <c r="K105" s="4" t="n">
@@ -11975,7 +10787,7 @@
       <c r="I106" s="4" t="n">
         <v>134.45</v>
       </c>
-      <c r="J106" s="6" t="n">
+      <c r="J106" s="5" t="n">
         <v>0.35</v>
       </c>
       <c r="K106" s="4" t="n">
@@ -12049,7 +10861,7 @@
       <c r="I107" s="4" t="n">
         <v>846.37</v>
       </c>
-      <c r="J107" s="6" t="n">
+      <c r="J107" s="5" t="n">
         <v>3.15</v>
       </c>
       <c r="K107" s="4" t="n">
@@ -12123,7 +10935,7 @@
       <c r="I108" s="4" t="n">
         <v>193.62</v>
       </c>
-      <c r="J108" s="6" t="n">
+      <c r="J108" s="5" t="n">
         <v>3.42</v>
       </c>
       <c r="K108" s="4" t="n">
@@ -12419,7 +11231,7 @@
       <c r="I112" s="4" t="n">
         <v>436.49</v>
       </c>
-      <c r="J112" s="6" t="n">
+      <c r="J112" s="5" t="n">
         <v>7.04</v>
       </c>
       <c r="K112" s="4" t="n">
@@ -12567,7 +11379,7 @@
       <c r="I114" s="4" t="n">
         <v>91.53</v>
       </c>
-      <c r="J114" s="6" t="n">
+      <c r="J114" s="5" t="n">
         <v>8.83</v>
       </c>
       <c r="K114" s="4" t="n">
@@ -12789,7 +11601,7 @@
       <c r="I117" s="4" t="n">
         <v>1499.37</v>
       </c>
-      <c r="J117" s="6" t="n">
+      <c r="J117" s="5" t="n">
         <v>17.96</v>
       </c>
       <c r="K117" s="4" t="n">
@@ -13011,7 +11823,7 @@
       <c r="I120" s="4" t="n">
         <v>130.9</v>
       </c>
-      <c r="J120" s="6" t="n">
+      <c r="J120" s="5" t="n">
         <v>12.6</v>
       </c>
       <c r="K120" s="4" t="n">
@@ -13159,7 +11971,7 @@
       <c r="I122" s="4" t="n">
         <v>109.39</v>
       </c>
-      <c r="J122" s="6" t="n">
+      <c r="J122" s="5" t="n">
         <v>1.87</v>
       </c>
       <c r="K122" s="4" t="n">
@@ -13233,7 +12045,7 @@
       <c r="I123" s="4" t="n">
         <v>108.49</v>
       </c>
-      <c r="J123" s="6" t="n">
+      <c r="J123" s="5" t="n">
         <v>2.3</v>
       </c>
       <c r="K123" s="4" t="n">
@@ -13307,7 +12119,7 @@
       <c r="I124" s="4" t="n">
         <v>185.98</v>
       </c>
-      <c r="J124" s="6" t="n">
+      <c r="J124" s="5" t="n">
         <v>2.91</v>
       </c>
       <c r="K124" s="4" t="n">
@@ -13381,7 +12193,7 @@
       <c r="I125" s="4" t="n">
         <v>126.35</v>
       </c>
-      <c r="J125" s="6" t="n">
+      <c r="J125" s="5" t="n">
         <v>9.18</v>
       </c>
       <c r="K125" s="4" t="n">
@@ -13603,7 +12415,7 @@
       <c r="I128" s="4" t="n">
         <v>222.18</v>
       </c>
-      <c r="J128" s="6" t="n">
+      <c r="J128" s="5" t="n">
         <v>3.3</v>
       </c>
       <c r="K128" s="4" t="n">
@@ -13751,7 +12563,7 @@
       <c r="I130" s="4" t="n">
         <v>413.28</v>
       </c>
-      <c r="J130" s="6" t="n">
+      <c r="J130" s="5" t="n">
         <v>3.45</v>
       </c>
       <c r="K130" s="4" t="n">
@@ -13973,7 +12785,7 @@
       <c r="I133" s="4" t="n">
         <v>235.69</v>
       </c>
-      <c r="J133" s="6" t="n">
+      <c r="J133" s="5" t="n">
         <v>5.13</v>
       </c>
       <c r="K133" s="4" t="n">
@@ -14269,7 +13081,7 @@
       <c r="I137" s="4" t="n">
         <v>814.79</v>
       </c>
-      <c r="J137" s="6" t="n">
+      <c r="J137" s="5" t="n">
         <v>2.35</v>
       </c>
       <c r="K137" s="4" t="n">
@@ -14343,7 +13155,7 @@
       <c r="I138" s="4" t="n">
         <v>75.61</v>
       </c>
-      <c r="J138" s="6" t="n">
+      <c r="J138" s="5" t="n">
         <v>0.74</v>
       </c>
       <c r="K138" s="4" t="n">
@@ -14491,7 +13303,7 @@
       <c r="I140" s="4" t="n">
         <v>162.83</v>
       </c>
-      <c r="J140" s="6" t="n">
+      <c r="J140" s="5" t="n">
         <v>0.64</v>
       </c>
       <c r="K140" s="4" t="n">
@@ -14639,7 +13451,7 @@
       <c r="I142" s="4" t="n">
         <v>61.66</v>
       </c>
-      <c r="J142" s="6" t="n">
+      <c r="J142" s="5" t="n">
         <v>4.76</v>
       </c>
       <c r="K142" s="4" t="n">
@@ -14861,7 +13673,7 @@
       <c r="I145" s="4" t="n">
         <v>151.61</v>
       </c>
-      <c r="J145" s="6" t="n">
+      <c r="J145" s="5" t="n">
         <v>0.78</v>
       </c>
       <c r="K145" s="4" t="n">
@@ -14935,7 +13747,7 @@
       <c r="I146" s="4" t="n">
         <v>242.23</v>
       </c>
-      <c r="J146" s="6" t="n">
+      <c r="J146" s="5" t="n">
         <v>8.539999999999999</v>
       </c>
       <c r="K146" s="4" t="n">
@@ -15009,7 +13821,7 @@
       <c r="I147" s="4" t="n">
         <v>10.74</v>
       </c>
-      <c r="J147" s="6" t="n">
+      <c r="J147" s="5" t="n">
         <v>14.5</v>
       </c>
       <c r="K147" s="4" t="n">
@@ -15675,7 +14487,7 @@
       <c r="I156" s="4" t="n">
         <v>194.1</v>
       </c>
-      <c r="J156" s="6" t="n">
+      <c r="J156" s="5" t="n">
         <v>4.23</v>
       </c>
       <c r="K156" s="4" t="n">
@@ -15749,7 +14561,7 @@
       <c r="I157" s="4" t="n">
         <v>142.59</v>
       </c>
-      <c r="J157" s="6" t="n">
+      <c r="J157" s="5" t="n">
         <v>2.22</v>
       </c>
       <c r="K157" s="4" t="n">
@@ -15971,7 +14783,7 @@
       <c r="I160" s="4" t="n">
         <v>222.51</v>
       </c>
-      <c r="J160" s="6" t="n">
+      <c r="J160" s="5" t="n">
         <v>4.78</v>
       </c>
       <c r="K160" s="4" t="n">
@@ -16193,7 +15005,7 @@
       <c r="I163" s="4" t="n">
         <v>28.3</v>
       </c>
-      <c r="J163" s="6" t="n">
+      <c r="J163" s="5" t="n">
         <v>6.31</v>
       </c>
       <c r="K163" s="4" t="n">
@@ -16267,7 +15079,7 @@
       <c r="I164" s="4" t="n">
         <v>140.69</v>
       </c>
-      <c r="J164" s="6" t="n">
+      <c r="J164" s="5" t="n">
         <v>2.73</v>
       </c>
       <c r="K164" s="4" t="n">
@@ -16415,7 +15227,7 @@
       <c r="I166" s="4" t="n">
         <v>18.22</v>
       </c>
-      <c r="J166" s="6" t="n">
+      <c r="J166" s="5" t="n">
         <v>5.32</v>
       </c>
       <c r="K166" s="4" t="n">
@@ -16563,7 +15375,7 @@
       <c r="I168" s="4" t="n">
         <v>124.88</v>
       </c>
-      <c r="J168" s="6" t="n">
+      <c r="J168" s="5" t="n">
         <v>2.95</v>
       </c>
       <c r="K168" s="4" t="n">
@@ -16933,7 +15745,7 @@
       <c r="I173" s="4" t="n">
         <v>148.87</v>
       </c>
-      <c r="J173" s="6" t="n">
+      <c r="J173" s="5" t="n">
         <v>2.33</v>
       </c>
       <c r="K173" s="4" t="n">
@@ -17081,7 +15893,7 @@
       <c r="I175" s="4" t="n">
         <v>87.89</v>
       </c>
-      <c r="J175" s="6" t="n">
+      <c r="J175" s="5" t="n">
         <v>2.26</v>
       </c>
       <c r="K175" s="4" t="n">
@@ -17155,7 +15967,7 @@
       <c r="I176" s="4" t="n">
         <v>94.90000000000001</v>
       </c>
-      <c r="J176" s="6" t="n">
+      <c r="J176" s="5" t="n">
         <v>3.69</v>
       </c>
       <c r="K176" s="4" t="n">
@@ -17303,7 +16115,7 @@
       <c r="I178" s="4" t="n">
         <v>61.99</v>
       </c>
-      <c r="J178" s="6" t="n">
+      <c r="J178" s="5" t="n">
         <v>0.6</v>
       </c>
       <c r="K178" s="4" t="n">
@@ -17451,7 +16263,7 @@
       <c r="I180" s="4" t="n">
         <v>14.27</v>
       </c>
-      <c r="J180" s="6" t="n">
+      <c r="J180" s="5" t="n">
         <v>0.59</v>
       </c>
       <c r="K180" s="4" t="n">
@@ -17525,7 +16337,7 @@
       <c r="I181" s="4" t="n">
         <v>30.86</v>
       </c>
-      <c r="J181" s="6" t="n">
+      <c r="J181" s="5" t="n">
         <v>8.140000000000001</v>
       </c>
       <c r="K181" s="4" t="n">
@@ -17599,7 +16411,7 @@
       <c r="I182" s="4" t="n">
         <v>35.13</v>
       </c>
-      <c r="J182" s="6" t="n">
+      <c r="J182" s="5" t="n">
         <v>7.87</v>
       </c>
       <c r="K182" s="4" t="n">
@@ -18117,7 +16929,7 @@
       <c r="I189" s="4" t="n">
         <v>352.68</v>
       </c>
-      <c r="J189" s="6" t="n">
+      <c r="J189" s="5" t="n">
         <v>5.4</v>
       </c>
       <c r="K189" s="4" t="n">
@@ -18561,7 +17373,7 @@
       <c r="I195" s="4" t="n">
         <v>81.45999999999999</v>
       </c>
-      <c r="J195" s="6" t="n">
+      <c r="J195" s="5" t="n">
         <v>8.92</v>
       </c>
       <c r="K195" s="4" t="n">
@@ -18635,7 +17447,7 @@
       <c r="I196" s="4" t="n">
         <v>131.33</v>
       </c>
-      <c r="J196" s="6" t="n">
+      <c r="J196" s="5" t="n">
         <v>12.28</v>
       </c>
       <c r="K196" s="4" t="n">
@@ -18783,7 +17595,7 @@
       <c r="I198" s="4" t="n">
         <v>333.58</v>
       </c>
-      <c r="J198" s="6" t="n">
+      <c r="J198" s="5" t="n">
         <v>7.46</v>
       </c>
       <c r="K198" s="4" t="n">
@@ -18857,7 +17669,7 @@
       <c r="I199" s="4" t="n">
         <v>99.13</v>
       </c>
-      <c r="J199" s="6" t="n">
+      <c r="J199" s="5" t="n">
         <v>4.68</v>
       </c>
       <c r="K199" s="4" t="n">
@@ -19005,7 +17817,7 @@
       <c r="I201" s="4" t="n">
         <v>938.4</v>
       </c>
-      <c r="J201" s="6" t="n">
+      <c r="J201" s="5" t="n">
         <v>8.050000000000001</v>
       </c>
       <c r="K201" s="4" t="n">
@@ -19301,7 +18113,7 @@
       <c r="I205" s="4" t="n">
         <v>487.28</v>
       </c>
-      <c r="J205" s="6" t="n">
+      <c r="J205" s="5" t="n">
         <v>4.37</v>
       </c>
       <c r="K205" s="4" t="n">
@@ -19375,7 +18187,7 @@
       <c r="I206" s="4" t="n">
         <v>564.22</v>
       </c>
-      <c r="J206" s="6" t="n">
+      <c r="J206" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="K206" s="4" t="n">
@@ -19523,7 +18335,7 @@
       <c r="I208" s="4" t="n">
         <v>245.11</v>
       </c>
-      <c r="J208" s="6" t="n">
+      <c r="J208" s="5" t="n">
         <v>15.45</v>
       </c>
       <c r="K208" s="4" t="n">
@@ -19597,7 +18409,7 @@
       <c r="I209" s="4" t="n">
         <v>193.26</v>
       </c>
-      <c r="J209" s="6" t="n">
+      <c r="J209" s="5" t="n">
         <v>1.05</v>
       </c>
       <c r="K209" s="4" t="n">
@@ -19671,7 +18483,7 @@
       <c r="I210" s="4" t="n">
         <v>149.66</v>
       </c>
-      <c r="J210" s="6" t="n">
+      <c r="J210" s="5" t="n">
         <v>147.09</v>
       </c>
       <c r="K210" s="4" t="n">
@@ -19745,7 +18557,7 @@
       <c r="I211" s="4" t="n">
         <v>153.1</v>
       </c>
-      <c r="J211" s="6" t="n">
+      <c r="J211" s="5" t="n">
         <v>17.39</v>
       </c>
       <c r="K211" s="4" t="n">
@@ -19893,7 +18705,7 @@
       <c r="I213" s="4" t="n">
         <v>362.27</v>
       </c>
-      <c r="J213" s="6" t="n">
+      <c r="J213" s="5" t="n">
         <v>7.98</v>
       </c>
       <c r="K213" s="4" t="n">
@@ -19967,7 +18779,7 @@
       <c r="I214" s="4" t="n">
         <v>69.12</v>
       </c>
-      <c r="J214" s="6" t="n">
+      <c r="J214" s="5" t="n">
         <v>6.29</v>
       </c>
       <c r="K214" s="4" t="n">
@@ -20041,7 +18853,7 @@
       <c r="I215" s="4" t="n">
         <v>47.81</v>
       </c>
-      <c r="J215" s="6" t="n">
+      <c r="J215" s="5" t="n">
         <v>5.01</v>
       </c>
       <c r="K215" s="4" t="n">
@@ -20263,7 +19075,7 @@
       <c r="I218" s="4" t="n">
         <v>55.1</v>
       </c>
-      <c r="J218" s="6" t="n">
+      <c r="J218" s="5" t="n">
         <v>4.18</v>
       </c>
       <c r="K218" s="4" t="n">
@@ -20559,7 +19371,7 @@
       <c r="I222" s="4" t="n">
         <v>92.02</v>
       </c>
-      <c r="J222" s="6" t="n">
+      <c r="J222" s="5" t="n">
         <v>1.48</v>
       </c>
       <c r="K222" s="4" t="n">
@@ -20633,7 +19445,7 @@
       <c r="I223" s="4" t="n">
         <v>63.01</v>
       </c>
-      <c r="J223" s="6" t="n">
+      <c r="J223" s="5" t="n">
         <v>1.99</v>
       </c>
       <c r="K223" s="4" t="n">
@@ -20707,7 +19519,7 @@
       <c r="I224" s="4" t="n">
         <v>514.55</v>
       </c>
-      <c r="J224" s="6" t="n">
+      <c r="J224" s="5" t="n">
         <v>8.220000000000001</v>
       </c>
       <c r="K224" s="4" t="n">
@@ -20929,7 +19741,7 @@
       <c r="I227" s="4" t="n">
         <v>358.67</v>
       </c>
-      <c r="J227" s="6" t="n">
+      <c r="J227" s="5" t="n">
         <v>2.84</v>
       </c>
       <c r="K227" s="4" t="n">
@@ -21077,7 +19889,7 @@
       <c r="I229" s="4" t="n">
         <v>598.47</v>
       </c>
-      <c r="J229" s="6" t="n">
+      <c r="J229" s="5" t="n">
         <v>6.6</v>
       </c>
       <c r="K229" s="4" t="n">
@@ -21299,7 +20111,7 @@
       <c r="I232" s="4" t="n">
         <v>46.23</v>
       </c>
-      <c r="J232" s="6" t="n">
+      <c r="J232" s="5" t="n">
         <v>1.12</v>
       </c>
       <c r="K232" s="4" t="n">
@@ -21521,7 +20333,7 @@
       <c r="I235" s="4" t="n">
         <v>312.88</v>
       </c>
-      <c r="J235" s="6" t="n">
+      <c r="J235" s="5" t="n">
         <v>0.47</v>
       </c>
       <c r="K235" s="4" t="n">
@@ -21669,7 +20481,7 @@
       <c r="I237" s="4" t="n">
         <v>68.92</v>
       </c>
-      <c r="J237" s="6" t="n">
+      <c r="J237" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="K237" s="4" t="n">
@@ -21891,7 +20703,7 @@
       <c r="I240" s="4" t="n">
         <v>939.03</v>
       </c>
-      <c r="J240" s="6" t="n">
+      <c r="J240" s="5" t="n">
         <v>14.43</v>
       </c>
       <c r="K240" s="4" t="n">
@@ -22187,7 +20999,7 @@
       <c r="I244" s="4" t="n">
         <v>335</v>
       </c>
-      <c r="J244" s="6" t="n">
+      <c r="J244" s="5" t="n">
         <v>4.13</v>
       </c>
       <c r="K244" s="4" t="n">
@@ -22261,7 +21073,7 @@
       <c r="I245" s="4" t="n">
         <v>335</v>
       </c>
-      <c r="J245" s="6" t="n">
+      <c r="J245" s="5" t="n">
         <v>4.13</v>
       </c>
       <c r="K245" s="4" t="n">
@@ -22557,7 +21369,7 @@
       <c r="I249" s="4" t="n">
         <v>19.22</v>
       </c>
-      <c r="J249" s="6" t="n">
+      <c r="J249" s="5" t="n">
         <v>2.02</v>
       </c>
       <c r="K249" s="4" t="n">
@@ -22631,7 +21443,7 @@
       <c r="I250" s="4" t="n">
         <v>58.51</v>
       </c>
-      <c r="J250" s="6" t="n">
+      <c r="J250" s="5" t="n">
         <v>4.73</v>
       </c>
       <c r="K250" s="4" t="n">
@@ -22705,7 +21517,7 @@
       <c r="I251" s="4" t="n">
         <v>90.08</v>
       </c>
-      <c r="J251" s="6" t="n">
+      <c r="J251" s="5" t="n">
         <v>3.7</v>
       </c>
       <c r="K251" s="4" t="n">
@@ -22779,7 +21591,7 @@
       <c r="I252" s="4" t="n">
         <v>32.02</v>
       </c>
-      <c r="J252" s="6" t="n">
+      <c r="J252" s="5" t="n">
         <v>1.72</v>
       </c>
       <c r="K252" s="4" t="n">
@@ -22853,7 +21665,7 @@
       <c r="I253" s="4" t="n">
         <v>109.03</v>
       </c>
-      <c r="J253" s="6" t="n">
+      <c r="J253" s="5" t="n">
         <v>1.63</v>
       </c>
       <c r="K253" s="4" t="n">
@@ -23075,7 +21887,7 @@
       <c r="I256" s="4" t="n">
         <v>23.75</v>
       </c>
-      <c r="J256" s="6" t="n">
+      <c r="J256" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="K256" s="4" t="n">
@@ -23149,7 +21961,7 @@
       <c r="I257" s="4" t="n">
         <v>24.4</v>
       </c>
-      <c r="J257" s="6" t="n">
+      <c r="J257" s="5" t="n">
         <v>0.57</v>
       </c>
       <c r="K257" s="4" t="n">
@@ -23371,7 +22183,7 @@
       <c r="I260" s="4" t="n">
         <v>32.21</v>
       </c>
-      <c r="J260" s="6" t="n">
+      <c r="J260" s="5" t="n">
         <v>10.38</v>
       </c>
       <c r="K260" s="4" t="n">
@@ -23519,7 +22331,7 @@
       <c r="I262" s="4" t="n">
         <v>270</v>
       </c>
-      <c r="J262" s="6" t="n">
+      <c r="J262" s="5" t="n">
         <v>4.44</v>
       </c>
       <c r="K262" s="4" t="n">
@@ -23593,7 +22405,7 @@
       <c r="I263" s="4" t="n">
         <v>171.77</v>
       </c>
-      <c r="J263" s="6" t="n">
+      <c r="J263" s="5" t="n">
         <v>12.21</v>
       </c>
       <c r="K263" s="4" t="n">
@@ -23889,7 +22701,7 @@
       <c r="I267" s="4" t="n">
         <v>151.52</v>
       </c>
-      <c r="J267" s="6" t="n">
+      <c r="J267" s="5" t="n">
         <v>2.89</v>
       </c>
       <c r="K267" s="4" t="n">
@@ -23963,7 +22775,7 @@
       <c r="I268" s="4" t="n">
         <v>32.98</v>
       </c>
-      <c r="J268" s="6" t="n">
+      <c r="J268" s="5" t="n">
         <v>5.87</v>
       </c>
       <c r="K268" s="4" t="n">
@@ -24407,7 +23219,7 @@
       <c r="I274" s="4" t="n">
         <v>261.51</v>
       </c>
-      <c r="J274" s="6" t="n">
+      <c r="J274" s="5" t="n">
         <v>7.25</v>
       </c>
       <c r="K274" s="4" t="n">
@@ -24481,7 +23293,7 @@
       <c r="I275" s="4" t="n">
         <v>41.39</v>
       </c>
-      <c r="J275" s="6" t="n">
+      <c r="J275" s="5" t="n">
         <v>0.15</v>
       </c>
       <c r="K275" s="4" t="n">
@@ -24555,7 +23367,7 @@
       <c r="I276" s="4" t="n">
         <v>29.89</v>
       </c>
-      <c r="J276" s="6" t="n">
+      <c r="J276" s="5" t="n">
         <v>0.34</v>
       </c>
       <c r="K276" s="4" t="n">
@@ -24629,7 +23441,7 @@
       <c r="I277" s="4" t="n">
         <v>345.88</v>
       </c>
-      <c r="J277" s="6" t="n">
+      <c r="J277" s="5" t="n">
         <v>2.81</v>
       </c>
       <c r="K277" s="4" t="n">
@@ -24703,7 +23515,7 @@
       <c r="I278" s="4" t="n">
         <v>128.12</v>
       </c>
-      <c r="J278" s="6" t="n">
+      <c r="J278" s="5" t="n">
         <v>5.82</v>
       </c>
       <c r="K278" s="4" t="n">
@@ -24777,7 +23589,7 @@
       <c r="I279" s="4" t="n">
         <v>87.12</v>
       </c>
-      <c r="J279" s="6" t="n">
+      <c r="J279" s="5" t="n">
         <v>2.49</v>
       </c>
       <c r="K279" s="4" t="n">
@@ -24999,7 +23811,7 @@
       <c r="I282" s="4" t="n">
         <v>161.92</v>
       </c>
-      <c r="J282" s="6" t="n">
+      <c r="J282" s="5" t="n">
         <v>7.05</v>
       </c>
       <c r="K282" s="4" t="n">
@@ -25147,7 +23959,7 @@
       <c r="I284" s="4" t="n">
         <v>96.93000000000001</v>
       </c>
-      <c r="J284" s="6" t="n">
+      <c r="J284" s="5" t="n">
         <v>8.06</v>
       </c>
       <c r="K284" s="4" t="n">
@@ -25295,7 +24107,7 @@
       <c r="I286" s="4" t="n">
         <v>391.06</v>
       </c>
-      <c r="J286" s="6" t="n">
+      <c r="J286" s="5" t="n">
         <v>4.89</v>
       </c>
       <c r="K286" s="4" t="n">
@@ -25443,7 +24255,7 @@
       <c r="I288" s="4" t="n">
         <v>185.35</v>
       </c>
-      <c r="J288" s="6" t="n">
+      <c r="J288" s="5" t="n">
         <v>2.65</v>
       </c>
       <c r="K288" s="4" t="n">
@@ -25517,7 +24329,7 @@
       <c r="I289" s="4" t="n">
         <v>22.43</v>
       </c>
-      <c r="J289" s="6" t="n">
+      <c r="J289" s="5" t="n">
         <v>0.63</v>
       </c>
       <c r="K289" s="4" t="n">
@@ -25591,7 +24403,7 @@
       <c r="I290" s="4" t="n">
         <v>90.38</v>
       </c>
-      <c r="J290" s="6" t="n">
+      <c r="J290" s="5" t="n">
         <v>1.35</v>
       </c>
       <c r="K290" s="4" t="n">
@@ -25739,7 +24551,7 @@
       <c r="I292" s="4" t="n">
         <v>30.23</v>
       </c>
-      <c r="J292" s="6" t="n">
+      <c r="J292" s="5" t="n">
         <v>4.99</v>
       </c>
       <c r="K292" s="4" t="n">
@@ -25813,7 +24625,7 @@
       <c r="I293" s="4" t="n">
         <v>55.23</v>
       </c>
-      <c r="J293" s="6" t="n">
+      <c r="J293" s="5" t="n">
         <v>1.56</v>
       </c>
       <c r="K293" s="4" t="n">
@@ -25887,7 +24699,7 @@
       <c r="I294" s="4" t="n">
         <v>108.54</v>
       </c>
-      <c r="J294" s="6" t="n">
+      <c r="J294" s="5" t="n">
         <v>15</v>
       </c>
       <c r="K294" s="4" t="n">
@@ -26035,7 +24847,7 @@
       <c r="I296" s="4" t="n">
         <v>332.56</v>
       </c>
-      <c r="J296" s="6" t="n">
+      <c r="J296" s="5" t="n">
         <v>5.74</v>
       </c>
       <c r="K296" s="4" t="n">
@@ -26183,7 +24995,7 @@
       <c r="I298" s="4" t="n">
         <v>139.25</v>
       </c>
-      <c r="J298" s="6" t="n">
+      <c r="J298" s="5" t="n">
         <v>0.5600000000000001</v>
       </c>
       <c r="K298" s="4" t="n">
@@ -26257,7 +25069,7 @@
       <c r="I299" s="4" t="n">
         <v>427.16</v>
       </c>
-      <c r="J299" s="6" t="n">
+      <c r="J299" s="5" t="n">
         <v>3.82</v>
       </c>
       <c r="K299" s="4" t="n">
@@ -26479,7 +25291,7 @@
       <c r="I302" s="4" t="n">
         <v>34.28</v>
       </c>
-      <c r="J302" s="6" t="n">
+      <c r="J302" s="5" t="n">
         <v>1.89</v>
       </c>
       <c r="K302" s="4" t="n">
@@ -26553,7 +25365,7 @@
       <c r="I303" s="4" t="n">
         <v>1335.39</v>
       </c>
-      <c r="J303" s="6" t="n">
+      <c r="J303" s="5" t="n">
         <v>2.57</v>
       </c>
       <c r="K303" s="4" t="n">
@@ -26627,7 +25439,7 @@
       <c r="I304" s="4" t="n">
         <v>1035.39</v>
       </c>
-      <c r="J304" s="6" t="n">
+      <c r="J304" s="5" t="n">
         <v>0.58</v>
       </c>
       <c r="K304" s="4" t="n">
@@ -26775,7 +25587,7 @@
       <c r="I306" s="4" t="n">
         <v>92.7</v>
       </c>
-      <c r="J306" s="6" t="n">
+      <c r="J306" s="5" t="n">
         <v>8.27</v>
       </c>
       <c r="K306" s="4" t="n">
@@ -26849,7 +25661,7 @@
       <c r="I307" s="4" t="n">
         <v>138.41</v>
       </c>
-      <c r="J307" s="6" t="n">
+      <c r="J307" s="5" t="n">
         <v>3.26</v>
       </c>
       <c r="K307" s="4" t="n">
@@ -27293,7 +26105,7 @@
       <c r="I313" s="4" t="n">
         <v>40.08</v>
       </c>
-      <c r="J313" s="6" t="n">
+      <c r="J313" s="5" t="n">
         <v>5.67</v>
       </c>
       <c r="K313" s="4" t="n">
@@ -27367,7 +26179,7 @@
       <c r="I314" s="4" t="n">
         <v>148.09</v>
       </c>
-      <c r="J314" s="6" t="n">
+      <c r="J314" s="5" t="n">
         <v>9.07</v>
       </c>
       <c r="K314" s="4" t="n">
@@ -27515,7 +26327,7 @@
       <c r="I316" s="4" t="n">
         <v>29.64</v>
       </c>
-      <c r="J316" s="6" t="n">
+      <c r="J316" s="5" t="n">
         <v>2.62</v>
       </c>
       <c r="K316" s="4" t="n">
@@ -27589,7 +26401,7 @@
       <c r="I317" s="4" t="n">
         <v>73.31</v>
       </c>
-      <c r="J317" s="6" t="n">
+      <c r="J317" s="5" t="n">
         <v>0.77</v>
       </c>
       <c r="K317" s="4" t="n">
@@ -27737,7 +26549,7 @@
       <c r="I319" s="4" t="n">
         <v>95.54000000000001</v>
       </c>
-      <c r="J319" s="6" t="n">
+      <c r="J319" s="5" t="n">
         <v>5.29</v>
       </c>
       <c r="K319" s="4" t="n">
@@ -28107,7 +26919,7 @@
       <c r="I324" s="4" t="n">
         <v>117.58</v>
       </c>
-      <c r="J324" s="6" t="n">
+      <c r="J324" s="5" t="n">
         <v>0.72</v>
       </c>
       <c r="K324" s="4" t="n">
@@ -28181,7 +26993,7 @@
       <c r="I325" s="4" t="n">
         <v>69.29000000000001</v>
       </c>
-      <c r="J325" s="6" t="n">
+      <c r="J325" s="5" t="n">
         <v>12.01</v>
       </c>
       <c r="K325" s="4" t="n">
@@ -28255,7 +27067,7 @@
       <c r="I326" s="4" t="n">
         <v>69.29000000000001</v>
       </c>
-      <c r="J326" s="6" t="n">
+      <c r="J326" s="5" t="n">
         <v>0.8100000000000001</v>
       </c>
       <c r="K326" s="4" t="n">
@@ -28699,7 +27511,7 @@
       <c r="I332" s="4" t="n">
         <v>1133.7</v>
       </c>
-      <c r="J332" s="6" t="n">
+      <c r="J332" s="5" t="n">
         <v>9.199999999999999</v>
       </c>
       <c r="K332" s="4" t="n">
@@ -28921,7 +27733,7 @@
       <c r="I335" s="4" t="n">
         <v>334.68</v>
       </c>
-      <c r="J335" s="6" t="n">
+      <c r="J335" s="5" t="n">
         <v>4.21</v>
       </c>
       <c r="K335" s="4" t="n">
@@ -28995,7 +27807,7 @@
       <c r="I336" s="4" t="n">
         <v>294.34</v>
       </c>
-      <c r="J336" s="6" t="n">
+      <c r="J336" s="5" t="n">
         <v>4.42</v>
       </c>
       <c r="K336" s="4" t="n">
@@ -29069,7 +27881,7 @@
       <c r="I337" s="4" t="n">
         <v>79</v>
       </c>
-      <c r="J337" s="6" t="n">
+      <c r="J337" s="5" t="n">
         <v>14.71</v>
       </c>
       <c r="K337" s="4" t="n">
@@ -29439,7 +28251,7 @@
       <c r="I342" s="4" t="n">
         <v>332.96</v>
       </c>
-      <c r="J342" s="6" t="n">
+      <c r="J342" s="5" t="n">
         <v>3.85</v>
       </c>
       <c r="K342" s="4" t="n">
@@ -29513,7 +28325,7 @@
       <c r="I343" s="4" t="n">
         <v>190.18</v>
       </c>
-      <c r="J343" s="6" t="n">
+      <c r="J343" s="5" t="n">
         <v>7.32</v>
       </c>
       <c r="K343" s="4" t="n">
@@ -29809,7 +28621,7 @@
       <c r="I347" s="4" t="n">
         <v>82.23</v>
       </c>
-      <c r="J347" s="6" t="n">
+      <c r="J347" s="5" t="n">
         <v>1.08</v>
       </c>
       <c r="K347" s="4" t="n">
@@ -29883,7 +28695,7 @@
       <c r="I348" s="4" t="n">
         <v>107.23</v>
       </c>
-      <c r="J348" s="6" t="n">
+      <c r="J348" s="5" t="n">
         <v>1.22</v>
       </c>
       <c r="K348" s="4" t="n">
@@ -30031,7 +28843,7 @@
       <c r="I350" s="4" t="n">
         <v>288.17</v>
       </c>
-      <c r="J350" s="6" t="n">
+      <c r="J350" s="5" t="n">
         <v>2.02</v>
       </c>
       <c r="K350" s="4" t="n">
@@ -30105,7 +28917,7 @@
       <c r="I351" s="4" t="n">
         <v>257.27</v>
       </c>
-      <c r="J351" s="6" t="n">
+      <c r="J351" s="5" t="n">
         <v>0.25</v>
       </c>
       <c r="K351" s="4" t="n">
@@ -30179,7 +28991,7 @@
       <c r="I352" s="4" t="n">
         <v>54.79</v>
       </c>
-      <c r="J352" s="6" t="n">
+      <c r="J352" s="5" t="n">
         <v>0.77</v>
       </c>
       <c r="K352" s="4" t="n">
@@ -30327,7 +29139,7 @@
       <c r="I354" s="4" t="n">
         <v>1079.61</v>
       </c>
-      <c r="J354" s="6" t="n">
+      <c r="J354" s="5" t="n">
         <v>5.07</v>
       </c>
       <c r="K354" s="4" t="n">
@@ -30401,7 +29213,7 @@
       <c r="I355" s="4" t="n">
         <v>144.84</v>
       </c>
-      <c r="J355" s="6" t="n">
+      <c r="J355" s="5" t="n">
         <v>1</v>
       </c>
       <c r="K355" s="4" t="n">
@@ -30623,7 +29435,7 @@
       <c r="I358" s="4" t="n">
         <v>400.8</v>
       </c>
-      <c r="J358" s="6" t="n">
+      <c r="J358" s="5" t="n">
         <v>3.12</v>
       </c>
       <c r="K358" s="4" t="n">
@@ -30697,7 +29509,7 @@
       <c r="I359" s="4" t="n">
         <v>104.7</v>
       </c>
-      <c r="J359" s="6" t="n">
+      <c r="J359" s="5" t="n">
         <v>19.69</v>
       </c>
       <c r="K359" s="4" t="n">
@@ -30771,7 +29583,7 @@
       <c r="I360" s="4" t="n">
         <v>377.73</v>
       </c>
-      <c r="J360" s="6" t="n">
+      <c r="J360" s="5" t="n">
         <v>3.85</v>
       </c>
       <c r="K360" s="4" t="n">
@@ -30845,7 +29657,7 @@
       <c r="I361" s="4" t="n">
         <v>190.01</v>
       </c>
-      <c r="J361" s="6" t="n">
+      <c r="J361" s="5" t="n">
         <v>4.73</v>
       </c>
       <c r="K361" s="4" t="n">
@@ -30919,7 +29731,7 @@
       <c r="I362" s="4" t="n">
         <v>108.05</v>
       </c>
-      <c r="J362" s="6" t="n">
+      <c r="J362" s="5" t="n">
         <v>1.34</v>
       </c>
       <c r="K362" s="4" t="n">
@@ -30993,7 +29805,7 @@
       <c r="I363" s="4" t="n">
         <v>290.6</v>
       </c>
-      <c r="J363" s="6" t="n">
+      <c r="J363" s="5" t="n">
         <v>2.1</v>
       </c>
       <c r="K363" s="4" t="n">
@@ -31215,7 +30027,7 @@
       <c r="I366" s="4" t="n">
         <v>46.83</v>
       </c>
-      <c r="J366" s="6" t="n">
+      <c r="J366" s="5" t="n">
         <v>3.15</v>
       </c>
       <c r="K366" s="4" t="n">
@@ -31289,7 +30101,7 @@
       <c r="I367" s="4" t="n">
         <v>180.05</v>
       </c>
-      <c r="J367" s="6" t="n">
+      <c r="J367" s="5" t="n">
         <v>0.96</v>
       </c>
       <c r="K367" s="4" t="n">
@@ -31437,7 +30249,7 @@
       <c r="I369" s="4" t="n">
         <v>137.71</v>
       </c>
-      <c r="J369" s="6" t="n">
+      <c r="J369" s="5" t="n">
         <v>0.05</v>
       </c>
       <c r="K369" s="4" t="n">
@@ -31807,7 +30619,7 @@
       <c r="I374" s="4" t="n">
         <v>21.47</v>
       </c>
-      <c r="J374" s="6" t="n">
+      <c r="J374" s="5" t="n">
         <v>5.74</v>
       </c>
       <c r="K374" s="4" t="n">
@@ -31881,7 +30693,7 @@
       <c r="I375" s="4" t="n">
         <v>132.18</v>
       </c>
-      <c r="J375" s="6" t="n">
+      <c r="J375" s="5" t="n">
         <v>3.22</v>
       </c>
       <c r="K375" s="4" t="n">
@@ -31955,7 +30767,7 @@
       <c r="I376" s="4" t="n">
         <v>193.43</v>
       </c>
-      <c r="J376" s="6" t="n">
+      <c r="J376" s="5" t="n">
         <v>1.37</v>
       </c>
       <c r="K376" s="4" t="n">
@@ -32029,7 +30841,7 @@
       <c r="I377" s="4" t="n">
         <v>215.36</v>
       </c>
-      <c r="J377" s="6" t="n">
+      <c r="J377" s="5" t="n">
         <v>3.82</v>
       </c>
       <c r="K377" s="4" t="n">
@@ -32177,7 +30989,7 @@
       <c r="I379" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="J379" s="6" t="n">
+      <c r="J379" s="5" t="n">
         <v>3.16</v>
       </c>
       <c r="K379" s="4" t="n">
@@ -32251,7 +31063,7 @@
       <c r="I380" s="4" t="n">
         <v>245</v>
       </c>
-      <c r="J380" s="6" t="n">
+      <c r="J380" s="5" t="n">
         <v>3.16</v>
       </c>
       <c r="K380" s="4" t="n">
@@ -32325,7 +31137,7 @@
       <c r="I381" s="4" t="n">
         <v>122.78</v>
       </c>
-      <c r="J381" s="6" t="n">
+      <c r="J381" s="5" t="n">
         <v>2.26</v>
       </c>
       <c r="K381" s="4" t="n">
@@ -32399,7 +31211,7 @@
       <c r="I382" s="4" t="n">
         <v>463.82</v>
       </c>
-      <c r="J382" s="6" t="n">
+      <c r="J382" s="5" t="n">
         <v>5.18</v>
       </c>
       <c r="K382" s="4" t="n">
@@ -32547,7 +31359,7 @@
       <c r="I384" s="4" t="n">
         <v>634.54</v>
       </c>
-      <c r="J384" s="6" t="n">
+      <c r="J384" s="5" t="n">
         <v>2.68</v>
       </c>
       <c r="K384" s="4" t="n">
@@ -32769,7 +31581,7 @@
       <c r="I387" s="4" t="n">
         <v>236.93</v>
       </c>
-      <c r="J387" s="6" t="n">
+      <c r="J387" s="5" t="n">
         <v>11.76</v>
       </c>
       <c r="K387" s="4" t="n">
@@ -32917,7 +31729,7 @@
       <c r="I389" s="4" t="n">
         <v>200.21</v>
       </c>
-      <c r="J389" s="6" t="n">
+      <c r="J389" s="5" t="n">
         <v>2.69</v>
       </c>
       <c r="K389" s="4" t="n">
@@ -32991,7 +31803,7 @@
       <c r="I390" s="4" t="n">
         <v>94.31999999999999</v>
       </c>
-      <c r="J390" s="6" t="n">
+      <c r="J390" s="5" t="n">
         <v>0.88</v>
       </c>
       <c r="K390" s="4" t="n">
@@ -33065,7 +31877,7 @@
       <c r="I391" s="4" t="n">
         <v>73.95</v>
       </c>
-      <c r="J391" s="6" t="n">
+      <c r="J391" s="5" t="n">
         <v>2.71</v>
       </c>
       <c r="K391" s="4" t="n">
@@ -33139,7 +31951,7 @@
       <c r="I392" s="4" t="n">
         <v>82.7</v>
       </c>
-      <c r="J392" s="6" t="n">
+      <c r="J392" s="5" t="n">
         <v>8.74</v>
       </c>
       <c r="K392" s="4" t="n">
@@ -33213,7 +32025,7 @@
       <c r="I393" s="4" t="n">
         <v>62.09</v>
       </c>
-      <c r="J393" s="6" t="n">
+      <c r="J393" s="5" t="n">
         <v>6.58</v>
       </c>
       <c r="K393" s="4" t="n">
@@ -33287,7 +32099,7 @@
       <c r="I394" s="4" t="n">
         <v>205.78</v>
       </c>
-      <c r="J394" s="6" t="n">
+      <c r="J394" s="5" t="n">
         <v>0.5</v>
       </c>
       <c r="K394" s="4" t="n">
@@ -33361,7 +32173,7 @@
       <c r="I395" s="4" t="n">
         <v>51.62</v>
       </c>
-      <c r="J395" s="6" t="n">
+      <c r="J395" s="5" t="n">
         <v>3.64</v>
       </c>
       <c r="K395" s="4" t="n">
@@ -33435,7 +32247,7 @@
       <c r="I396" s="4" t="n">
         <v>25.61</v>
       </c>
-      <c r="J396" s="6" t="n">
+      <c r="J396" s="5" t="n">
         <v>1.91</v>
       </c>
       <c r="K396" s="4" t="n">
@@ -33509,7 +32321,7 @@
       <c r="I397" s="4" t="n">
         <v>32.14</v>
       </c>
-      <c r="J397" s="6" t="n">
+      <c r="J397" s="5" t="n">
         <v>3.28</v>
       </c>
       <c r="K397" s="4" t="n">
@@ -33731,7 +32543,7 @@
       <c r="I400" s="4" t="n">
         <v>295.1</v>
       </c>
-      <c r="J400" s="6" t="n">
+      <c r="J400" s="5" t="n">
         <v>4.65</v>
       </c>
       <c r="K400" s="4" t="n">
@@ -33879,7 +32691,7 @@
       <c r="I402" s="4" t="n">
         <v>32.67</v>
       </c>
-      <c r="J402" s="6" t="n">
+      <c r="J402" s="5" t="n">
         <v>11.12</v>
       </c>
       <c r="K402" s="4" t="n">
@@ -33953,7 +32765,7 @@
       <c r="I403" s="4" t="n">
         <v>406.93</v>
       </c>
-      <c r="J403" s="6" t="n">
+      <c r="J403" s="5" t="n">
         <v>0.19</v>
       </c>
       <c r="K403" s="4" t="n">
@@ -34027,7 +32839,7 @@
       <c r="I404" s="4" t="n">
         <v>406.93</v>
       </c>
-      <c r="J404" s="6" t="n">
+      <c r="J404" s="5" t="n">
         <v>0.19</v>
       </c>
       <c r="K404" s="4" t="n">
@@ -34101,7 +32913,7 @@
       <c r="I405" s="4" t="n">
         <v>956.12</v>
       </c>
-      <c r="J405" s="6" t="n">
+      <c r="J405" s="5" t="n">
         <v>1.25</v>
       </c>
       <c r="K405" s="4" t="n">
@@ -34249,7 +33061,7 @@
       <c r="I407" s="4" t="n">
         <v>130.61</v>
       </c>
-      <c r="J407" s="6" t="n">
+      <c r="J407" s="5" t="n">
         <v>4.42</v>
       </c>
       <c r="K407" s="4" t="n">
@@ -34397,7 +33209,7 @@
       <c r="I409" s="4" t="n">
         <v>181.78</v>
       </c>
-      <c r="J409" s="6" t="n">
+      <c r="J409" s="5" t="n">
         <v>22.34</v>
       </c>
       <c r="K409" s="4" t="n">
@@ -34693,7 +33505,7 @@
       <c r="I413" s="4" t="n">
         <v>65.47</v>
       </c>
-      <c r="J413" s="6" t="n">
+      <c r="J413" s="5" t="n">
         <v>0.91</v>
       </c>
       <c r="K413" s="4" t="n">
@@ -34915,7 +33727,7 @@
       <c r="I416" s="4" t="n">
         <v>37.34</v>
       </c>
-      <c r="J416" s="6" t="n">
+      <c r="J416" s="5" t="n">
         <v>16.69</v>
       </c>
       <c r="K416" s="4" t="n">
@@ -34989,7 +33801,7 @@
       <c r="I417" s="4" t="n">
         <v>279.67</v>
       </c>
-      <c r="J417" s="6" t="n">
+      <c r="J417" s="5" t="n">
         <v>8.35</v>
       </c>
       <c r="K417" s="4" t="n">
@@ -35063,7 +33875,7 @@
       <c r="I418" s="4" t="n">
         <v>27.2</v>
       </c>
-      <c r="J418" s="6" t="n">
+      <c r="J418" s="5" t="n">
         <v>6.04</v>
       </c>
       <c r="K418" s="4" t="n">
@@ -35285,7 +34097,7 @@
       <c r="I421" s="4" t="n">
         <v>404.03</v>
       </c>
-      <c r="J421" s="6" t="n">
+      <c r="J421" s="5" t="n">
         <v>4.26</v>
       </c>
       <c r="K421" s="4" t="n">
@@ -35359,7 +34171,7 @@
       <c r="I422" s="4" t="n">
         <v>279.32</v>
       </c>
-      <c r="J422" s="6" t="n">
+      <c r="J422" s="5" t="n">
         <v>2.56</v>
       </c>
       <c r="K422" s="4" t="n">
@@ -35507,7 +34319,7 @@
       <c r="I424" s="4" t="n">
         <v>151.08</v>
       </c>
-      <c r="J424" s="6" t="n">
+      <c r="J424" s="5" t="n">
         <v>4.57</v>
       </c>
       <c r="K424" s="4" t="n">
@@ -35581,7 +34393,7 @@
       <c r="I425" s="4" t="n">
         <v>102.86</v>
       </c>
-      <c r="J425" s="6" t="n">
+      <c r="J425" s="5" t="n">
         <v>0.38</v>
       </c>
       <c r="K425" s="4" t="n">
@@ -35729,7 +34541,7 @@
       <c r="I427" s="4" t="n">
         <v>125.7</v>
       </c>
-      <c r="J427" s="6" t="n">
+      <c r="J427" s="5" t="n">
         <v>4.01</v>
       </c>
       <c r="K427" s="4" t="n">
@@ -35803,7 +34615,7 @@
       <c r="I428" s="4" t="n">
         <v>279.52</v>
       </c>
-      <c r="J428" s="6" t="n">
+      <c r="J428" s="5" t="n">
         <v>0.57</v>
       </c>
       <c r="K428" s="4" t="n">
@@ -35877,7 +34689,7 @@
       <c r="I429" s="4" t="n">
         <v>141.46</v>
       </c>
-      <c r="J429" s="6" t="n">
+      <c r="J429" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K429" s="4" t="n">
@@ -35951,7 +34763,7 @@
       <c r="I430" s="4" t="n">
         <v>334.68</v>
       </c>
-      <c r="J430" s="6" t="n">
+      <c r="J430" s="5" t="n">
         <v>2.18</v>
       </c>
       <c r="K430" s="4" t="n">
@@ -36099,7 +34911,7 @@
       <c r="I432" s="4" t="n">
         <v>75.54000000000001</v>
       </c>
-      <c r="J432" s="6" t="n">
+      <c r="J432" s="5" t="n">
         <v>2.58</v>
       </c>
       <c r="K432" s="4" t="n">
@@ -36173,7 +34985,7 @@
       <c r="I433" s="4" t="n">
         <v>150.36</v>
       </c>
-      <c r="J433" s="6" t="n">
+      <c r="J433" s="5" t="n">
         <v>1.97</v>
       </c>
       <c r="K433" s="4" t="n">
@@ -36247,7 +35059,7 @@
       <c r="I434" s="4" t="n">
         <v>311.33</v>
       </c>
-      <c r="J434" s="6" t="n">
+      <c r="J434" s="5" t="n">
         <v>10.42</v>
       </c>
       <c r="K434" s="4" t="n">
@@ -36691,7 +35503,7 @@
       <c r="I440" s="4" t="n">
         <v>70.3</v>
       </c>
-      <c r="J440" s="6" t="n">
+      <c r="J440" s="5" t="n">
         <v>4.16</v>
       </c>
       <c r="K440" s="4" t="n">
@@ -36913,7 +35725,7 @@
       <c r="I443" s="4" t="n">
         <v>72.78</v>
       </c>
-      <c r="J443" s="6" t="n">
+      <c r="J443" s="5" t="n">
         <v>2.11</v>
       </c>
       <c r="K443" s="4" t="n">
@@ -36987,7 +35799,7 @@
       <c r="I444" s="4" t="n">
         <v>180.49</v>
       </c>
-      <c r="J444" s="6" t="n">
+      <c r="J444" s="5" t="n">
         <v>6.37</v>
       </c>
       <c r="K444" s="4" t="n">
@@ -37135,7 +35947,7 @@
       <c r="I446" s="4" t="n">
         <v>163.08</v>
       </c>
-      <c r="J446" s="6" t="n">
+      <c r="J446" s="5" t="n">
         <v>1.72</v>
       </c>
       <c r="K446" s="4" t="n">
@@ -37209,7 +36021,7 @@
       <c r="I447" s="4" t="n">
         <v>1167.22</v>
       </c>
-      <c r="J447" s="6" t="n">
+      <c r="J447" s="5" t="n">
         <v>2.12</v>
       </c>
       <c r="K447" s="4" t="n">
@@ -37431,7 +36243,7 @@
       <c r="I450" s="4" t="n">
         <v>221.07</v>
       </c>
-      <c r="J450" s="6" t="n">
+      <c r="J450" s="5" t="n">
         <v>8.43</v>
       </c>
       <c r="K450" s="4" t="n">
@@ -37505,7 +36317,7 @@
       <c r="I451" s="4" t="n">
         <v>113.25</v>
       </c>
-      <c r="J451" s="6" t="n">
+      <c r="J451" s="5" t="n">
         <v>2.12</v>
       </c>
       <c r="K451" s="4" t="n">
@@ -37579,7 +36391,7 @@
       <c r="I452" s="4" t="n">
         <v>35.01</v>
       </c>
-      <c r="J452" s="6" t="n">
+      <c r="J452" s="5" t="n">
         <v>4.95</v>
       </c>
       <c r="K452" s="4" t="n">
@@ -37653,7 +36465,7 @@
       <c r="I453" s="4" t="n">
         <v>189.09</v>
       </c>
-      <c r="J453" s="6" t="n">
+      <c r="J453" s="5" t="n">
         <v>4.85</v>
       </c>
       <c r="K453" s="4" t="n">
@@ -37727,7 +36539,7 @@
       <c r="I454" s="4" t="n">
         <v>189.09</v>
       </c>
-      <c r="J454" s="6" t="n">
+      <c r="J454" s="5" t="n">
         <v>4.85</v>
       </c>
       <c r="K454" s="4" t="n">
@@ -37801,7 +36613,7 @@
       <c r="I455" s="4" t="n">
         <v>87.44</v>
       </c>
-      <c r="J455" s="6" t="n">
+      <c r="J455" s="5" t="n">
         <v>5</v>
       </c>
       <c r="K455" s="4" t="n">
@@ -37949,7 +36761,7 @@
       <c r="I457" s="4" t="n">
         <v>63.85</v>
       </c>
-      <c r="J457" s="6" t="n">
+      <c r="J457" s="5" t="n">
         <v>1.83</v>
       </c>
       <c r="K457" s="4" t="n">
@@ -38319,7 +37131,7 @@
       <c r="I462" s="4" t="n">
         <v>137.49</v>
       </c>
-      <c r="J462" s="6" t="n">
+      <c r="J462" s="5" t="n">
         <v>1.05</v>
       </c>
       <c r="K462" s="4" t="n">
@@ -38393,7 +37205,7 @@
       <c r="I463" s="4" t="n">
         <v>181.28</v>
       </c>
-      <c r="J463" s="6" t="n">
+      <c r="J463" s="5" t="n">
         <v>1.45</v>
       </c>
       <c r="K463" s="4" t="n">
@@ -38541,7 +37353,7 @@
       <c r="I465" s="4" t="n">
         <v>68.14</v>
       </c>
-      <c r="J465" s="6" t="n">
+      <c r="J465" s="5" t="n">
         <v>4.71</v>
       </c>
       <c r="K465" s="4" t="n">
@@ -38615,7 +37427,7 @@
       <c r="I466" s="4" t="n">
         <v>169.46</v>
       </c>
-      <c r="J466" s="6" t="n">
+      <c r="J466" s="5" t="n">
         <v>0.75</v>
       </c>
       <c r="K466" s="4" t="n">
@@ -38763,7 +37575,7 @@
       <c r="I468" s="4" t="n">
         <v>52.97</v>
       </c>
-      <c r="J468" s="6" t="n">
+      <c r="J468" s="5" t="n">
         <v>10.08</v>
       </c>
       <c r="K468" s="4" t="n">
@@ -39207,7 +38019,7 @@
       <c r="I474" s="4" t="n">
         <v>41.19</v>
       </c>
-      <c r="J474" s="6" t="n">
+      <c r="J474" s="5" t="n">
         <v>0.41</v>
       </c>
       <c r="K474" s="4" t="n">
@@ -39281,7 +38093,7 @@
       <c r="I475" s="4" t="n">
         <v>41.19</v>
       </c>
-      <c r="J475" s="6" t="n">
+      <c r="J475" s="5" t="n">
         <v>0.41</v>
       </c>
       <c r="K475" s="4" t="n">
@@ -39503,7 +38315,7 @@
       <c r="I478" s="4" t="n">
         <v>202.25</v>
       </c>
-      <c r="J478" s="6" t="n">
+      <c r="J478" s="5" t="n">
         <v>2.22</v>
       </c>
       <c r="K478" s="4" t="n">
@@ -39651,7 +38463,7 @@
       <c r="I480" s="4" t="n">
         <v>175.73</v>
       </c>
-      <c r="J480" s="6" t="n">
+      <c r="J480" s="5" t="n">
         <v>3.64</v>
       </c>
       <c r="K480" s="4" t="n">
@@ -39799,7 +38611,7 @@
       <c r="I482" s="4" t="n">
         <v>440.34</v>
       </c>
-      <c r="J482" s="6" t="n">
+      <c r="J482" s="5" t="n">
         <v>6.91</v>
       </c>
       <c r="K482" s="4" t="n">
@@ -39873,7 +38685,7 @@
       <c r="I483" s="4" t="n">
         <v>440.34</v>
       </c>
-      <c r="J483" s="6" t="n">
+      <c r="J483" s="5" t="n">
         <v>6.91</v>
       </c>
       <c r="K483" s="4" t="n">
@@ -40021,7 +38833,7 @@
       <c r="I485" s="4" t="n">
         <v>480.93</v>
       </c>
-      <c r="J485" s="6" t="n">
+      <c r="J485" s="5" t="n">
         <v>1.39</v>
       </c>
       <c r="K485" s="4" t="n">
@@ -40465,7 +39277,7 @@
       <c r="I491" s="4" t="n">
         <v>134.06</v>
       </c>
-      <c r="J491" s="6" t="n">
+      <c r="J491" s="5" t="n">
         <v>3.98</v>
       </c>
       <c r="K491" s="4" t="n">
@@ -40539,7 +39351,7 @@
       <c r="I492" s="4" t="n">
         <v>287.62</v>
       </c>
-      <c r="J492" s="6" t="n">
+      <c r="J492" s="5" t="n">
         <v>2.52</v>
       </c>
       <c r="K492" s="4" t="n">
@@ -40761,7 +39573,7 @@
       <c r="I495" s="4" t="n">
         <v>14.73</v>
       </c>
-      <c r="J495" s="6" t="n">
+      <c r="J495" s="5" t="n">
         <v>0.2</v>
       </c>
       <c r="K495" s="4" t="n">
@@ -41205,7 +40017,7 @@
       <c r="I501" s="4" t="n">
         <v>279.6</v>
       </c>
-      <c r="J501" s="6" t="n">
+      <c r="J501" s="5" t="n">
         <v>3.8</v>
       </c>
       <c r="K501" s="4" t="n">
@@ -41279,7 +40091,7 @@
       <c r="I502" s="4" t="n">
         <v>80.09</v>
       </c>
-      <c r="J502" s="6" t="n">
+      <c r="J502" s="5" t="n">
         <v>0.17</v>
       </c>
       <c r="K502" s="4" t="n">
@@ -41427,7 +40239,7 @@
       <c r="I504" s="4" t="n">
         <v>181.38</v>
       </c>
-      <c r="J504" s="6" t="n">
+      <c r="J504" s="5" t="n">
         <v>0.87</v>
       </c>
       <c r="K504" s="4" t="n">
@@ -41501,7 +40313,7 @@
       <c r="I505" s="4" t="n">
         <v>100.72</v>
       </c>
-      <c r="J505" s="6" t="n">
+      <c r="J505" s="5" t="n">
         <v>2.5</v>
       </c>
       <c r="K505" s="4" t="n">
@@ -41575,7 +40387,7 @@
       <c r="I506" s="4" t="n">
         <v>114.1</v>
       </c>
-      <c r="J506" s="6" t="n">
+      <c r="J506" s="5" t="n">
         <v>3.99</v>
       </c>
       <c r="K506" s="4" t="n">
@@ -41649,7 +40461,7 @@
       <c r="I507" s="4" t="n">
         <v>188.07</v>
       </c>
-      <c r="J507" s="6" t="n">
+      <c r="J507" s="5" t="n">
         <v>1.67</v>
       </c>
       <c r="K507" s="4" t="n">
@@ -41723,7 +40535,7 @@
       <c r="I508" s="4" t="n">
         <v>262.9</v>
       </c>
-      <c r="J508" s="6" t="n">
+      <c r="J508" s="5" t="n">
         <v>5.12</v>
       </c>
       <c r="K508" s="4" t="n">
@@ -41797,7 +40609,7 @@
       <c r="I509" s="4" t="n">
         <v>313.45</v>
       </c>
-      <c r="J509" s="6" t="n">
+      <c r="J509" s="5" t="n">
         <v>1.68</v>
       </c>
       <c r="K509" s="4" t="n">
@@ -41871,7 +40683,7 @@
       <c r="I510" s="4" t="n">
         <v>155.08</v>
       </c>
-      <c r="J510" s="6" t="n">
+      <c r="J510" s="5" t="n">
         <v>3.74</v>
       </c>
       <c r="K510" s="4" t="n">
@@ -42241,7 +41053,7 @@
       <c r="I515" s="4" t="n">
         <v>344.5</v>
       </c>
-      <c r="J515" s="6" t="n">
+      <c r="J515" s="5" t="n">
         <v>0.27</v>
       </c>
       <c r="K515" s="4" t="n">
@@ -42315,7 +41127,7 @@
       <c r="I516" s="4" t="n">
         <v>60.09</v>
       </c>
-      <c r="J516" s="6" t="n">
+      <c r="J516" s="5" t="n">
         <v>9.130000000000001</v>
       </c>
       <c r="K516" s="4" t="n">
@@ -42389,7 +41201,7 @@
       <c r="I517" s="4" t="n">
         <v>47.25</v>
       </c>
-      <c r="J517" s="6" t="n">
+      <c r="J517" s="5" t="n">
         <v>0.88</v>
       </c>
       <c r="K517" s="4" t="n">
@@ -42685,7 +41497,7 @@
       <c r="I521" s="4" t="n">
         <v>39.84</v>
       </c>
-      <c r="J521" s="6" t="n">
+      <c r="J521" s="5" t="n">
         <v>26.08</v>
       </c>
       <c r="K521" s="4" t="n">
@@ -42759,7 +41571,7 @@
       <c r="I522" s="4" t="n">
         <v>126.68</v>
       </c>
-      <c r="J522" s="6" t="n">
+      <c r="J522" s="5" t="n">
         <v>1.03</v>
       </c>
       <c r="K522" s="4" t="n">
@@ -42981,7 +41793,7 @@
       <c r="I525" s="4" t="n">
         <v>71.41</v>
       </c>
-      <c r="J525" s="6" t="n">
+      <c r="J525" s="5" t="n">
         <v>2.17</v>
       </c>
       <c r="K525" s="4" t="n">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -539,7 +539,7 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=96 · 30 scored · 106 already in CURRENT · biggest blocker: model disagreement (19) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 118 already in CURRENT · biggest blocker: model disagreement (19) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 4 position(s) left CURRENT on a STOP BREACH (R1 3 · R2 1) and are recorded in EXIT HISTORY with their loss intact · 1 newly breached today</t>
+          <t>🔴 4 position(s) left CURRENT on a STOP BREACH (R1 3 · R2 1) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-16 · prices = 2026-09-15 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-17 · prices = 2026-09-15 close</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · feature_store STALE (57 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (2 day(s) old) · ensemble STALE (2 day(s) old) · feature_store STALE (58 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -867,7 +867,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1168,7 +1168,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1269,7 +1269,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1370,7 +1370,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1471,7 +1471,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1570,7 +1570,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1671,7 +1671,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1772,7 +1772,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1873,7 +1873,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1974,7 +1974,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2075,7 +2075,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2176,7 +2176,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2277,7 +2277,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2378,7 +2378,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2479,7 +2479,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2580,7 +2580,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2782,7 +2782,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2881,7 +2881,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2982,7 +2982,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3083,7 +3083,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3184,7 +3184,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3285,7 +3285,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3386,7 +3386,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3487,7 +3487,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3588,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3689,7 +3689,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3790,7 +3790,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3891,7 +3891,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3992,7 +3992,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4093,7 +4093,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4194,7 +4194,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4598,7 +4598,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4699,7 +4699,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4800,7 +4800,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5606,7 +5606,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5808,7 +5808,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5907,7 +5907,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6008,7 +6008,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6109,7 +6109,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6210,7 +6210,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6311,7 +6311,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6412,7 +6412,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6513,7 +6513,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6614,7 +6614,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6715,7 +6715,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6917,7 +6917,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7018,7 +7018,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7119,7 +7119,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7220,7 +7220,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7321,7 +7321,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7420,7 +7420,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7521,7 +7521,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7622,7 +7622,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7723,7 +7723,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7824,7 +7824,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7923,7 +7923,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8024,7 +8024,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8125,7 +8125,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8226,7 +8226,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8325,7 +8325,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8527,7 +8527,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8628,7 +8628,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8729,7 +8729,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8830,7 +8830,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8931,7 +8931,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9032,7 +9032,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9133,7 +9133,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9234,7 +9234,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9335,7 +9335,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9436,7 +9436,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9537,7 +9537,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9638,7 +9638,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9739,7 +9739,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9840,7 +9840,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9941,7 +9941,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10042,7 +10042,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10143,7 +10143,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10244,7 +10244,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10345,7 +10345,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10446,7 +10446,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10547,7 +10547,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10648,7 +10648,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10749,7 +10749,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10850,7 +10850,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10951,7 +10951,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11052,7 +11052,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11153,7 +11153,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11254,7 +11254,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11355,7 +11355,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11456,7 +11456,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11557,7 +11557,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11658,7 +11658,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11759,7 +11759,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11862,7 +11862,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12068,7 +12068,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12888,7 +12888,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13998,7 +13998,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-09-16</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-09-17</t>
         </is>
       </c>
     </row>
@@ -14101,7 +14101,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-16</t>
+          <t>2026-09-17</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -14144,7 +14144,7 @@
         <v>-7.54</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-21 · prices = 2026-09-18 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-22 · prices = 2026-09-18 close</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 30 scored · 131 already in CURRENT · biggest blocker: model disagreement (18) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 141 already in CURRENT · biggest blocker: model disagreement (17) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (3 day(s) old) · ensemble STALE (3 day(s) old) · feature_store STALE (62 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (4 day(s) old) · ensemble STALE (4 day(s) old) · feature_store STALE (63 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14387,7 +14387,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16319,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-09-21</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-09-22</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-21</t>
+          <t>2026-09-22</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -16465,7 +16465,7 @@
         <v>-9.82</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-22 · prices = 2026-09-18 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-23 · prices = 2026-09-18 close</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (4 day(s) old) · ensemble STALE (4 day(s) old) · feature_store STALE (63 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (5 day(s) old) · ensemble STALE (5 day(s) old) · feature_store STALE (64 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -865,7 +865,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -966,7 +966,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1067,7 +1067,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1170,7 +1170,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1271,7 +1271,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1372,7 +1372,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1473,7 +1473,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1574,7 +1574,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1675,7 +1675,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1776,7 +1776,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1877,7 +1877,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1978,7 +1978,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2079,7 +2079,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2180,7 +2180,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2281,7 +2281,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2382,7 +2382,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2483,7 +2483,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2584,7 +2584,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2784,7 +2784,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2885,7 +2885,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2986,7 +2986,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3087,7 +3087,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3289,7 +3289,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3390,7 +3390,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3491,7 +3491,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3592,7 +3592,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3693,7 +3693,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3794,7 +3794,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3994,7 +3994,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4095,7 +4095,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4196,7 +4196,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4295,7 +4295,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4396,7 +4396,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4497,7 +4497,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4903,7 +4903,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5002,7 +5002,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 44d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5707,7 +5707,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 44d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6113,7 +6113,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6214,7 +6214,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6416,7 +6416,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6517,7 +6517,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6618,7 +6618,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7826,7 +7826,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7927,7 +7927,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8028,7 +8028,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8129,7 +8129,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8230,7 +8230,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8331,7 +8331,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8430,7 +8430,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8531,7 +8531,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8632,7 +8632,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8733,7 +8733,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8834,7 +8834,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8935,7 +8935,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9036,7 +9036,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9137,7 +9137,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9238,7 +9238,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9339,7 +9339,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9440,7 +9440,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9541,7 +9541,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9743,7 +9743,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9844,7 +9844,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10046,7 +10046,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10147,7 +10147,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10248,7 +10248,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10349,7 +10349,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10450,7 +10450,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10551,7 +10551,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10652,7 +10652,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10753,7 +10753,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10854,7 +10854,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10955,7 +10955,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11056,7 +11056,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11157,7 +11157,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11258,7 +11258,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11359,7 +11359,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11460,7 +11460,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11561,7 +11561,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11662,7 +11662,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11763,7 +11763,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11864,7 +11864,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11965,7 +11965,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12066,7 +12066,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12165,7 +12165,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12266,7 +12266,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12369,7 +12369,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12470,7 +12470,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12571,7 +12571,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12672,7 +12672,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12773,7 +12773,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12874,7 +12874,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12975,7 +12975,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13076,7 +13076,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13177,7 +13177,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13278,7 +13278,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13379,7 +13379,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13480,7 +13480,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13581,7 +13581,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13682,7 +13682,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13783,7 +13783,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13884,7 +13884,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13985,7 +13985,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14084,7 +14084,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14185,7 +14185,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14286,7 +14286,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14387,7 +14387,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15104,7 +15104,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 44d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16319,7 +16319,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-09-22</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-09-23</t>
         </is>
       </c>
     </row>
@@ -16422,7 +16422,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-22</t>
+          <t>2026-09-23</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -16465,7 +16465,7 @@
         <v>-9.82</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-24 · prices = 2026-09-23 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-25 · prices = 2026-09-23 close</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 30 scored · 135 already in CURRENT · biggest blocker: model disagreement (17) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 158 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · feature_store STALE (65 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (2 day(s) old) · ensemble STALE (2 day(s) old) · feature_store STALE (66 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1275,7 +1275,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1376,7 +1376,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 45d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 46d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1578,7 +1578,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1679,7 +1679,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1782,7 +1782,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1883,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1984,7 +1984,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2085,7 +2085,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2186,7 +2186,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3901,7 +3901,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4002,7 +4002,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4103,7 +4103,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4204,7 +4204,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4505,7 +4505,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4606,7 +4606,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4707,7 +4707,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5109,7 +5109,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5210,7 +5210,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5311,7 +5311,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5410,7 +5410,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5511,7 +5511,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5812,7 +5812,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5913,7 +5913,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6014,7 +6014,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6115,7 +6115,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6216,7 +6216,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6317,7 +6317,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6418,7 +6418,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6519,7 +6519,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6721,7 +6721,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6822,7 +6822,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6921,7 +6921,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7022,7 +7022,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7123,7 +7123,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7224,7 +7224,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7325,7 +7325,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7426,7 +7426,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7527,7 +7527,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7628,7 +7628,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7729,7 +7729,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9038,7 +9038,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9139,7 +9139,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9240,7 +9240,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9442,7 +9442,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9543,7 +9543,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9646,7 +9646,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9747,7 +9747,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9848,7 +9848,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9949,7 +9949,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10050,7 +10050,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10252,7 +10252,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10353,7 +10353,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10454,7 +10454,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10555,7 +10555,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10656,7 +10656,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 45d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 46d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10757,7 +10757,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10858,7 +10858,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10959,7 +10959,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11161,7 +11161,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11262,7 +11262,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11363,7 +11363,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11464,7 +11464,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11565,7 +11565,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11666,7 +11666,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11767,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11868,7 +11868,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11969,7 +11969,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12070,7 +12070,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12171,7 +12171,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12272,7 +12272,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12373,7 +12373,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12474,7 +12474,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12575,7 +12575,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12674,7 +12674,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12878,7 +12878,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12979,7 +12979,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13080,7 +13080,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13181,7 +13181,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13282,7 +13282,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13383,7 +13383,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13484,7 +13484,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13585,7 +13585,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13686,7 +13686,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13787,7 +13787,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15906,7 +15906,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16825,7 +16825,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 44d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 45d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16928,7 +16928,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 44d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 45d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17937,7 +17937,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-09-24</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-09-25</t>
         </is>
       </c>
     </row>
@@ -18040,7 +18040,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -18083,7 +18083,7 @@
         <v>-10.74</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -18114,7 +18114,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-24</t>
+          <t>2026-09-25</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -18157,7 +18157,7 @@
         <v>-11.83</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-29 · prices = 2026-09-28 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-09-30 · prices = 2026-09-28 close</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 30 scored · 169 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 174 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · feature_store STALE (70 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (2 day(s) old) · ensemble STALE (2 day(s) old) · feature_store STALE (71 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -970,7 +970,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1071,7 +1071,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1172,7 +1172,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1273,7 +1273,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1374,7 +1374,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1475,7 +1475,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1576,7 +1576,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1677,7 +1677,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1780,7 +1780,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 50d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 51d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1881,7 +1881,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1982,7 +1982,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2083,7 +2083,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2184,7 +2184,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2285,7 +2285,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2386,7 +2386,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2487,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2689,7 +2689,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2790,7 +2790,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2891,7 +2891,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2992,7 +2992,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3093,7 +3093,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3293,7 +3293,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3396,7 +3396,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3598,7 +3598,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3699,7 +3699,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3800,7 +3800,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3899,7 +3899,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3998,7 +3998,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4097,7 +4097,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4198,7 +4198,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4299,7 +4299,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4400,7 +4400,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4499,7 +4499,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4701,7 +4701,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4802,7 +4802,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5000,7 +5000,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5103,7 +5103,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5204,7 +5204,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5305,7 +5305,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5406,7 +5406,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5507,7 +5507,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5608,7 +5608,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5810,7 +5810,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5911,7 +5911,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6012,7 +6012,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6111,7 +6111,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6212,7 +6212,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6313,7 +6313,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6414,7 +6414,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6515,7 +6515,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6616,7 +6616,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6818,7 +6818,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6919,7 +6919,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7020,7 +7020,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7121,7 +7121,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7222,7 +7222,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7323,7 +7323,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7424,7 +7424,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7525,7 +7525,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7626,7 +7626,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7727,7 +7727,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7828,7 +7828,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7929,7 +7929,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8030,7 +8030,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8131,7 +8131,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8232,7 +8232,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8333,7 +8333,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8434,7 +8434,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8535,7 +8535,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8737,7 +8737,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8838,7 +8838,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8939,7 +8939,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9040,7 +9040,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9141,7 +9141,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9242,7 +9242,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9343,7 +9343,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9547,7 +9547,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9648,7 +9648,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9749,7 +9749,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9850,7 +9850,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9951,7 +9951,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10052,7 +10052,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10153,7 +10153,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10254,7 +10254,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10355,7 +10355,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10456,7 +10456,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10557,7 +10557,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10658,7 +10658,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10759,7 +10759,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10860,7 +10860,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10961,7 +10961,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11062,7 +11062,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11163,7 +11163,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11264,7 +11264,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11365,7 +11365,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11466,7 +11466,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11567,7 +11567,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11668,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11769,7 +11769,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 50d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 51d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11870,7 +11870,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11971,7 +11971,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12072,7 +12072,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12173,7 +12173,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12274,7 +12274,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12375,7 +12375,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12476,7 +12476,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12577,7 +12577,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12678,7 +12678,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12779,7 +12779,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12880,7 +12880,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12981,7 +12981,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13082,7 +13082,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13183,7 +13183,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13284,7 +13284,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13385,7 +13385,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13486,7 +13486,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13587,7 +13587,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13688,7 +13688,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13789,7 +13789,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13888,7 +13888,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13989,7 +13989,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14090,7 +14090,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14191,7 +14191,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14290,7 +14290,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14391,7 +14391,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14492,7 +14492,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14593,7 +14593,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14694,7 +14694,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14795,7 +14795,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14896,7 +14896,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14997,7 +14997,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15098,7 +15098,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15199,7 +15199,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15300,7 +15300,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15401,7 +15401,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15502,7 +15502,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15603,7 +15603,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15704,7 +15704,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15805,7 +15805,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15906,7 +15906,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16007,7 +16007,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16108,7 +16108,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16209,7 +16209,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16411,7 +16411,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16512,7 +16512,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16613,7 +16613,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16714,7 +16714,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16815,7 +16815,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16916,7 +16916,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17015,7 +17015,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17116,7 +17116,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17217,7 +17217,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17318,7 +17318,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17419,7 +17419,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17520,7 +17520,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17621,7 +17621,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17722,7 +17722,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17823,7 +17823,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 49d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 50d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18544,7 +18544,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 49d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 50d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19448,7 +19448,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-09-29</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-09-30</t>
         </is>
       </c>
     </row>
@@ -19551,7 +19551,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -19594,7 +19594,7 @@
         <v>-12.65</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -19625,7 +19625,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -19668,7 +19668,7 @@
         <v>-5.9</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -19699,7 +19699,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-09-29</t>
+          <t>2026-09-30</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -19742,7 +19742,7 @@
         <v>-15.37</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-01 · prices = 2026-09-30 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-02 · prices = 2026-09-30 close</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 30 scored · 174 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 183 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · feature_store STALE (72 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (2 day(s) old) · ensemble STALE (2 day(s) old) · feature_store STALE (73 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1174,7 +1174,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1277,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1378,7 +1378,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1580,7 +1580,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1681,7 +1681,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1784,7 +1784,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 52d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 53d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1885,7 +1885,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1986,7 +1986,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2087,7 +2087,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2188,7 +2188,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2289,7 +2289,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2493,7 +2493,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2594,7 +2594,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2794,7 +2794,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2895,7 +2895,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2996,7 +2996,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3194,7 +3194,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3295,7 +3295,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3398,7 +3398,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3499,7 +3499,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3600,7 +3600,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3802,7 +3802,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3903,7 +3903,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4004,7 +4004,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4105,7 +4105,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4206,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4305,7 +4305,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4406,7 +4406,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4507,7 +4507,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4608,7 +4608,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4709,7 +4709,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4808,7 +4808,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4909,7 +4909,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5010,7 +5010,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5111,7 +5111,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5212,7 +5212,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5313,7 +5313,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5515,7 +5515,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5616,7 +5616,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5717,7 +5717,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5818,7 +5818,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5919,7 +5919,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6020,7 +6020,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6121,7 +6121,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6222,7 +6222,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6325,7 +6325,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6426,7 +6426,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6527,7 +6527,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6628,7 +6628,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6729,7 +6729,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6828,7 +6828,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6929,7 +6929,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7030,7 +7030,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7131,7 +7131,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7232,7 +7232,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7333,7 +7333,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7434,7 +7434,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7535,7 +7535,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7636,7 +7636,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7737,7 +7737,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7939,7 +7939,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8040,7 +8040,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8141,7 +8141,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8242,7 +8242,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8343,7 +8343,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8444,7 +8444,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8545,7 +8545,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8646,7 +8646,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8747,7 +8747,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8848,7 +8848,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8949,7 +8949,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9050,7 +9050,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9151,7 +9151,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9250,7 +9250,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9351,7 +9351,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9452,7 +9452,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9553,7 +9553,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9654,7 +9654,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9755,7 +9755,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9856,7 +9856,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9957,7 +9957,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10058,7 +10058,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10159,7 +10159,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10361,7 +10361,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10462,7 +10462,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10563,7 +10563,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10664,7 +10664,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10765,7 +10765,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10866,7 +10866,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10967,7 +10967,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11068,7 +11068,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11167,7 +11167,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11371,7 +11371,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11472,7 +11472,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11573,7 +11573,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11874,7 +11874,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11975,7 +11975,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12076,7 +12076,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12177,7 +12177,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12278,7 +12278,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12379,7 +12379,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12480,7 +12480,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12581,7 +12581,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12682,7 +12682,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12783,7 +12783,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12884,7 +12884,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12985,7 +12985,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13086,7 +13086,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13187,7 +13187,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13288,7 +13288,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13389,7 +13389,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13490,7 +13490,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13591,7 +13591,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 52d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 53d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13692,7 +13692,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13793,7 +13793,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13894,7 +13894,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13995,7 +13995,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14096,7 +14096,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14197,7 +14197,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14298,7 +14298,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14399,7 +14399,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14500,7 +14500,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14601,7 +14601,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14702,7 +14702,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14803,7 +14803,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14904,7 +14904,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15005,7 +15005,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15106,7 +15106,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15207,7 +15207,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15308,7 +15308,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15409,7 +15409,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15510,7 +15510,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15611,7 +15611,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16114,7 +16114,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16720,7 +16720,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16821,7 +16821,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16922,7 +16922,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17324,7 +17324,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17425,7 +17425,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17526,7 +17526,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17627,7 +17627,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17728,7 +17728,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17829,7 +17829,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17930,7 +17930,7 @@
       </c>
       <c r="W178" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18031,7 +18031,7 @@
       </c>
       <c r="W179" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18132,7 +18132,7 @@
       </c>
       <c r="W180" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18233,7 +18233,7 @@
       </c>
       <c r="W181" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18334,7 +18334,7 @@
       </c>
       <c r="W182" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18435,7 +18435,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18536,7 +18536,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18637,7 +18637,7 @@
       </c>
       <c r="W185" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 16d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18738,7 +18738,7 @@
       </c>
       <c r="W186" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19354,7 +19354,7 @@
       </c>
       <c r="W192" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 51d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 52d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19457,7 +19457,7 @@
       </c>
       <c r="W193" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 51d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 52d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20363,7 +20363,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-10-01</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-10-02</t>
         </is>
       </c>
     </row>
@@ -20466,7 +20466,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -20509,7 +20509,7 @@
         <v>-11.69</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -20540,7 +20540,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -20583,7 +20583,7 @@
         <v>-6</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -20614,7 +20614,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-01</t>
+          <t>2026-10-02</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -20657,7 +20657,7 @@
         <v>-12.14</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-05 · prices = 2026-10-02 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-06 · prices = 2026-10-02 close</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 30 scored · 178 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 186 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (3 day(s) old) · ensemble STALE (3 day(s) old) · feature_store STALE (76 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (4 day(s) old) · ensemble STALE (4 day(s) old) · feature_store STALE (77 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 56d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 56d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13900,7 +13900,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="W178" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="W179" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="W180" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="W181" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="W182" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="W185" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="W186" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="W187" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="W188" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="W189" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="W195" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 55d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 56d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="W196" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 55d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 56d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-10-05</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-10-06</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -20818,7 +20818,7 @@
         <v>-12.78</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -20892,7 +20892,7 @@
         <v>-7.19</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-05</t>
+          <t>2026-10-06</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -20966,7 +20966,7 @@
         <v>-12.79</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-06 · prices = 2026-10-02 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-07 · prices = 2026-10-02 close</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (4 day(s) old) · ensemble STALE (4 day(s) old) · feature_store STALE (77 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (5 day(s) old) · ensemble STALE (5 day(s) old) · feature_store STALE (78 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 58d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 11d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 58d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13900,7 +13900,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="W178" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="W179" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="W180" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="W181" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="W182" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="W185" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="W186" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="W187" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="W188" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="W189" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="W195" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 56d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="W196" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 56d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-10-06</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-10-07</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -20818,7 +20818,7 @@
         <v>-12.78</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -20892,7 +20892,7 @@
         <v>-7.19</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-06</t>
+          <t>2026-10-07</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -20966,7 +20966,7 @@
         <v>-12.79</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-07 · prices = 2026-10-02 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-08 · prices = 2026-10-02 close</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (5 day(s) old) · ensemble STALE (5 day(s) old) · feature_store STALE (78 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (6 day(s) old) · ensemble STALE (6 day(s) old) · feature_store STALE (79 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1893,7 +1893,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 58d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 59d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1994,7 +1994,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2501,7 +2501,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2705,7 +2705,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2806,7 +2806,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2905,7 +2905,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3006,7 +3006,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3107,7 +3107,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3206,7 +3206,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3406,7 +3406,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3507,7 +3507,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3608,7 +3608,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3709,7 +3709,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3810,7 +3810,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3911,7 +3911,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4111,7 +4111,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4212,7 +4212,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4313,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4414,7 +4414,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4515,7 +4515,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4616,7 +4616,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4717,7 +4717,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4919,7 +4919,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5020,7 +5020,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5121,7 +5121,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5222,7 +5222,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5323,7 +5323,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5424,7 +5424,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5727,7 +5727,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5929,7 +5929,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6030,7 +6030,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6131,7 +6131,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6232,7 +6232,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6333,7 +6333,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6434,7 +6434,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6535,7 +6535,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6636,7 +6636,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6737,7 +6737,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6838,7 +6838,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6937,7 +6937,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7038,7 +7038,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7139,7 +7139,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7240,7 +7240,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7341,7 +7341,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7442,7 +7442,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7543,7 +7543,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7644,7 +7644,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7745,7 +7745,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7846,7 +7846,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7947,7 +7947,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8149,7 +8149,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8250,7 +8250,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8351,7 +8351,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8452,7 +8452,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8553,7 +8553,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8654,7 +8654,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8755,7 +8755,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 6d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8856,7 +8856,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8957,7 +8957,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9058,7 +9058,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9159,7 +9159,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9260,7 +9260,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9361,7 +9361,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9462,7 +9462,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9563,7 +9563,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9662,7 +9662,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9763,7 +9763,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9864,7 +9864,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9965,7 +9965,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10066,7 +10066,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10167,7 +10167,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10268,7 +10268,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 9d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10470,7 +10470,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10571,7 +10571,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10672,7 +10672,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10773,7 +10773,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10874,7 +10874,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10973,7 +10973,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11074,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11175,7 +11175,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11276,7 +11276,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11377,7 +11377,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11476,7 +11476,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11577,7 +11577,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11678,7 +11678,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11779,7 +11779,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11880,7 +11880,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11981,7 +11981,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12082,7 +12082,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12183,7 +12183,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12284,7 +12284,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12385,7 +12385,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 12d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 13d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12486,7 +12486,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12587,7 +12587,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12688,7 +12688,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12789,7 +12789,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12890,7 +12890,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12991,7 +12991,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13092,7 +13092,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13193,7 +13193,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13294,7 +13294,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13395,7 +13395,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 58d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 59d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13496,7 +13496,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13597,7 +13597,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13698,7 +13698,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13799,7 +13799,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13900,7 +13900,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14001,7 +14001,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14102,7 +14102,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14203,7 +14203,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14304,7 +14304,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14405,7 +14405,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14506,7 +14506,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14607,7 +14607,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14708,7 +14708,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14809,7 +14809,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15011,7 +15011,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15112,7 +15112,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15213,7 +15213,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15314,7 +15314,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15415,7 +15415,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15516,7 +15516,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15615,7 +15615,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15716,7 +15716,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15817,7 +15817,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15918,7 +15918,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16019,7 +16019,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16118,7 +16118,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16219,7 +16219,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16320,7 +16320,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16421,7 +16421,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16522,7 +16522,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16621,7 +16621,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16722,7 +16722,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16823,7 +16823,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16926,7 +16926,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17027,7 +17027,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17128,7 +17128,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17229,7 +17229,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17330,7 +17330,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17431,7 +17431,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17532,7 +17532,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17633,7 +17633,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 14d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17734,7 +17734,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17835,7 +17835,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17936,7 +17936,7 @@
       </c>
       <c r="W178" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18037,7 +18037,7 @@
       </c>
       <c r="W179" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18138,7 +18138,7 @@
       </c>
       <c r="W180" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18239,7 +18239,7 @@
       </c>
       <c r="W181" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="W182" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18441,7 +18441,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18542,7 +18542,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18643,7 +18643,7 @@
       </c>
       <c r="W185" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18744,7 +18744,7 @@
       </c>
       <c r="W186" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18845,7 +18845,7 @@
       </c>
       <c r="W187" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18946,7 +18946,7 @@
       </c>
       <c r="W188" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19047,7 +19047,7 @@
       </c>
       <c r="W189" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19663,7 +19663,7 @@
       </c>
       <c r="W195" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 58d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19766,7 +19766,7 @@
       </c>
       <c r="W196" s="4" t="inlineStr">
         <is>
-          <t>HOLD · held 57d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>HOLD · held 58d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20672,7 +20672,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-10-07</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-10-08</t>
         </is>
       </c>
     </row>
@@ -20775,7 +20775,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -20818,7 +20818,7 @@
         <v>-12.78</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>
@@ -20849,7 +20849,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -20892,7 +20892,7 @@
         <v>-7.19</v>
       </c>
       <c r="K6" s="4" t="n">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
@@ -20923,7 +20923,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>2026-10-07</t>
+          <t>2026-10-08</t>
         </is>
       </c>
       <c r="B7" s="4" t="inlineStr">
@@ -20966,7 +20966,7 @@
         <v>-12.79</v>
       </c>
       <c r="K7" s="4" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="L7" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -532,7 +532,7 @@
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>🔴 6 position(s) left CURRENT on a STOP BREACH (R1 5 · R2 1) and are recorded in EXIT HISTORY with their loss intact · 0 newly breached today</t>
+          <t>⚠ lifecycle dataset is dated 2026-10-08, not this report's as-of · rerun the pipeline</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=2 · 516 scored · 19 already in CURRENT · biggest blocker: model disagreement (397) · lost to the 15-name ensemble truncation: 2 · lifecycle defects: 1</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 185 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (15 day(s) old) · ensemble STALE (15 day(s) old) · dynamic_risk STALE (1 day(s) old) · feature_store STALE (32 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (15 day(s) old) · ensemble STALE (15 day(s) old) · feature_store STALE (88 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -725,17 +725,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N8" s="6" t="n">
-        <v>55821306891.77267</v>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n">
@@ -826,17 +828,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N9" s="6" t="n">
-        <v>60145065197.75477</v>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n">
@@ -927,17 +931,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N10" s="6" t="n">
-        <v>36450207083.03044</v>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n">
@@ -1028,17 +1034,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>1148153621496.884</v>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n">
@@ -1129,17 +1137,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N12" s="6" t="n">
-        <v>32203271981.67537</v>
+      <c r="N12" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q12" s="4" t="n">
@@ -1230,17 +1240,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N13" s="6" t="n">
-        <v>55705746694.15555</v>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n">
@@ -1331,17 +1343,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N14" s="6" t="n">
-        <v>384946167342.452</v>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n">
@@ -1430,17 +1444,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N15" s="6" t="n">
-        <v>779650568675.8146</v>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n">
@@ -1531,17 +1547,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N16" s="6" t="n">
-        <v>254741674944.2797</v>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n">
@@ -1630,17 +1648,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N17" s="6" t="n">
-        <v>235993477555.1642</v>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n">
@@ -1731,17 +1751,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N18" s="6" t="n">
-        <v>62849235603.77505</v>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n">
@@ -1830,17 +1852,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N19" s="6" t="n">
-        <v>57451318481.69431</v>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n">
@@ -1929,17 +1953,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>33265955329.40047</v>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n">
@@ -2028,17 +2054,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>13570629696.23986</v>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n">
@@ -2128,11 +2156,11 @@
         </is>
       </c>
       <c r="N22" s="6" t="n">
-        <v>236374160811.6292</v>
+        <v>197696964011.1858</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
@@ -2228,17 +2256,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N23" s="6" t="n">
-        <v>25609435171.5677</v>
+      <c r="N23" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q23" s="4" t="n">
@@ -2327,17 +2357,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N24" s="6" t="n">
-        <v>145915020334.7654</v>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n">
@@ -2428,17 +2460,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N25" s="6" t="n">
-        <v>244399323814.9681</v>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n">
@@ -2529,17 +2563,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>106733315426.1837</v>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n">
@@ -2628,17 +2664,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>93885819187.30971</v>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n">
@@ -2728,11 +2766,11 @@
         </is>
       </c>
       <c r="N28" s="6" t="n">
-        <v>374110588272.0536</v>
+        <v>405415174406.5037</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
@@ -2826,17 +2864,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N29" s="6" t="n">
-        <v>204126787125.5292</v>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n">
@@ -2925,17 +2965,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N30" s="6" t="n">
-        <v>22110573124.50639</v>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n">
@@ -3025,11 +3067,11 @@
         </is>
       </c>
       <c r="N31" s="6" t="n">
-        <v>5562883949883.733</v>
+        <v>4912471004503.345</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
@@ -3123,17 +3165,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N32" s="6" t="n">
-        <v>56676105494.18487</v>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n">
@@ -3223,11 +3267,11 @@
         </is>
       </c>
       <c r="N33" s="6" t="n">
-        <v>66435468197.60057</v>
+        <v>71285303012.65192</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
@@ -3321,17 +3365,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N34" s="6" t="n">
-        <v>7149900531.60001</v>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n">
@@ -3420,17 +3466,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N35" s="6" t="n">
-        <v>80723503024.88382</v>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n">
@@ -3519,17 +3567,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N36" s="6" t="n">
-        <v>121338885046.4976</v>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n">
@@ -3618,17 +3668,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N37" s="6" t="n">
-        <v>114683252142.2478</v>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n">
@@ -3717,17 +3769,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>250899617946.5399</v>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n">
@@ -3816,17 +3870,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
-        <v>338688148563.4765</v>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n">
@@ -3916,11 +3972,11 @@
         </is>
       </c>
       <c r="N40" s="6" t="n">
-        <v>3710222886174.651</v>
+        <v>2925499309897.075</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
@@ -4014,17 +4070,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N41" s="6" t="n">
-        <v>200909281260.8732</v>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n">
@@ -4113,17 +4171,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>104447969119.3363</v>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n">
@@ -4212,17 +4272,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N43" s="6" t="n">
-        <v>131371149496.006</v>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n">
@@ -4311,17 +4373,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N44" s="6" t="n">
-        <v>44534850626.98576</v>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n">
@@ -4410,17 +4474,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N45" s="6" t="n">
-        <v>28313919957.99379</v>
+      <c r="N45" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q45" s="4" t="n">
@@ -4509,17 +4575,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>28287853879.70126</v>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n">
@@ -4608,17 +4676,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N47" s="6" t="n">
-        <v>113527219166.1637</v>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n">
@@ -4707,17 +4777,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N48" s="6" t="n">
-        <v>109799408364.9603</v>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n">
@@ -4806,17 +4878,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N49" s="6" t="n">
-        <v>103395110098.2371</v>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n">
@@ -4905,17 +4979,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N50" s="6" t="n">
-        <v>26133645761.89021</v>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n">
@@ -5004,17 +5080,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N51" s="6" t="n">
-        <v>47304232439.99541</v>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n">
@@ -5103,17 +5181,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>76453962641.50443</v>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n">
@@ -5202,17 +5282,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
-        <v>17278259805.07866</v>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n">
@@ -5301,17 +5383,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N54" s="6" t="n">
-        <v>11686918084.21924</v>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n">
@@ -5400,17 +5484,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N55" s="6" t="n">
-        <v>53431824008.73483</v>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n">
@@ -5499,17 +5585,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>18801824734.90267</v>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n">
@@ -5598,17 +5686,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N57" s="6" t="n">
-        <v>42227950130.60567</v>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n">
@@ -5697,17 +5787,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>101367795088.8651</v>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n">
@@ -5796,17 +5888,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N59" s="6" t="n">
-        <v>349784048425.1405</v>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n">
@@ -5895,17 +5989,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N60" s="6" t="n">
-        <v>17766423082.03612</v>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n">
@@ -5994,17 +6090,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N61" s="6" t="n">
-        <v>182347578316.0937</v>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n">
@@ -6093,17 +6191,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N62" s="6" t="n">
-        <v>23415314751.69306</v>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n">
@@ -6192,17 +6292,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>134710050827.5805</v>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n">
@@ -6291,17 +6393,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N64" s="6" t="n">
-        <v>73688548164.94472</v>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n">
@@ -6390,17 +6494,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
-        <v>14092887984.21872</v>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n">
@@ -6489,17 +6595,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N66" s="6" t="n">
-        <v>22346010577.31221</v>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n">
@@ -6588,17 +6696,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
-        <v>93734615014.81729</v>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n">
@@ -6688,11 +6798,11 @@
         </is>
       </c>
       <c r="N68" s="6" t="n">
-        <v>4669818485578.365</v>
+        <v>4902301301361.686</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
@@ -6786,17 +6896,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
-        <v>74696456507.8008</v>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n">
@@ -6885,17 +6997,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
-        <v>28313919957.99379</v>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n">
@@ -6984,17 +7098,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N71" s="6" t="n">
-        <v>26785514945.32329</v>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n">
@@ -7083,17 +7199,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N72" s="6" t="n">
-        <v>1024471780310.382</v>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n">
@@ -7182,17 +7300,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N73" s="6" t="n">
-        <v>101788801301.5422</v>
+      <c r="N73" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q73" s="4" t="n">
@@ -7281,17 +7401,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N74" s="6" t="n">
-        <v>31160183031.05467</v>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n">
@@ -7380,17 +7502,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N75" s="6" t="n">
-        <v>111840731773.986</v>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n">
@@ -7479,17 +7603,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N76" s="6" t="n">
-        <v>31325643416.70934</v>
+      <c r="N76" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q76" s="4" t="n">
@@ -7578,17 +7704,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N77" s="6" t="n">
-        <v>34292567329.75598</v>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n">
@@ -7778,17 +7906,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N79" s="6" t="n">
-        <v>38538960821.18196</v>
+      <c r="N79" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q79" s="4" t="n">
@@ -7877,17 +8007,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N80" s="6" t="n">
-        <v>174020334853.8839</v>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n">
@@ -7976,17 +8108,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N81" s="6" t="n">
-        <v>24355665453.13372</v>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n">
@@ -8075,17 +8209,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N82" s="6" t="n">
-        <v>15830695667.06441</v>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n">
@@ -8174,17 +8310,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N83" s="6" t="n">
-        <v>54954087385.76248</v>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n">
@@ -8273,17 +8411,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N84" s="6" t="n">
-        <v>5450043893.417612</v>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n">
@@ -8372,17 +8512,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N85" s="6" t="n">
-        <v>18348476077.55541</v>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n">
@@ -8471,17 +8613,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N86" s="6" t="n">
-        <v>11773348509.40141</v>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n">
@@ -8570,17 +8714,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N87" s="6" t="n">
-        <v>73164431094.90726</v>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n">
@@ -8669,17 +8815,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N88" s="6" t="n">
-        <v>418890007002.7825</v>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n">
@@ -8769,11 +8917,11 @@
         </is>
       </c>
       <c r="N89" s="6" t="n">
-        <v>77037113169.76082</v>
+        <v>78469340035.26892</v>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
@@ -8867,17 +9015,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N90" s="6" t="n">
-        <v>4101096608748.116</v>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n">
@@ -8966,17 +9116,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N91" s="6" t="n">
-        <v>8220533433.757716</v>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n">
@@ -9065,17 +9217,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N92" s="6" t="n">
-        <v>4139043588458.335</v>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n">
@@ -9164,17 +9318,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N93" s="6" t="n">
-        <v>157797456994.3445</v>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n">
@@ -9263,17 +9419,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N94" s="6" t="n">
-        <v>168538839812.6613</v>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n">
@@ -9362,17 +9520,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N95" s="6" t="n">
-        <v>13049684141.30225</v>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n">
@@ -9461,17 +9621,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N96" s="6" t="n">
-        <v>25917911346.15949</v>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n">
@@ -9560,17 +9722,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N97" s="6" t="n">
-        <v>24541437631.37434</v>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n">
@@ -9660,11 +9824,11 @@
         </is>
       </c>
       <c r="N98" s="6" t="n">
-        <v>356451133426.2439</v>
+        <v>386990229190.2689</v>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
@@ -9758,17 +9922,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N99" s="6" t="n">
-        <v>13353650333.27187</v>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n">
@@ -9857,17 +10023,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N100" s="6" t="n">
-        <v>40420343507.9501</v>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n">
@@ -9956,17 +10124,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N101" s="6" t="n">
-        <v>14335076007.28123</v>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n">
@@ -10055,17 +10225,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N102" s="6" t="n">
-        <v>73994595431.27229</v>
+      <c r="N102" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q102" s="4" t="n">
@@ -10154,17 +10326,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N103" s="6" t="n">
-        <v>93993971476.67818</v>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n">
@@ -10253,17 +10427,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N104" s="6" t="n">
-        <v>34761619381.53812</v>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n">
@@ -10352,17 +10528,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N105" s="6" t="n">
-        <v>883486667.3958555</v>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n">
@@ -10451,17 +10629,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N106" s="6" t="n">
-        <v>24660393372.34336</v>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n">
@@ -10550,17 +10730,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N107" s="6" t="n">
-        <v>20483303501.60166</v>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n">
@@ -10649,17 +10831,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N108" s="6" t="n">
-        <v>79506017508.44188</v>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n">
@@ -10748,17 +10932,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N109" s="6" t="n">
-        <v>46015060778.90593</v>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n">
@@ -10847,17 +11033,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N110" s="6" t="n">
-        <v>26001595631.65267</v>
+      <c r="N110" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q110" s="4" t="n">
@@ -10947,11 +11135,11 @@
         </is>
       </c>
       <c r="N111" s="6" t="n">
-        <v>86936069250.94154</v>
+        <v>83368118461.96332</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
@@ -11045,17 +11233,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N112" s="6" t="n">
-        <v>34697645052.8852</v>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n">
@@ -11144,17 +11334,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N113" s="6" t="n">
-        <v>172067956103.03</v>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n">
@@ -11243,17 +11435,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N114" s="6" t="n">
-        <v>119096774599.5189</v>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n">
@@ -11342,17 +11536,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N115" s="6" t="n">
-        <v>21847412064.79042</v>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n">
@@ -11442,11 +11638,11 @@
         </is>
       </c>
       <c r="N116" s="6" t="n">
-        <v>506407349523.8503</v>
+        <v>477639241496.4196</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
@@ -11540,17 +11736,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N117" s="6" t="n">
-        <v>15606301757.02553</v>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n">
@@ -11639,17 +11837,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N118" s="6" t="n">
-        <v>97971554728.03851</v>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n">
@@ -11738,17 +11938,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N119" s="6" t="n">
-        <v>23420706947.93826</v>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n">
@@ -11837,17 +12039,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N120" s="6" t="n">
-        <v>31325643416.70934</v>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n">
@@ -11936,17 +12140,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N121" s="6" t="n">
-        <v>34142868075.79692</v>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n">
@@ -12035,17 +12241,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N122" s="6" t="n">
-        <v>23670094946.86908</v>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n">
@@ -12134,17 +12342,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N123" s="6" t="n">
-        <v>123737118993.5351</v>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n">
@@ -12233,17 +12443,19 @@
           <t>Consumer Disc</t>
         </is>
       </c>
-      <c r="N124" s="6" t="n">
-        <v>108943167965.9134</v>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n">
@@ -12332,17 +12544,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N125" s="6" t="n">
-        <v>63095734448.01942</v>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n">
@@ -12431,17 +12645,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N126" s="6" t="n">
-        <v>62201377127.44849</v>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n">
@@ -12530,17 +12746,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N127" s="6" t="n">
-        <v>14638615375.50617</v>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n">
@@ -12629,17 +12847,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N128" s="6" t="n">
-        <v>457404044030.0422</v>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n">
@@ -12728,17 +12948,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N129" s="6" t="n">
-        <v>30732649292.04296</v>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n">
@@ -12827,17 +13049,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N130" s="6" t="n">
-        <v>10176536626.20533</v>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n">
@@ -12926,17 +13150,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N131" s="6" t="n">
-        <v>69855402603.26953</v>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n">
@@ -13025,17 +13251,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N132" s="6" t="n">
-        <v>25668471016.67867</v>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n">
@@ -13124,17 +13352,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N133" s="6" t="n">
-        <v>11266784820.70996</v>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n">
@@ -13223,17 +13453,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N134" s="6" t="n">
-        <v>188018247349.0267</v>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n">
@@ -13322,17 +13554,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N135" s="6" t="n">
-        <v>438328793419.2465</v>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n">
@@ -13421,17 +13655,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N136" s="6" t="n">
-        <v>16865530253.88742</v>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n">
@@ -13520,17 +13756,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N137" s="6" t="n">
-        <v>56402713743.18951</v>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n">
@@ -13619,17 +13857,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N138" s="6" t="n">
-        <v>133505758956.2373</v>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n">
@@ -13718,17 +13958,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N139" s="6" t="n">
-        <v>13480313738.1309</v>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n">
@@ -13817,17 +14059,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N140" s="6" t="n">
-        <v>85467303076.69794</v>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n">
@@ -13916,17 +14160,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N141" s="6" t="n">
-        <v>154739076282.088</v>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n">
@@ -14015,17 +14261,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N142" s="6" t="n">
-        <v>85842034088.75208</v>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n">
@@ -14114,17 +14362,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N143" s="6" t="n">
-        <v>43331128521.18373</v>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n">
@@ -14213,17 +14463,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N144" s="6" t="n">
-        <v>47752927365.76912</v>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n">
@@ -14312,17 +14564,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N145" s="6" t="n">
-        <v>26260319155.78527</v>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n">
@@ -14411,17 +14665,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N146" s="6" t="n">
-        <v>121227179253.6498</v>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n">
@@ -14510,17 +14766,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N147" s="6" t="n">
-        <v>10228218569.34046</v>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n">
@@ -14609,17 +14867,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N148" s="6" t="n">
-        <v>230993628017.3185</v>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n">
@@ -14708,17 +14968,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N149" s="6" t="n">
-        <v>12829212537.09402</v>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n">
@@ -14807,17 +15069,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N150" s="6" t="n">
-        <v>45540731268.32545</v>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n">
@@ -14906,17 +15170,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N151" s="6" t="n">
-        <v>34793650764.90936</v>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n">
@@ -15005,17 +15271,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N152" s="6" t="n">
-        <v>149761437488.7368</v>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n">
@@ -15104,17 +15372,19 @@
           <t>Staples</t>
         </is>
       </c>
-      <c r="N153" s="6" t="n">
-        <v>40775566175.02126</v>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n">
@@ -15203,17 +15473,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N154" s="6" t="n">
-        <v>24564051543.2472</v>
+      <c r="N154" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q154" s="4" t="n">
@@ -15302,17 +15574,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N155" s="6" t="n">
-        <v>341979442513.7094</v>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n">
@@ -15402,11 +15676,11 @@
         </is>
       </c>
       <c r="N156" s="6" t="n">
-        <v>302412682128.3234</v>
+        <v>314267882987.9221</v>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
@@ -15500,17 +15774,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N157" s="6" t="n">
-        <v>105949765544.345</v>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n">
@@ -15599,17 +15875,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N158" s="6" t="n">
-        <v>81940762318.02795</v>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n">
@@ -15698,17 +15976,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N159" s="6" t="n">
-        <v>52868866585.08813</v>
+      <c r="N159" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O159" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P159" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q159" s="4" t="n">
@@ -15797,17 +16077,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N160" s="6" t="n">
-        <v>134958424601.9781</v>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n">
@@ -15897,11 +16179,11 @@
         </is>
       </c>
       <c r="N161" s="6" t="n">
-        <v>56963937334.11829</v>
+        <v>64923212314.32135</v>
       </c>
       <c r="O161" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P161" s="4" t="inlineStr">
@@ -15995,17 +16277,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N162" s="6" t="n">
-        <v>15310874616.82032</v>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n">
@@ -16094,17 +16378,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N163" s="6" t="n">
-        <v>37480036055.17048</v>
+      <c r="N163" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q163" s="4" t="n">
@@ -16193,17 +16479,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N164" s="6" t="n">
-        <v>27504262230.30312</v>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n">
@@ -16292,17 +16580,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N165" s="6" t="n">
-        <v>77339257804.89984</v>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n">
@@ -16392,11 +16682,11 @@
         </is>
       </c>
       <c r="N166" s="6" t="n">
-        <v>213353612143.8822</v>
+        <v>139862085574.5275</v>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
@@ -16490,17 +16780,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N167" s="6" t="n">
-        <v>68533040512.60461</v>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n">
@@ -16589,17 +16881,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N168" s="6" t="n">
-        <v>14983042106.22657</v>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n">
@@ -16690,17 +16984,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N169" s="6" t="n">
-        <v>25692123442.84064</v>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n">
@@ -16789,17 +17085,19 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="N170" s="6" t="n">
-        <v>14900471117.87098</v>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n">
@@ -16888,17 +17186,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N171" s="6" t="n">
-        <v>21892733982.28471</v>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n">
@@ -16987,17 +17287,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N172" s="6" t="n">
-        <v>24997697021.78508</v>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n">
@@ -17086,17 +17388,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N173" s="6" t="n">
-        <v>175954346729.7462</v>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n">
@@ -17185,17 +17489,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N174" s="6" t="n">
-        <v>35768440057.64751</v>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n">
@@ -17284,17 +17590,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N175" s="6" t="n">
-        <v>60020554038.7197</v>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n">
@@ -17383,17 +17691,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N176" s="6" t="n">
-        <v>192796879330.571</v>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n">
@@ -17482,17 +17792,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N177" s="6" t="n">
-        <v>162742131564.2231</v>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n">
@@ -17581,17 +17893,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N178" s="6" t="n">
-        <v>14002320047.85851</v>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n">
@@ -17680,17 +17994,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N179" s="6" t="n">
-        <v>161287236217.0399</v>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n">
@@ -17779,17 +18095,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N180" s="6" t="n">
-        <v>272082118209.1784</v>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n">
@@ -17878,17 +18196,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N181" s="6" t="n">
-        <v>9425404555.789734</v>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n">
@@ -17977,17 +18297,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N182" s="6" t="n">
-        <v>65629636672.922</v>
+      <c r="N182" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P182" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q182" s="4" t="n">
@@ -18076,17 +18398,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N183" s="6" t="n">
-        <v>21652098793.07927</v>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n">
@@ -18175,17 +18499,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N184" s="6" t="n">
-        <v>12525642149.63788</v>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n">
@@ -18274,17 +18600,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N185" s="6" t="n">
-        <v>21973538551.06546</v>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n">
@@ -18373,17 +18701,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N186" s="6" t="n">
-        <v>25709877064.15226</v>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n">
@@ -18472,17 +18802,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N187" s="6" t="n">
-        <v>20179016711.53197</v>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n">
@@ -18571,17 +18903,19 @@
           <t>Communication</t>
         </is>
       </c>
-      <c r="N188" s="6" t="n">
-        <v>107275364783.553</v>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n">
@@ -18670,17 +19004,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N189" s="6" t="n">
-        <v>16592048174.21631</v>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n">
@@ -18769,17 +19105,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N190" s="6" t="n">
-        <v>10370507263.25762</v>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n">
@@ -18870,17 +19208,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N191" s="6" t="n">
-        <v>418890007002.7825</v>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n">
@@ -18971,17 +19311,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N192" s="6" t="n">
-        <v>53431824008.73483</v>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n">
@@ -19073,11 +19415,11 @@
         </is>
       </c>
       <c r="N193" s="6" t="n">
-        <v>3710222886174.651</v>
+        <v>2925499309897.075</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P193" s="4" t="inlineStr">
@@ -19173,17 +19515,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N194" s="6" t="n">
-        <v>11773348509.40141</v>
+      <c r="N194" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P194" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q194" s="4" t="n">
@@ -19274,17 +19618,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N195" s="6" t="n">
-        <v>136489737964.495</v>
+      <c r="N195" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n">
@@ -19376,11 +19722,11 @@
         </is>
       </c>
       <c r="N196" s="6" t="n">
-        <v>213353612143.8822</v>
+        <v>139862085574.5275</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P196" s="4" t="inlineStr">
@@ -19478,17 +19824,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N197" s="6" t="n">
-        <v>106733315426.1837</v>
+      <c r="N197" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n">
@@ -19581,17 +19929,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N198" s="6" t="n">
-        <v>114683252142.2478</v>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n">
@@ -19682,17 +20032,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N199" s="6" t="n">
-        <v>109799408364.9603</v>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n">
@@ -19783,17 +20135,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N200" s="6" t="n">
-        <v>24541437631.37434</v>
+      <c r="N200" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n">
@@ -19884,17 +20238,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N201" s="6" t="n">
-        <v>4139043588458.335</v>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n">
@@ -19985,17 +20341,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N202" s="6" t="n">
-        <v>5310066989.662829</v>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
-          <t>2026-09-15</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-17 · prices = 2026-10-02 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-19 · prices = 2026-10-02 close</t>
         </is>
       </c>
     </row>
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (15 day(s) old) · ensemble STALE (15 day(s) old) · feature_store STALE (88 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (17 day(s) old) · ensemble STALE (17 day(s) old) · feature_store STALE (90 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1382,7 +1382,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1485,7 +1485,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1586,7 +1586,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1689,7 +1689,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1790,7 +1790,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1891,7 +1891,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1992,7 +1992,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2093,7 +2093,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2192,7 +2192,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2295,7 +2295,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2398,7 +2398,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2499,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2602,7 +2602,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2903,7 +2903,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3004,7 +3004,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3103,7 +3103,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3204,7 +3204,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3303,7 +3303,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3404,7 +3404,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3505,7 +3505,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3606,7 +3606,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3707,7 +3707,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3808,7 +3808,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3909,7 +3909,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4109,7 +4109,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4210,7 +4210,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4311,7 +4311,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4412,7 +4412,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4614,7 +4614,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4715,7 +4715,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4816,7 +4816,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4917,7 +4917,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5018,7 +5018,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5119,7 +5119,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5220,7 +5220,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5321,7 +5321,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5422,7 +5422,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5523,7 +5523,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5624,7 +5624,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5725,7 +5725,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5826,7 +5826,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5927,7 +5927,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6028,7 +6028,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6129,7 +6129,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6230,7 +6230,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6331,7 +6331,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6432,7 +6432,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6533,7 +6533,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6634,7 +6634,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6735,7 +6735,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6935,7 +6935,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7036,7 +7036,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7137,7 +7137,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7238,7 +7238,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7339,7 +7339,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7440,7 +7440,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7541,7 +7541,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7642,7 +7642,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7743,7 +7743,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7844,7 +7844,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7945,7 +7945,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8046,7 +8046,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8147,7 +8147,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8248,7 +8248,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8349,7 +8349,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8450,7 +8450,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8551,7 +8551,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8652,7 +8652,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8753,7 +8753,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 15d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8854,7 +8854,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9054,7 +9054,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9155,7 +9155,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9357,7 +9357,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9458,7 +9458,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9559,7 +9559,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9660,7 +9660,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9761,7 +9761,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9860,7 +9860,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9961,7 +9961,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10062,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10163,7 +10163,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10264,7 +10264,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10365,7 +10365,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10466,7 +10466,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10567,7 +10567,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10668,7 +10668,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10769,7 +10769,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 17d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10870,7 +10870,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10971,7 +10971,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11072,7 +11072,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11171,7 +11171,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11272,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11373,7 +11373,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11474,7 +11474,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11575,7 +11575,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11674,7 +11674,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11775,7 +11775,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11876,7 +11876,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11977,7 +11977,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12078,7 +12078,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12179,7 +12179,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12280,7 +12280,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12381,7 +12381,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12482,7 +12482,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12583,7 +12583,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12684,7 +12684,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12785,7 +12785,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12886,7 +12886,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12987,7 +12987,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13088,7 +13088,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13189,7 +13189,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13290,7 +13290,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13391,7 +13391,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13492,7 +13492,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13593,7 +13593,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13694,7 +13694,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13795,7 +13795,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13896,7 +13896,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13997,7 +13997,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14098,7 +14098,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14199,7 +14199,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14300,7 +14300,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14401,7 +14401,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14502,7 +14502,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14603,7 +14603,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14704,7 +14704,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14906,7 +14906,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15007,7 +15007,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15108,7 +15108,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15209,7 +15209,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15310,7 +15310,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15411,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15512,7 +15512,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15613,7 +15613,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15712,7 +15712,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15813,7 +15813,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15914,7 +15914,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16015,7 +16015,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16116,7 +16116,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16215,7 +16215,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16316,7 +16316,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16417,7 +16417,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16518,7 +16518,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16619,7 +16619,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16718,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16819,7 +16819,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16920,7 +16920,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17023,7 +17023,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 40d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17124,7 +17124,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17225,7 +17225,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17326,7 +17326,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17427,7 +17427,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17528,7 +17528,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17629,7 +17629,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17730,7 +17730,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17831,7 +17831,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17932,7 +17932,7 @@
       </c>
       <c r="W178" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18033,7 +18033,7 @@
       </c>
       <c r="W179" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18134,7 +18134,7 @@
       </c>
       <c r="W180" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="W181" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18336,7 +18336,7 @@
       </c>
       <c r="W182" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18437,7 +18437,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18538,7 +18538,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18639,7 +18639,7 @@
       </c>
       <c r="W185" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18740,7 +18740,7 @@
       </c>
       <c r="W186" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18841,7 +18841,7 @@
       </c>
       <c r="W187" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18942,7 +18942,7 @@
       </c>
       <c r="W188" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19043,7 +19043,7 @@
       </c>
       <c r="W189" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19144,7 +19144,7 @@
       </c>
       <c r="W190" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 30d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20563,7 +20563,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-10-17</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-10-19</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-20 · prices = 2026-10-19 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-21 · prices = 2026-10-19 close</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 30 scored · 148 already in CURRENT · biggest blocker: model disagreement (16) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 202 already in CURRENT · biggest blocker: model disagreement (15) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · feature_store STALE (91 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (2 day(s) old) · ensemble STALE (2 day(s) old) · feature_store STALE (92 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -766,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -869,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -972,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1075,7 +1075,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1180,7 +1180,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1281,7 +1281,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1384,7 +1384,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1487,7 +1487,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1590,7 +1590,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1693,7 +1693,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1796,7 +1796,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1897,7 +1897,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2101,7 +2101,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2202,7 +2202,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2303,7 +2303,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2406,7 +2406,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2509,7 +2509,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2612,7 +2612,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2816,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2919,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3022,7 +3022,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3226,7 +3226,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3327,7 +3327,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3428,7 +3428,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3529,7 +3529,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3630,7 +3630,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 18d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 19d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3731,7 +3731,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3832,7 +3832,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3933,7 +3933,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4034,7 +4034,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4135,7 +4135,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4236,7 +4236,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4337,7 +4337,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4438,7 +4438,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4539,7 +4539,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4642,7 +4642,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4743,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4846,7 +4846,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4949,7 +4949,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5050,7 +5050,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5151,7 +5151,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5252,7 +5252,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5353,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5454,7 +5454,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5557,7 +5557,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5759,7 +5759,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5860,7 +5860,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5961,7 +5961,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6062,7 +6062,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6163,7 +6163,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6264,7 +6264,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6365,7 +6365,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6466,7 +6466,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6567,7 +6567,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6668,7 +6668,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6769,7 +6769,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6870,7 +6870,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6969,7 +6969,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7070,7 +7070,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7171,7 +7171,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7272,7 +7272,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7371,7 +7371,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7472,7 +7472,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7573,7 +7573,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7674,7 +7674,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7775,7 +7775,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7975,7 +7975,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8076,7 +8076,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8177,7 +8177,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8278,7 +8278,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8379,7 +8379,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8480,7 +8480,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8581,7 +8581,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8682,7 +8682,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8785,7 +8785,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8886,7 +8886,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8987,7 +8987,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9088,7 +9088,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9189,7 +9189,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9290,7 +9290,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9391,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9492,7 +9492,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9593,7 +9593,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9694,7 +9694,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9795,7 +9795,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9997,7 +9997,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10098,7 +10098,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10199,7 +10199,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10300,7 +10300,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10401,7 +10401,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10502,7 +10502,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10702,7 +10702,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10803,7 +10803,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10904,7 +10904,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11005,7 +11005,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11106,7 +11106,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11207,7 +11207,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11308,7 +11308,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11409,7 +11409,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11510,7 +11510,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11611,7 +11611,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11712,7 +11712,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11813,7 +11813,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11914,7 +11914,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12015,7 +12015,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12116,7 +12116,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12217,7 +12217,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12318,7 +12318,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12419,7 +12419,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12520,7 +12520,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12621,7 +12621,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12722,7 +12722,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12823,7 +12823,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12924,7 +12924,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13025,7 +13025,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13126,7 +13126,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13227,7 +13227,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13328,7 +13328,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13427,7 +13427,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13528,7 +13528,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13629,7 +13629,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13730,7 +13730,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13831,7 +13831,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13932,7 +13932,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14031,7 +14031,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14132,7 +14132,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14233,7 +14233,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14334,7 +14334,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14435,7 +14435,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14536,7 +14536,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14637,7 +14637,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14738,7 +14738,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14839,7 +14839,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14938,7 +14938,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15039,7 +15039,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15140,7 +15140,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15241,7 +15241,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15342,7 +15342,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15443,7 +15443,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15544,7 +15544,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 23d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15746,7 +15746,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15847,7 +15847,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15948,7 +15948,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16049,7 +16049,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16150,7 +16150,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16251,7 +16251,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16352,7 +16352,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16453,7 +16453,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16554,7 +16554,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16655,7 +16655,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16756,7 +16756,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16857,7 +16857,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16958,7 +16958,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17057,7 +17057,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17158,7 +17158,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17259,7 +17259,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17360,7 +17360,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17461,7 +17461,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17562,7 +17562,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17663,7 +17663,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 25d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17764,7 +17764,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17865,7 +17865,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17966,7 +17966,7 @@
       </c>
       <c r="W178" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18067,7 +18067,7 @@
       </c>
       <c r="W179" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18168,7 +18168,7 @@
       </c>
       <c r="W180" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18269,7 +18269,7 @@
       </c>
       <c r="W181" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18370,7 +18370,7 @@
       </c>
       <c r="W182" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18469,7 +18469,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18570,7 +18570,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18671,7 +18671,7 @@
       </c>
       <c r="W185" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18774,7 +18774,7 @@
       </c>
       <c r="W186" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18875,7 +18875,7 @@
       </c>
       <c r="W187" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 20d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 21d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18974,7 +18974,7 @@
       </c>
       <c r="W188" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="W189" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19176,7 +19176,7 @@
       </c>
       <c r="W190" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19277,7 +19277,7 @@
       </c>
       <c r="W191" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 32d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19378,7 +19378,7 @@
       </c>
       <c r="W192" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19479,7 +19479,7 @@
       </c>
       <c r="W193" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19580,7 +19580,7 @@
       </c>
       <c r="W194" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19681,7 +19681,7 @@
       </c>
       <c r="W195" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19782,7 +19782,7 @@
       </c>
       <c r="W196" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19883,7 +19883,7 @@
       </c>
       <c r="W197" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19984,7 +19984,7 @@
       </c>
       <c r="W198" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20085,7 +20085,7 @@
       </c>
       <c r="W199" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20186,7 +20186,7 @@
       </c>
       <c r="W200" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20287,7 +20287,7 @@
       </c>
       <c r="W201" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20388,7 +20388,7 @@
       </c>
       <c r="W202" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 35d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20489,7 +20489,7 @@
       </c>
       <c r="W203" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20590,7 +20590,7 @@
       </c>
       <c r="W204" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20693,7 +20693,7 @@
       </c>
       <c r="W205" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 42d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 43d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20792,7 +20792,7 @@
       </c>
       <c r="W206" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20893,7 +20893,7 @@
       </c>
       <c r="W207" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 34d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20994,7 +20994,7 @@
       </c>
       <c r="W208" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 27d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -22310,7 +22310,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-10-20</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-10-21</t>
         </is>
       </c>
     </row>
@@ -22413,7 +22413,7 @@
     <row r="5">
       <c r="A5" s="4" t="inlineStr">
         <is>
-          <t>2026-10-20</t>
+          <t>2026-10-21</t>
         </is>
       </c>
       <c r="B5" s="4" t="inlineStr">
@@ -22456,7 +22456,7 @@
         <v>-6.88</v>
       </c>
       <c r="K5" s="4" t="n">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="L5" s="4" t="inlineStr">
         <is>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 NEW=3 · 30 scored · 203 already in CURRENT · biggest blocker: model disagreement (15) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 516 scored · 204 already in CURRENT · biggest blocker: model disagreement (265) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · feature_store STALE (95 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 203 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -725,19 +725,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N8" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N8" s="6" t="n">
+        <v>16565326493.18021</v>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n">
@@ -793,7 +791,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -828,19 +826,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N9" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N9" s="6" t="n">
+        <v>35546758199.90703</v>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n">
@@ -896,7 +892,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -931,19 +927,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N10" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N10" s="6" t="n">
+        <v>52299796618.21564</v>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n">
@@ -999,7 +993,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1034,19 +1028,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N11" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N11" s="6" t="n">
+        <v>35107507718.48309</v>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n">
@@ -1102,7 +1094,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1138,11 +1130,11 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>197696964011.1858</v>
+        <v>237465214365.1677</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1203,7 +1195,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1238,19 +1230,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N13" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N13" s="6" t="n">
+        <v>160250723888.1421</v>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n">
@@ -1306,7 +1296,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1341,19 +1331,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N14" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N14" s="6" t="n">
+        <v>78342964276.6212</v>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n">
@@ -1409,7 +1397,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1444,19 +1432,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N15" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N15" s="6" t="n">
+        <v>11638580103.4434</v>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n">
@@ -1510,7 +1496,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1545,19 +1531,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N16" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N16" s="6" t="n">
+        <v>43331128521.18373</v>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n">
@@ -1613,7 +1597,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1648,19 +1632,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N17" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N17" s="6" t="n">
+        <v>42325295609.19834</v>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n">
@@ -1714,7 +1696,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1749,19 +1731,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N18" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N18" s="6" t="n">
+        <v>33481121738.60545</v>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n">
@@ -1817,7 +1797,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1852,19 +1832,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N19" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N19" s="6" t="n">
+        <v>139572545770.6767</v>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n">
@@ -1920,7 +1898,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1955,19 +1933,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N20" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N20" s="6" t="n">
+        <v>14893610777.10915</v>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n">
@@ -2021,7 +1997,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2056,19 +2032,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N21" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N21" s="6" t="n">
+        <v>42024252767.73121</v>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n">
@@ -2124,7 +2098,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2159,19 +2133,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N22" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N22" s="6" t="n">
+        <v>106856267459.9962</v>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n">
@@ -2227,7 +2199,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2263,11 +2235,11 @@
         </is>
       </c>
       <c r="N23" s="6" t="n">
-        <v>386990229190.2689</v>
+        <v>375318524237.9146</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2328,7 +2300,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2363,19 +2335,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N24" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N24" s="6" t="n">
+        <v>54025649909.99312</v>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n">
@@ -2431,7 +2401,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2466,19 +2436,17 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N25" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N25" s="6" t="n">
+        <v>23469292626.86464</v>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n">
@@ -2534,7 +2502,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2569,19 +2537,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N26" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N26" s="6" t="n">
+        <v>27052038697.19351</v>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n">
@@ -2637,7 +2603,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2672,19 +2638,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N27" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N27" s="6" t="n">
+        <v>14541191703.75174</v>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n">
@@ -2740,7 +2704,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2775,19 +2739,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N28" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N28" s="6" t="n">
+        <v>1135010815672.314</v>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n">
@@ -2843,7 +2805,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2878,19 +2840,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N29" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N29" s="6" t="n">
+        <v>48752849010.3387</v>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n">
@@ -2946,7 +2906,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2981,19 +2941,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N30" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N30" s="6" t="n">
+        <v>32501245188.6184</v>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n">
@@ -3049,7 +3007,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3084,19 +3042,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N31" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N31" s="6" t="n">
+        <v>52710847623.63955</v>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n">
@@ -3150,7 +3106,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3185,19 +3141,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N32" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N32" s="6" t="n">
+        <v>133475021658.0953</v>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n">
@@ -3253,7 +3207,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3288,19 +3242,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N33" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N33" s="6" t="n">
+        <v>68391164728.14307</v>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n">
@@ -3356,7 +3308,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3391,19 +3343,17 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N34" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N34" s="6" t="n">
+        <v>23512564504.17719</v>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n">
@@ -3457,7 +3407,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3492,19 +3442,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N35" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N35" s="6" t="n">
+        <v>5040806191.026701</v>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n">
@@ -3560,7 +3508,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3595,19 +3543,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N36" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N36" s="6" t="n">
+        <v>14986492476.39007</v>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n">
@@ -3663,7 +3609,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3698,19 +3644,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N37" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N37" s="6" t="n">
+        <v>97454074176.63052</v>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n">
@@ -3766,7 +3710,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3801,19 +3745,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N38" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N38" s="6" t="n">
+        <v>29100469778.37717</v>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n">
@@ -3869,7 +3811,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3904,19 +3846,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N39" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N39" s="6" t="n">
+        <v>14285649813.94612</v>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n">
@@ -3970,7 +3910,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -4005,19 +3945,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N40" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N40" s="6" t="n">
+        <v>18184442878.42896</v>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n">
@@ -4073,7 +4011,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -4108,19 +4046,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N41" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N41" s="6" t="n">
+        <v>44207911687.56331</v>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n">
@@ -4176,7 +4112,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4213,19 +4149,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N42" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N42" s="6" t="n">
+        <v>120725774433.4873</v>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n">
@@ -4281,7 +4215,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -4316,19 +4250,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N43" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N43" s="6" t="n">
+        <v>29730348496.77023</v>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n">
@@ -4384,7 +4316,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4419,19 +4351,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N44" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N44" s="6" t="n">
+        <v>27447323434.78532</v>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n">
@@ -4487,7 +4417,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4523,11 +4453,11 @@
         </is>
       </c>
       <c r="N45" s="6" t="n">
-        <v>71285303012.65192</v>
+        <v>70097091758.43842</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -4588,7 +4518,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -4623,19 +4553,17 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N46" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N46" s="6" t="n">
+        <v>23555916164.69393</v>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n">
@@ -4691,7 +4619,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4726,19 +4654,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N47" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N47" s="6" t="n">
+        <v>8379150674.384088</v>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n">
@@ -4794,7 +4720,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -4829,19 +4755,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N48" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N48" s="6" t="n">
+        <v>19467043530.01433</v>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n">
@@ -4897,7 +4821,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4932,19 +4856,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N49" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N49" s="6" t="n">
+        <v>76594925837.28877</v>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n">
@@ -5000,7 +4922,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -5035,19 +4957,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N50" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N50" s="6" t="n">
+        <v>260015956316.5267</v>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n">
@@ -5101,7 +5021,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -5136,19 +5056,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N51" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N51" s="6" t="n">
+        <v>88044047616.46739</v>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n">
@@ -5204,7 +5122,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5239,19 +5157,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N52" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N52" s="6" t="n">
+        <v>13743583962.97344</v>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n">
@@ -5305,7 +5221,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5340,19 +5256,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N53" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N53" s="6" t="n">
+        <v>14044296835.7795</v>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n">
@@ -5408,7 +5322,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5443,19 +5357,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N54" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N54" s="6" t="n">
+        <v>54966742488.92049</v>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n">
@@ -5511,7 +5423,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5546,19 +5458,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N55" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N55" s="6" t="n">
+        <v>10334750585.25211</v>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n">
@@ -5612,7 +5522,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -5647,19 +5557,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N56" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N56" s="6" t="n">
+        <v>113005608974.8537</v>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n">
@@ -5713,7 +5621,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -5748,19 +5656,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N57" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N57" s="6" t="n">
+        <v>22898129121.07968</v>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n">
@@ -5816,7 +5722,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -5851,19 +5757,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N58" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N58" s="6" t="n">
+        <v>22069881433.58583</v>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n">
@@ -5917,7 +5821,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -5952,19 +5856,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N59" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N59" s="6" t="n">
+        <v>181175721711.0555</v>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n">
@@ -6020,7 +5922,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -6055,19 +5957,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N60" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N60" s="6" t="n">
+        <v>86836037996.05959</v>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n">
@@ -6121,7 +6021,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -6156,19 +6056,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N61" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N61" s="6" t="n">
+        <v>13079766770.08932</v>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n">
@@ -6222,7 +6120,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -6257,19 +6155,17 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N62" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N62" s="6" t="n">
+        <v>18437413677.71741</v>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n">
@@ -6323,7 +6219,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -6358,19 +6254,17 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N63" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N63" s="6" t="n">
+        <v>172186857498.601</v>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n">
@@ -6426,7 +6320,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -6461,19 +6355,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N64" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N64" s="6" t="n">
+        <v>22304885593.77609</v>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n">
@@ -6527,7 +6419,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -6562,19 +6454,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N65" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N65" s="6" t="n">
+        <v>15845282993.28703</v>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n">
@@ -6630,7 +6520,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -6665,19 +6555,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N66" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N66" s="6" t="n">
+        <v>181677020981.8806</v>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n">
@@ -6731,7 +6619,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -6766,19 +6654,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N67" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N67" s="6" t="n">
+        <v>119536352567.372</v>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n">
@@ -6832,7 +6718,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6867,19 +6753,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N68" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N68" s="6" t="n">
+        <v>80519301730.83093</v>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n">
@@ -6933,7 +6817,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -6968,19 +6852,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N69" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N69" s="6" t="n">
+        <v>64833579512.20567</v>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n">
@@ -7034,7 +6916,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -7069,19 +6951,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N70" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N70" s="6" t="n">
+        <v>472824530511.796</v>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n">
@@ -7135,7 +7015,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -7170,19 +7050,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N71" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N71" s="6" t="n">
+        <v>6934258060.16568</v>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n">
@@ -7236,7 +7114,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -7271,19 +7149,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N72" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N72" s="6" t="n">
+        <v>25786951295.65876</v>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n">
@@ -7337,7 +7213,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -7373,11 +7249,11 @@
         </is>
       </c>
       <c r="N73" s="6" t="n">
-        <v>2925499309897.075</v>
+        <v>3894933077036.549</v>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -7436,7 +7312,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -7471,19 +7347,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N74" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N74" s="6" t="n">
+        <v>91769845384.9781</v>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n">
@@ -7537,7 +7411,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7572,19 +7446,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N75" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N75" s="6" t="n">
+        <v>24417432734.96738</v>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n">
@@ -7638,7 +7510,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -7674,11 +7546,11 @@
         </is>
       </c>
       <c r="N76" s="6" t="n">
-        <v>83368118461.96332</v>
+        <v>89454048377.8867</v>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -7737,7 +7609,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -7772,19 +7644,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N77" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N77" s="6" t="n">
+        <v>56650011191.95325</v>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n">
@@ -7838,7 +7708,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -7873,19 +7743,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N78" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N78" s="6" t="n">
+        <v>152615976562.5463</v>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n">
@@ -7939,7 +7807,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -7975,11 +7843,11 @@
         </is>
       </c>
       <c r="N79" s="6" t="n">
-        <v>4902301301361.686</v>
+        <v>5074578790806.488</v>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -8038,7 +7906,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -8073,19 +7941,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N80" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N80" s="6" t="n">
+        <v>83348924453.15994</v>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n">
@@ -8139,7 +8005,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -8174,19 +8040,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N81" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N81" s="6" t="n">
+        <v>13255618607.19861</v>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n">
@@ -8240,7 +8104,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -8275,19 +8139,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N82" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N82" s="6" t="n">
+        <v>11043328726.70052</v>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n">
@@ -8341,7 +8203,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -8376,19 +8238,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N83" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N83" s="6" t="n">
+        <v>125574078540.1959</v>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n">
@@ -8442,7 +8302,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -8477,19 +8337,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N84" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N84" s="6" t="n">
+        <v>31651915672.26271</v>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n">
@@ -8543,7 +8401,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -8578,19 +8436,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N85" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N85" s="6" t="n">
+        <v>57902857947.4638</v>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n">
@@ -8644,7 +8500,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -8679,19 +8535,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N86" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N86" s="6" t="n">
+        <v>24254928571.09423</v>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n">
@@ -8745,7 +8599,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -8780,19 +8634,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N87" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N87" s="6" t="n">
+        <v>132068729514.6421</v>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n">
@@ -8846,7 +8698,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -8881,19 +8733,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N88" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N88" s="6" t="n">
+        <v>114921159720.324</v>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n">
@@ -8947,7 +8797,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8982,19 +8832,17 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N89" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N89" s="6" t="n">
+        <v>21463473177.2398</v>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n">
@@ -9048,7 +8896,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -9083,19 +8931,17 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N90" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N90" s="6" t="n">
+        <v>185012043477.1862</v>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n">
@@ -9149,7 +8995,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -9184,19 +9030,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N91" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N91" s="6" t="n">
+        <v>123509396601.4861</v>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n">
@@ -9250,7 +9094,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -9285,19 +9129,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N92" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N92" s="6" t="n">
+        <v>59237947158.77261</v>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n">
@@ -9351,7 +9193,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -9386,19 +9228,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N93" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N93" s="6" t="n">
+        <v>18407720014.68958</v>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n">
@@ -9452,7 +9292,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -9487,19 +9327,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N94" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N94" s="6" t="n">
+        <v>28973435877.01321</v>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n">
@@ -9553,7 +9391,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -9588,19 +9426,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N95" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N95" s="6" t="n">
+        <v>80334112475.79723</v>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n">
@@ -9654,7 +9490,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -9689,19 +9525,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N96" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N96" s="6" t="n">
+        <v>173980269803.8291</v>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n">
@@ -9755,7 +9589,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -9790,19 +9624,17 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N97" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N97" s="6" t="n">
+        <v>90489877439.44135</v>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n">
@@ -9856,7 +9688,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -9891,19 +9723,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N98" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N98" s="6" t="n">
+        <v>27058268376.48824</v>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n">
@@ -9957,7 +9787,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -9992,19 +9822,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N99" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N99" s="6" t="n">
+        <v>13280058862.43732</v>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n">
@@ -10058,7 +9886,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -10093,19 +9921,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N100" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N100" s="6" t="n">
+        <v>74113956796.00749</v>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n">
@@ -10159,7 +9985,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -10194,19 +10020,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N101" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N101" s="6" t="n">
+        <v>27220744551.05336</v>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n">
@@ -10260,7 +10084,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -10296,11 +10120,11 @@
         </is>
       </c>
       <c r="N102" s="6" t="n">
-        <v>64923212314.32135</v>
+        <v>55398754393.85931</v>
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
@@ -10359,7 +10183,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -10394,19 +10218,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N103" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N103" s="6" t="n">
+        <v>82889591627.31059</v>
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n">
@@ -10460,7 +10282,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -10495,19 +10317,17 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N104" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N104" s="6" t="n">
+        <v>34617842683.75591</v>
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n">
@@ -10561,7 +10381,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -10596,19 +10416,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N105" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N105" s="6" t="n">
+        <v>753355563733.7185</v>
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n">
@@ -10662,7 +10480,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -10697,19 +10515,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N106" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N106" s="6" t="n">
+        <v>33465706661.96794</v>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n">
@@ -10763,7 +10579,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -10798,19 +10614,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N107" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N107" s="6" t="n">
+        <v>64387268290.14609</v>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n">
@@ -10864,7 +10678,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -10899,19 +10713,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N108" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N108" s="6" t="n">
+        <v>102683343166.8086</v>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n">
@@ -10965,7 +10777,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -11000,19 +10812,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N109" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N109" s="6" t="n">
+        <v>22495725294.22522</v>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n">
@@ -11066,7 +10876,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -11102,11 +10912,11 @@
         </is>
       </c>
       <c r="N110" s="6" t="n">
-        <v>78469340035.26892</v>
+        <v>83080671870.19131</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -11165,7 +10975,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -11200,19 +11010,17 @@
           <t>Consumer Disc</t>
         </is>
       </c>
-      <c r="N111" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N111" s="6" t="n">
+        <v>102991171934.07</v>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n">
@@ -11266,7 +11074,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -11301,19 +11109,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N112" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N112" s="6" t="n">
+        <v>40401733537.30011</v>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n">
@@ -11367,7 +11173,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -11402,19 +11208,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N113" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N113" s="6" t="n">
+        <v>47293341491.86511</v>
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n">
@@ -11468,7 +11272,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -11503,19 +11307,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N114" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N114" s="6" t="n">
+        <v>59169786195.87192</v>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n">
@@ -11569,7 +11371,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -11604,19 +11406,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N115" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N115" s="6" t="n">
+        <v>73248713266.5041</v>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n">
@@ -11670,7 +11470,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -11705,19 +11505,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N116" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N116" s="6" t="n">
+        <v>25503512602.75335</v>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n">
@@ -11771,7 +11569,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -11806,19 +11604,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N117" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N117" s="6" t="n">
+        <v>546260754212.6935</v>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n">
@@ -11872,7 +11668,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -11907,19 +11703,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N118" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N118" s="6" t="n">
+        <v>156639035387.289</v>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n">
@@ -11973,7 +11767,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -12008,19 +11802,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N119" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N119" s="6" t="n">
+        <v>64150493251.06628</v>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n">
@@ -12074,7 +11866,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -12109,19 +11901,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N120" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N120" s="6" t="n">
+        <v>37887853374.84371</v>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n">
@@ -12175,7 +11965,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -12210,19 +12000,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N121" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N121" s="6" t="n">
+        <v>23960727497.45567</v>
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n">
@@ -12276,7 +12064,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -12311,19 +12099,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N122" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N122" s="6" t="n">
+        <v>25846396357.69842</v>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n">
@@ -12377,7 +12163,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -12412,19 +12198,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N123" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N123" s="6" t="n">
+        <v>16266720329.71902</v>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n">
@@ -12478,7 +12262,7 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -12513,19 +12297,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N124" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N124" s="6" t="n">
+        <v>32129206511.4126</v>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n">
@@ -12579,7 +12361,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -12614,19 +12396,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N125" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N125" s="6" t="n">
+        <v>37042475302.99583</v>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n">
@@ -12680,7 +12460,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -12715,19 +12495,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N126" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N126" s="6" t="n">
+        <v>19399922723.90986</v>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n">
@@ -12781,7 +12559,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -12816,19 +12594,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N127" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N127" s="6" t="n">
+        <v>98559842315.65967</v>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n">
@@ -12882,7 +12658,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -12917,19 +12693,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N128" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N128" s="6" t="n">
+        <v>89557095464.32736</v>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n">
@@ -12983,7 +12757,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -13018,19 +12792,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N129" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N129" s="6" t="n">
+        <v>21052321804.7523</v>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n">
@@ -13084,7 +12856,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -13119,19 +12891,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N130" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N130" s="6" t="n">
+        <v>30338911841.94266</v>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n">
@@ -13185,7 +12955,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -13220,19 +12990,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N131" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N131" s="6" t="n">
+        <v>56532735426.60712</v>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n">
@@ -13286,7 +13054,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -13321,19 +13089,17 @@
           <t>Consumer Disc</t>
         </is>
       </c>
-      <c r="N132" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N132" s="6" t="n">
+        <v>20945946985.81395</v>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n">
@@ -13387,7 +13153,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -13422,19 +13188,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N133" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N133" s="6" t="n">
+        <v>109925892401.5142</v>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n">
@@ -13488,7 +13252,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -13523,19 +13287,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N134" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N134" s="6" t="n">
+        <v>21423972391.2723</v>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n">
@@ -13589,7 +13351,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -13624,19 +13386,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N135" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N135" s="6" t="n">
+        <v>27599422828.54258</v>
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n">
@@ -13690,7 +13450,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -13725,19 +13485,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N136" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N136" s="6" t="n">
+        <v>22227980135.64559</v>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n">
@@ -13791,7 +13549,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -13826,19 +13584,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N137" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N137" s="6" t="n">
+        <v>56027339479.37971</v>
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n">
@@ -13892,7 +13648,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -13927,19 +13683,17 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N138" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N138" s="6" t="n">
+        <v>34087880601.02591</v>
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n">
@@ -13993,7 +13747,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -14028,19 +13782,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N139" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N139" s="6" t="n">
+        <v>48028608023.96908</v>
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n">
@@ -14094,7 +13846,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -14129,19 +13881,17 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N140" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N140" s="6" t="n">
+        <v>69390497307.31636</v>
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n">
@@ -14195,7 +13945,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -14230,19 +13980,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N141" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N141" s="6" t="n">
+        <v>10799409266.63105</v>
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n">
@@ -14296,7 +14044,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -14331,19 +14079,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N142" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N142" s="6" t="n">
+        <v>22485368014.91627</v>
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n">
@@ -14397,7 +14143,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -14432,19 +14178,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N143" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N143" s="6" t="n">
+        <v>34689656544.60545</v>
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n">
@@ -14498,7 +14242,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -14533,19 +14277,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N144" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N144" s="6" t="n">
+        <v>28086653727.67912</v>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n">
@@ -14599,7 +14341,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -14634,19 +14376,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N145" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N145" s="6" t="n">
+        <v>25072636247.77122</v>
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n">
@@ -14700,7 +14440,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -14735,19 +14475,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N146" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N146" s="6" t="n">
+        <v>96827785626.12506</v>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n">
@@ -14801,7 +14539,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -14836,19 +14574,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N147" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N147" s="6" t="n">
+        <v>64017690131.78958</v>
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n">
@@ -14902,7 +14638,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -14937,19 +14673,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N148" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N148" s="6" t="n">
+        <v>9449307890.342999</v>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n">
@@ -15003,7 +14737,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -15038,19 +14772,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N149" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N149" s="6" t="n">
+        <v>73943499425.51872</v>
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n">
@@ -15104,7 +14836,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -15139,19 +14871,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N150" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N150" s="6" t="n">
+        <v>14115621351.87959</v>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n">
@@ -15205,7 +14935,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -15240,19 +14970,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N151" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N151" s="6" t="n">
+        <v>825467539.8117318</v>
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Small</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n">
@@ -15306,7 +15034,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -15341,19 +15069,17 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N152" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N152" s="6" t="n">
+        <v>12947919779.15331</v>
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n">
@@ -15407,7 +15133,7 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -15442,19 +15168,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N153" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N153" s="6" t="n">
+        <v>14292230113.86092</v>
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n">
@@ -15508,7 +15232,7 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -15544,11 +15268,11 @@
         </is>
       </c>
       <c r="N154" s="6" t="n">
-        <v>139862085574.5275</v>
+        <v>204550243110.9356</v>
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -15607,7 +15331,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -15642,19 +15366,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N155" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N155" s="6" t="n">
+        <v>13645831365.88924</v>
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n">
@@ -15708,7 +15430,7 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -15743,19 +15465,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N156" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N156" s="6" t="n">
+        <v>87297136838.81131</v>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n">
@@ -15809,7 +15529,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -15844,19 +15564,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N157" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N157" s="6" t="n">
+        <v>30718499642.34457</v>
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n">
@@ -15910,7 +15628,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -15945,19 +15663,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N158" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N158" s="6" t="n">
+        <v>111045253533.3641</v>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n">
@@ -16011,7 +15727,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -16047,11 +15763,11 @@
         </is>
       </c>
       <c r="N159" s="6" t="n">
-        <v>4912471004503.345</v>
+        <v>5094481623274.441</v>
       </c>
       <c r="O159" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P159" s="4" t="inlineStr">
@@ -16110,7 +15826,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -16145,19 +15861,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N160" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N160" s="6" t="n">
+        <v>14537843856.07661</v>
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n">
@@ -16211,7 +15925,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -16246,19 +15960,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N161" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N161" s="6" t="n">
+        <v>992887401325.0432</v>
       </c>
       <c r="O161" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n">
@@ -16312,7 +16024,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -16347,19 +16059,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N162" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N162" s="6" t="n">
+        <v>82432790167.59808</v>
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n">
@@ -16413,7 +16123,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -16449,11 +16159,11 @@
         </is>
       </c>
       <c r="N163" s="6" t="n">
-        <v>2659500032721.515</v>
+        <v>2674853493963.549</v>
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -16512,7 +16222,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -16547,19 +16257,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N164" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N164" s="6" t="n">
+        <v>21902818280.68457</v>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n">
@@ -16613,7 +16321,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -16648,19 +16356,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N165" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N165" s="6" t="n">
+        <v>53592004345.77758</v>
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n">
@@ -16714,7 +16420,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -16749,19 +16455,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N166" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N166" s="6" t="n">
+        <v>122913617306.017</v>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n">
@@ -16815,7 +16519,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -16850,19 +16554,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N167" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N167" s="6" t="n">
+        <v>136238546003.0834</v>
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n">
@@ -16916,7 +16618,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -16951,19 +16653,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N168" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N168" s="6" t="n">
+        <v>296346634854.8615</v>
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n">
@@ -17017,7 +16717,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -17052,19 +16752,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N169" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N169" s="6" t="n">
+        <v>140993794935.8725</v>
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n">
@@ -17118,7 +16816,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -17153,19 +16851,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N170" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N170" s="6" t="n">
+        <v>3880610013548.706</v>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n">
@@ -17219,7 +16915,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -17254,19 +16950,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N171" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N171" s="6" t="n">
+        <v>3916516855912.108</v>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n">
@@ -17320,7 +17014,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -17355,19 +17049,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N172" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N172" s="6" t="n">
+        <v>48283639645.51581</v>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n">
@@ -17421,7 +17113,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -17456,19 +17148,17 @@
           <t>Staples</t>
         </is>
       </c>
-      <c r="N173" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N173" s="6" t="n">
+        <v>38627802301.14958</v>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n">
@@ -17522,7 +17212,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -17557,19 +17247,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N174" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N174" s="6" t="n">
+        <v>843723217211.8292</v>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n">
@@ -17623,7 +17311,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -17660,19 +17348,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N175" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N175" s="6" t="n">
+        <v>23453086212.00278</v>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n">
@@ -17726,7 +17412,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -17761,19 +17447,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N176" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N176" s="6" t="n">
+        <v>247286267818.7022</v>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n">
@@ -17827,7 +17511,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -17862,19 +17546,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N177" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N177" s="6" t="n">
+        <v>23329208255.60109</v>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n">
@@ -17928,7 +17610,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -17963,19 +17645,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N178" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N178" s="6" t="n">
+        <v>120753575770.9667</v>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n">
@@ -18029,7 +17709,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -18064,19 +17744,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N179" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N179" s="6" t="n">
+        <v>136772882559.5847</v>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n">
@@ -18130,7 +17808,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -18165,19 +17843,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N180" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N180" s="6" t="n">
+        <v>353590021100.3874</v>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n">
@@ -18231,7 +17907,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -18266,19 +17942,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N181" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N181" s="6" t="n">
+        <v>182683784530.852</v>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n">
@@ -18332,7 +18006,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -18368,11 +18042,11 @@
         </is>
       </c>
       <c r="N182" s="6" t="n">
-        <v>314267882987.9221</v>
+        <v>254976408779.9279</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P182" s="4" t="inlineStr">
@@ -18431,7 +18105,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -18466,19 +18140,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N183" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N183" s="6" t="n">
+        <v>217420254616.1736</v>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n">
@@ -18532,7 +18204,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -18567,19 +18239,17 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N184" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N184" s="6" t="n">
+        <v>18264172487.74352</v>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n">
@@ -18633,7 +18303,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -18668,19 +18338,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N185" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N185" s="6" t="n">
+        <v>202348504969.1966</v>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n">
@@ -18734,7 +18402,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -18769,19 +18437,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N186" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N186" s="6" t="n">
+        <v>28569326345.83695</v>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n">
@@ -18835,7 +18501,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -18870,19 +18536,17 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N187" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N187" s="6" t="n">
+        <v>113135786411.9562</v>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n">
@@ -18936,7 +18600,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -18971,19 +18635,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N188" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N188" s="6" t="n">
+        <v>382472311023.9288</v>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n">
@@ -19037,7 +18699,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -19072,19 +18734,17 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N189" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N189" s="6" t="n">
+        <v>14047531026.96879</v>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n">
@@ -19138,7 +18798,7 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -19173,19 +18833,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N190" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N190" s="6" t="n">
+        <v>281903196263.6478</v>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n">
@@ -19239,7 +18897,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -19274,19 +18932,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N191" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N191" s="6" t="n">
+        <v>205352502645.7146</v>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n">
@@ -19340,7 +18996,7 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -19375,19 +19031,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N192" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N192" s="6" t="n">
+        <v>85467303076.69794</v>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n">
@@ -19441,7 +19095,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -19476,19 +19130,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N193" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N193" s="6" t="n">
+        <v>82148568512.83273</v>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n">
@@ -19542,7 +19194,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -19578,11 +19230,11 @@
         </is>
       </c>
       <c r="N194" s="6" t="n">
-        <v>405415174406.5037</v>
+        <v>315791182863.2249</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P194" s="4" t="inlineStr">
@@ -19641,7 +19293,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -19676,19 +19328,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N195" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N195" s="6" t="n">
+        <v>217070096839.7714</v>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n">
@@ -19742,7 +19392,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -19777,19 +19427,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N196" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N196" s="6" t="n">
+        <v>18484171953.69656</v>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n">
@@ -19843,7 +19491,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -19878,19 +19526,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N197" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N197" s="6" t="n">
+        <v>290201731938.0225</v>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n">
@@ -19944,7 +19590,7 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -19979,19 +19625,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N198" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N198" s="6" t="n">
+        <v>7488589075.216432</v>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n">
@@ -20045,7 +19689,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -20080,19 +19724,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N199" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N199" s="6" t="n">
+        <v>128647099802.9103</v>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n">
@@ -20146,7 +19788,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -20181,19 +19823,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N200" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N200" s="6" t="n">
+        <v>74148095394.52744</v>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n">
@@ -20247,7 +19887,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -20282,19 +19922,17 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="N201" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N201" s="6" t="n">
+        <v>11053504693.82843</v>
       </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n">
@@ -20348,7 +19986,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -20385,19 +20023,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N202" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N202" s="6" t="n">
+        <v>21305905675.42725</v>
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n">
@@ -20451,7 +20087,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -20486,19 +20122,17 @@
           <t>Communication</t>
         </is>
       </c>
-      <c r="N203" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N203" s="6" t="n">
+        <v>87096358995.60797</v>
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n">
@@ -20552,7 +20186,7 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -20587,19 +20221,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N204" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N204" s="6" t="n">
+        <v>178936937444.5307</v>
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n">
@@ -20653,7 +20285,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -20688,19 +20320,17 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N205" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N205" s="6" t="n">
+        <v>140993794935.8725</v>
       </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n">
@@ -20754,7 +20384,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -20789,19 +20419,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N206" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N206" s="6" t="n">
+        <v>287938673780.7982</v>
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n">
@@ -20855,7 +20483,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -20890,19 +20518,17 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N207" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N207" s="6" t="n">
+        <v>7059923578.936683</v>
       </c>
       <c r="O207" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n">
@@ -20956,7 +20582,7 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -20992,11 +20618,11 @@
         </is>
       </c>
       <c r="N208" s="6" t="n">
-        <v>477639241496.4196</v>
+        <v>459726988530.8718</v>
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P208" s="4" t="inlineStr">
@@ -21055,7 +20681,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -21090,19 +20716,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N209" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N209" s="6" t="n">
+        <v>40860154081.38228</v>
       </c>
       <c r="O209" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n">
@@ -21156,7 +20780,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -21191,19 +20815,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N210" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N210" s="6" t="n">
+        <v>143383771605.5808</v>
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n">
@@ -21294,19 +20916,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N211" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N211" s="6" t="n">
+        <v>14541191703.75174</v>
       </c>
       <c r="O211" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n">
@@ -21399,19 +21019,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N212" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N212" s="6" t="n">
+        <v>472824530511.796</v>
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n">
@@ -21502,19 +21120,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N213" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N213" s="6" t="n">
+        <v>56650011191.95325</v>
       </c>
       <c r="O213" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n">
@@ -21606,11 +21222,11 @@
         </is>
       </c>
       <c r="N214" s="6" t="n">
-        <v>2925499309897.075</v>
+        <v>3894933077036.549</v>
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P214" s="4" t="inlineStr">
@@ -21706,19 +21322,17 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N215" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N215" s="6" t="n">
+        <v>125574078540.1959</v>
       </c>
       <c r="O215" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n">
@@ -21810,11 +21424,11 @@
         </is>
       </c>
       <c r="N216" s="6" t="n">
-        <v>139862085574.5275</v>
+        <v>204550243110.9356</v>
       </c>
       <c r="O216" s="4" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P216" s="4" t="inlineStr">
@@ -21912,19 +21526,17 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N217" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N217" s="6" t="n">
+        <v>120725774433.4873</v>
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n">
@@ -22017,19 +21629,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N218" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N218" s="6" t="n">
+        <v>6105201468.341025</v>
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Mid</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n">
@@ -22122,19 +21732,17 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N219" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N219" s="6" t="n">
+        <v>132068729514.6421</v>
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n">
@@ -22225,19 +21833,17 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N220" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N220" s="6" t="n">
+        <v>25503512602.75335</v>
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n">
@@ -22328,19 +21934,17 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N221" s="4" t="inlineStr">
-        <is>
-          <t>MARKET_CAP_UNAVAILABLE</t>
-        </is>
+      <c r="N221" s="6" t="n">
+        <v>85467303076.69794</v>
       </c>
       <c r="O221" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2026-10-24</t>
         </is>
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Large</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n">

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -511,7 +511,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-24 · prices = 2026-10-23 close</t>
+          <t>AEGIS USA · CURRENT · what is investable now · workbook 2026-10-26 · prices = 2026-10-23 close</t>
         </is>
       </c>
     </row>
@@ -539,14 +539,14 @@
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>🔎 WHY NEW=0 · 516 scored · 204 already in CURRENT · biggest blocker: model disagreement (265) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
+          <t>🔎 WHY NEW=0 · 30 scored · 204 already in CURRENT · biggest blocker: model disagreement (15) · lost to the 15-name ensemble truncation: 0 · lifecycle defects: 0</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (1 day(s) old) · ensemble STALE (1 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 203 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (3 day(s) old) · ensemble STALE (3 day(s) old) · feature_store STALE (97 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -725,17 +725,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N8" s="6" t="n">
-        <v>16565326493.18021</v>
+      <c r="N8" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O8" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P8" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q8" s="4" t="n">
@@ -764,7 +766,7 @@
       </c>
       <c r="W8" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -791,7 +793,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -826,17 +828,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N9" s="6" t="n">
-        <v>35546758199.90703</v>
+      <c r="N9" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O9" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P9" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q9" s="4" t="n">
@@ -865,7 +869,7 @@
       </c>
       <c r="W9" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -892,7 +896,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -927,17 +931,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N10" s="6" t="n">
-        <v>52299796618.21564</v>
+      <c r="N10" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O10" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P10" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q10" s="4" t="n">
@@ -966,7 +972,7 @@
       </c>
       <c r="W10" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -993,7 +999,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1028,17 +1034,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N11" s="6" t="n">
-        <v>35107507718.48309</v>
+      <c r="N11" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O11" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P11" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q11" s="4" t="n">
@@ -1067,7 +1075,7 @@
       </c>
       <c r="W11" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1094,7 +1102,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1130,11 +1138,11 @@
         </is>
       </c>
       <c r="N12" s="6" t="n">
-        <v>237465214365.1677</v>
+        <v>197696964011.1858</v>
       </c>
       <c r="O12" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P12" s="4" t="inlineStr">
@@ -1168,7 +1176,7 @@
       </c>
       <c r="W12" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1195,7 +1203,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1230,17 +1238,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N13" s="6" t="n">
-        <v>160250723888.1421</v>
+      <c r="N13" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O13" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P13" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q13" s="4" t="n">
@@ -1269,7 +1279,7 @@
       </c>
       <c r="W13" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1296,7 +1306,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1331,17 +1341,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N14" s="6" t="n">
-        <v>78342964276.6212</v>
+      <c r="N14" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O14" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P14" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q14" s="4" t="n">
@@ -1370,7 +1382,7 @@
       </c>
       <c r="W14" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1397,7 +1409,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1432,17 +1444,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N15" s="6" t="n">
-        <v>11638580103.4434</v>
+      <c r="N15" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O15" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P15" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q15" s="4" t="n">
@@ -1469,7 +1483,7 @@
       </c>
       <c r="W15" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1496,7 +1510,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1531,17 +1545,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N16" s="6" t="n">
-        <v>43331128521.18373</v>
+      <c r="N16" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O16" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P16" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q16" s="4" t="n">
@@ -1570,7 +1586,7 @@
       </c>
       <c r="W16" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1597,7 +1613,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1632,17 +1648,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N17" s="6" t="n">
-        <v>42325295609.19834</v>
+      <c r="N17" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O17" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P17" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q17" s="4" t="n">
@@ -1669,7 +1687,7 @@
       </c>
       <c r="W17" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1696,7 +1714,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1731,17 +1749,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N18" s="6" t="n">
-        <v>33481121738.60545</v>
+      <c r="N18" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O18" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P18" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q18" s="4" t="n">
@@ -1770,7 +1790,7 @@
       </c>
       <c r="W18" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1797,7 +1817,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1832,17 +1852,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N19" s="6" t="n">
-        <v>139572545770.6767</v>
+      <c r="N19" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O19" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P19" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q19" s="4" t="n">
@@ -1871,7 +1893,7 @@
       </c>
       <c r="W19" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1898,7 +1920,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -1933,17 +1955,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N20" s="6" t="n">
-        <v>14893610777.10915</v>
+      <c r="N20" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O20" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P20" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q20" s="4" t="n">
@@ -1970,7 +1994,7 @@
       </c>
       <c r="W20" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -1997,7 +2021,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2032,17 +2056,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N21" s="6" t="n">
-        <v>42024252767.73121</v>
+      <c r="N21" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O21" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P21" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q21" s="4" t="n">
@@ -2071,7 +2097,7 @@
       </c>
       <c r="W21" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2124,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2133,17 +2159,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N22" s="6" t="n">
-        <v>106856267459.9962</v>
+      <c r="N22" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O22" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P22" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q22" s="4" t="n">
@@ -2172,7 +2200,7 @@
       </c>
       <c r="W22" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2199,7 +2227,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2235,11 +2263,11 @@
         </is>
       </c>
       <c r="N23" s="6" t="n">
-        <v>375318524237.9146</v>
+        <v>386990229190.2689</v>
       </c>
       <c r="O23" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P23" s="4" t="inlineStr">
@@ -2273,7 +2301,7 @@
       </c>
       <c r="W23" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2300,7 +2328,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2335,17 +2363,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N24" s="6" t="n">
-        <v>54025649909.99312</v>
+      <c r="N24" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O24" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P24" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q24" s="4" t="n">
@@ -2374,7 +2404,7 @@
       </c>
       <c r="W24" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2401,7 +2431,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2436,17 +2466,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N25" s="6" t="n">
-        <v>23469292626.86464</v>
+      <c r="N25" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O25" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P25" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q25" s="4" t="n">
@@ -2475,7 +2507,7 @@
       </c>
       <c r="W25" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2502,7 +2534,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2537,17 +2569,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N26" s="6" t="n">
-        <v>27052038697.19351</v>
+      <c r="N26" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O26" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P26" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q26" s="4" t="n">
@@ -2576,7 +2610,7 @@
       </c>
       <c r="W26" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2603,7 +2637,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2638,17 +2672,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N27" s="6" t="n">
-        <v>14541191703.75174</v>
+      <c r="N27" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O27" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P27" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q27" s="4" t="n">
@@ -2677,7 +2713,7 @@
       </c>
       <c r="W27" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2704,7 +2740,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2739,17 +2775,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N28" s="6" t="n">
-        <v>1135010815672.314</v>
+      <c r="N28" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O28" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P28" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q28" s="4" t="n">
@@ -2778,7 +2816,7 @@
       </c>
       <c r="W28" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2843,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2840,17 +2878,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N29" s="6" t="n">
-        <v>48752849010.3387</v>
+      <c r="N29" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O29" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P29" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q29" s="4" t="n">
@@ -2879,7 +2919,7 @@
       </c>
       <c r="W29" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -2906,7 +2946,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -2941,17 +2981,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N30" s="6" t="n">
-        <v>32501245188.6184</v>
+      <c r="N30" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O30" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P30" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q30" s="4" t="n">
@@ -2980,7 +3022,7 @@
       </c>
       <c r="W30" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3007,7 +3049,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3042,17 +3084,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N31" s="6" t="n">
-        <v>52710847623.63955</v>
+      <c r="N31" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O31" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P31" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q31" s="4" t="n">
@@ -3079,7 +3123,7 @@
       </c>
       <c r="W31" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3106,7 +3150,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3141,17 +3185,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N32" s="6" t="n">
-        <v>133475021658.0953</v>
+      <c r="N32" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O32" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P32" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q32" s="4" t="n">
@@ -3180,7 +3226,7 @@
       </c>
       <c r="W32" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3207,7 +3253,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3242,17 +3288,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N33" s="6" t="n">
-        <v>68391164728.14307</v>
+      <c r="N33" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O33" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P33" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q33" s="4" t="n">
@@ -3281,7 +3329,7 @@
       </c>
       <c r="W33" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3308,7 +3356,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3343,17 +3391,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N34" s="6" t="n">
-        <v>23512564504.17719</v>
+      <c r="N34" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O34" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P34" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q34" s="4" t="n">
@@ -3380,7 +3430,7 @@
       </c>
       <c r="W34" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3407,7 +3457,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3442,17 +3492,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N35" s="6" t="n">
-        <v>5040806191.026701</v>
+      <c r="N35" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O35" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P35" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q35" s="4" t="n">
@@ -3481,7 +3533,7 @@
       </c>
       <c r="W35" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 22d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3560,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3543,17 +3595,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N36" s="6" t="n">
-        <v>14986492476.39007</v>
+      <c r="N36" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O36" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P36" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q36" s="4" t="n">
@@ -3582,7 +3636,7 @@
       </c>
       <c r="W36" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3609,7 +3663,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3644,17 +3698,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N37" s="6" t="n">
-        <v>97454074176.63052</v>
+      <c r="N37" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O37" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P37" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q37" s="4" t="n">
@@ -3683,7 +3739,7 @@
       </c>
       <c r="W37" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3710,7 +3766,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3745,17 +3801,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N38" s="6" t="n">
-        <v>29100469778.37717</v>
+      <c r="N38" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O38" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P38" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q38" s="4" t="n">
@@ -3784,7 +3842,7 @@
       </c>
       <c r="W38" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3811,7 +3869,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3846,17 +3904,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N39" s="6" t="n">
-        <v>14285649813.94612</v>
+      <c r="N39" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O39" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P39" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q39" s="4" t="n">
@@ -3883,7 +3943,7 @@
       </c>
       <c r="W39" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -3910,7 +3970,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -3945,17 +4005,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N40" s="6" t="n">
-        <v>18184442878.42896</v>
+      <c r="N40" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O40" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P40" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q40" s="4" t="n">
@@ -3984,7 +4046,7 @@
       </c>
       <c r="W40" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4073,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -4046,17 +4108,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N41" s="6" t="n">
-        <v>44207911687.56331</v>
+      <c r="N41" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O41" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P41" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q41" s="4" t="n">
@@ -4085,7 +4149,7 @@
       </c>
       <c r="W41" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4112,7 +4176,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4149,17 +4213,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N42" s="6" t="n">
-        <v>120725774433.4873</v>
+      <c r="N42" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O42" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P42" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q42" s="4" t="n">
@@ -4188,7 +4254,7 @@
       </c>
       <c r="W42" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 46d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 48d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4215,7 +4281,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -4250,17 +4316,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N43" s="6" t="n">
-        <v>29730348496.77023</v>
+      <c r="N43" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O43" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P43" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q43" s="4" t="n">
@@ -4289,7 +4357,7 @@
       </c>
       <c r="W43" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4316,7 +4384,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4351,17 +4419,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N44" s="6" t="n">
-        <v>27447323434.78532</v>
+      <c r="N44" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O44" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P44" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q44" s="4" t="n">
@@ -4390,7 +4460,7 @@
       </c>
       <c r="W44" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4417,7 +4487,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4453,11 +4523,11 @@
         </is>
       </c>
       <c r="N45" s="6" t="n">
-        <v>70097091758.43842</v>
+        <v>71285303012.65192</v>
       </c>
       <c r="O45" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P45" s="4" t="inlineStr">
@@ -4491,7 +4561,7 @@
       </c>
       <c r="W45" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4518,7 +4588,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -4553,17 +4623,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N46" s="6" t="n">
-        <v>23555916164.69393</v>
+      <c r="N46" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O46" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P46" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q46" s="4" t="n">
@@ -4592,7 +4664,7 @@
       </c>
       <c r="W46" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4619,7 +4691,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4654,17 +4726,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N47" s="6" t="n">
-        <v>8379150674.384088</v>
+      <c r="N47" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O47" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P47" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q47" s="4" t="n">
@@ -4693,7 +4767,7 @@
       </c>
       <c r="W47" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4720,7 +4794,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -4755,17 +4829,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N48" s="6" t="n">
-        <v>19467043530.01433</v>
+      <c r="N48" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O48" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P48" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q48" s="4" t="n">
@@ -4794,7 +4870,7 @@
       </c>
       <c r="W48" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4821,7 +4897,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -4856,17 +4932,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N49" s="6" t="n">
-        <v>76594925837.28877</v>
+      <c r="N49" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O49" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P49" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q49" s="4" t="n">
@@ -4895,7 +4973,7 @@
       </c>
       <c r="W49" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -4922,7 +5000,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -4957,17 +5035,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N50" s="6" t="n">
-        <v>260015956316.5267</v>
+      <c r="N50" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O50" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P50" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q50" s="4" t="n">
@@ -4994,7 +5074,7 @@
       </c>
       <c r="W50" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5021,7 +5101,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -5056,17 +5136,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N51" s="6" t="n">
-        <v>88044047616.46739</v>
+      <c r="N51" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O51" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P51" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q51" s="4" t="n">
@@ -5095,7 +5177,7 @@
       </c>
       <c r="W51" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5204,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5157,17 +5239,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N52" s="6" t="n">
-        <v>13743583962.97344</v>
+      <c r="N52" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O52" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P52" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q52" s="4" t="n">
@@ -5194,7 +5278,7 @@
       </c>
       <c r="W52" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5221,7 +5305,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5256,17 +5340,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N53" s="6" t="n">
-        <v>14044296835.7795</v>
+      <c r="N53" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O53" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P53" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q53" s="4" t="n">
@@ -5295,7 +5381,7 @@
       </c>
       <c r="W53" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5322,7 +5408,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5357,17 +5443,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N54" s="6" t="n">
-        <v>54966742488.92049</v>
+      <c r="N54" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O54" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P54" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q54" s="4" t="n">
@@ -5396,7 +5484,7 @@
       </c>
       <c r="W54" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5423,7 +5511,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5458,17 +5546,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N55" s="6" t="n">
-        <v>10334750585.25211</v>
+      <c r="N55" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O55" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P55" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q55" s="4" t="n">
@@ -5495,7 +5585,7 @@
       </c>
       <c r="W55" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5522,7 +5612,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -5557,17 +5647,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N56" s="6" t="n">
-        <v>113005608974.8537</v>
+      <c r="N56" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O56" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P56" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q56" s="4" t="n">
@@ -5594,7 +5686,7 @@
       </c>
       <c r="W56" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5621,7 +5713,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -5656,17 +5748,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N57" s="6" t="n">
-        <v>22898129121.07968</v>
+      <c r="N57" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O57" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P57" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q57" s="4" t="n">
@@ -5695,7 +5789,7 @@
       </c>
       <c r="W57" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5722,7 +5816,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -5757,17 +5851,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N58" s="6" t="n">
-        <v>22069881433.58583</v>
+      <c r="N58" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O58" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P58" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q58" s="4" t="n">
@@ -5794,7 +5890,7 @@
       </c>
       <c r="W58" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5821,7 +5917,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -5856,17 +5952,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N59" s="6" t="n">
-        <v>181175721711.0555</v>
+      <c r="N59" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O59" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P59" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q59" s="4" t="n">
@@ -5895,7 +5993,7 @@
       </c>
       <c r="W59" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -5922,7 +6020,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -5957,17 +6055,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N60" s="6" t="n">
-        <v>86836037996.05959</v>
+      <c r="N60" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O60" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P60" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q60" s="4" t="n">
@@ -5994,7 +6094,7 @@
       </c>
       <c r="W60" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6021,7 +6121,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -6056,17 +6156,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N61" s="6" t="n">
-        <v>13079766770.08932</v>
+      <c r="N61" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O61" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P61" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q61" s="4" t="n">
@@ -6093,7 +6195,7 @@
       </c>
       <c r="W61" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6120,7 +6222,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -6155,17 +6257,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N62" s="6" t="n">
-        <v>18437413677.71741</v>
+      <c r="N62" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O62" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P62" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q62" s="4" t="n">
@@ -6192,7 +6296,7 @@
       </c>
       <c r="W62" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6219,7 +6323,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -6254,17 +6358,19 @@
           <t>Utilities</t>
         </is>
       </c>
-      <c r="N63" s="6" t="n">
-        <v>172186857498.601</v>
+      <c r="N63" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O63" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P63" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q63" s="4" t="n">
@@ -6293,7 +6399,7 @@
       </c>
       <c r="W63" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6320,7 +6426,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -6355,17 +6461,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N64" s="6" t="n">
-        <v>22304885593.77609</v>
+      <c r="N64" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O64" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P64" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q64" s="4" t="n">
@@ -6392,7 +6500,7 @@
       </c>
       <c r="W64" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6419,7 +6527,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -6454,17 +6562,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N65" s="6" t="n">
-        <v>15845282993.28703</v>
+      <c r="N65" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O65" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P65" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q65" s="4" t="n">
@@ -6493,7 +6603,7 @@
       </c>
       <c r="W65" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6520,7 +6630,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -6555,17 +6665,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N66" s="6" t="n">
-        <v>181677020981.8806</v>
+      <c r="N66" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O66" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P66" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q66" s="4" t="n">
@@ -6592,7 +6704,7 @@
       </c>
       <c r="W66" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6619,7 +6731,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -6654,17 +6766,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N67" s="6" t="n">
-        <v>119536352567.372</v>
+      <c r="N67" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O67" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P67" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q67" s="4" t="n">
@@ -6691,7 +6805,7 @@
       </c>
       <c r="W67" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6718,7 +6832,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6753,17 +6867,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N68" s="6" t="n">
-        <v>80519301730.83093</v>
+      <c r="N68" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O68" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P68" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q68" s="4" t="n">
@@ -6790,7 +6906,7 @@
       </c>
       <c r="W68" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6817,7 +6933,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -6852,17 +6968,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N69" s="6" t="n">
-        <v>64833579512.20567</v>
+      <c r="N69" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O69" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P69" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q69" s="4" t="n">
@@ -6889,7 +7007,7 @@
       </c>
       <c r="W69" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -6916,7 +7034,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -6951,17 +7069,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N70" s="6" t="n">
-        <v>472824530511.796</v>
+      <c r="N70" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O70" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P70" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q70" s="4" t="n">
@@ -6988,7 +7108,7 @@
       </c>
       <c r="W70" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7015,7 +7135,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -7050,17 +7170,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N71" s="6" t="n">
-        <v>6934258060.16568</v>
+      <c r="N71" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O71" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P71" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q71" s="4" t="n">
@@ -7087,7 +7209,7 @@
       </c>
       <c r="W71" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7114,7 +7236,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -7149,17 +7271,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N72" s="6" t="n">
-        <v>25786951295.65876</v>
+      <c r="N72" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O72" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P72" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q72" s="4" t="n">
@@ -7186,7 +7310,7 @@
       </c>
       <c r="W72" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7213,7 +7337,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -7249,11 +7373,11 @@
         </is>
       </c>
       <c r="N73" s="6" t="n">
-        <v>3894933077036.549</v>
+        <v>2925499309897.075</v>
       </c>
       <c r="O73" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P73" s="4" t="inlineStr">
@@ -7285,7 +7409,7 @@
       </c>
       <c r="W73" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7312,7 +7436,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -7347,17 +7471,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N74" s="6" t="n">
-        <v>91769845384.9781</v>
+      <c r="N74" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O74" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P74" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q74" s="4" t="n">
@@ -7384,7 +7510,7 @@
       </c>
       <c r="W74" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7411,7 +7537,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7446,17 +7572,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N75" s="6" t="n">
-        <v>24417432734.96738</v>
+      <c r="N75" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O75" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P75" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q75" s="4" t="n">
@@ -7483,7 +7611,7 @@
       </c>
       <c r="W75" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7510,7 +7638,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -7546,11 +7674,11 @@
         </is>
       </c>
       <c r="N76" s="6" t="n">
-        <v>89454048377.8867</v>
+        <v>83368118461.96332</v>
       </c>
       <c r="O76" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P76" s="4" t="inlineStr">
@@ -7582,7 +7710,7 @@
       </c>
       <c r="W76" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7609,7 +7737,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -7644,17 +7772,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N77" s="6" t="n">
-        <v>56650011191.95325</v>
+      <c r="N77" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O77" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P77" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q77" s="4" t="n">
@@ -7681,7 +7811,7 @@
       </c>
       <c r="W77" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7708,7 +7838,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -7743,17 +7873,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N78" s="6" t="n">
-        <v>152615976562.5463</v>
+      <c r="N78" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O78" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P78" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q78" s="4" t="n">
@@ -7780,7 +7912,7 @@
       </c>
       <c r="W78" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7807,7 +7939,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -7843,11 +7975,11 @@
         </is>
       </c>
       <c r="N79" s="6" t="n">
-        <v>5074578790806.488</v>
+        <v>4902301301361.686</v>
       </c>
       <c r="O79" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P79" s="4" t="inlineStr">
@@ -7879,7 +8011,7 @@
       </c>
       <c r="W79" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -7906,7 +8038,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -7941,17 +8073,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N80" s="6" t="n">
-        <v>83348924453.15994</v>
+      <c r="N80" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O80" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P80" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q80" s="4" t="n">
@@ -7978,7 +8112,7 @@
       </c>
       <c r="W80" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8005,7 +8139,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -8040,17 +8174,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N81" s="6" t="n">
-        <v>13255618607.19861</v>
+      <c r="N81" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O81" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P81" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q81" s="4" t="n">
@@ -8077,7 +8213,7 @@
       </c>
       <c r="W81" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8104,7 +8240,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -8139,17 +8275,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N82" s="6" t="n">
-        <v>11043328726.70052</v>
+      <c r="N82" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O82" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P82" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q82" s="4" t="n">
@@ -8176,7 +8314,7 @@
       </c>
       <c r="W82" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8203,7 +8341,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -8238,17 +8376,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N83" s="6" t="n">
-        <v>125574078540.1959</v>
+      <c r="N83" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O83" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P83" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q83" s="4" t="n">
@@ -8275,7 +8415,7 @@
       </c>
       <c r="W83" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8302,7 +8442,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -8337,17 +8477,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N84" s="6" t="n">
-        <v>31651915672.26271</v>
+      <c r="N84" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O84" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P84" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q84" s="4" t="n">
@@ -8374,7 +8516,7 @@
       </c>
       <c r="W84" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8401,7 +8543,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -8436,17 +8578,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N85" s="6" t="n">
-        <v>57902857947.4638</v>
+      <c r="N85" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O85" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P85" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q85" s="4" t="n">
@@ -8473,7 +8617,7 @@
       </c>
       <c r="W85" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8500,7 +8644,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -8535,17 +8679,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N86" s="6" t="n">
-        <v>24254928571.09423</v>
+      <c r="N86" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O86" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P86" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q86" s="4" t="n">
@@ -8572,7 +8718,7 @@
       </c>
       <c r="W86" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8599,7 +8745,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -8634,17 +8780,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N87" s="6" t="n">
-        <v>132068729514.6421</v>
+      <c r="N87" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O87" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P87" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q87" s="4" t="n">
@@ -8671,7 +8819,7 @@
       </c>
       <c r="W87" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8698,7 +8846,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -8733,17 +8881,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N88" s="6" t="n">
-        <v>114921159720.324</v>
+      <c r="N88" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O88" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P88" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q88" s="4" t="n">
@@ -8770,7 +8920,7 @@
       </c>
       <c r="W88" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8797,7 +8947,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -8832,17 +8982,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N89" s="6" t="n">
-        <v>21463473177.2398</v>
+      <c r="N89" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O89" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P89" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q89" s="4" t="n">
@@ -8869,7 +9021,7 @@
       </c>
       <c r="W89" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8896,7 +9048,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -8931,17 +9083,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N90" s="6" t="n">
-        <v>185012043477.1862</v>
+      <c r="N90" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O90" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P90" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q90" s="4" t="n">
@@ -8968,7 +9122,7 @@
       </c>
       <c r="W90" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -8995,7 +9149,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -9030,17 +9184,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N91" s="6" t="n">
-        <v>123509396601.4861</v>
+      <c r="N91" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O91" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P91" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q91" s="4" t="n">
@@ -9067,7 +9223,7 @@
       </c>
       <c r="W91" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9094,7 +9250,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -9129,17 +9285,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N92" s="6" t="n">
-        <v>59237947158.77261</v>
+      <c r="N92" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O92" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P92" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q92" s="4" t="n">
@@ -9166,7 +9324,7 @@
       </c>
       <c r="W92" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9193,7 +9351,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -9228,17 +9386,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N93" s="6" t="n">
-        <v>18407720014.68958</v>
+      <c r="N93" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O93" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P93" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q93" s="4" t="n">
@@ -9265,7 +9425,7 @@
       </c>
       <c r="W93" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9292,7 +9452,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -9327,17 +9487,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N94" s="6" t="n">
-        <v>28973435877.01321</v>
+      <c r="N94" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O94" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P94" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q94" s="4" t="n">
@@ -9364,7 +9526,7 @@
       </c>
       <c r="W94" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9391,7 +9553,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -9426,17 +9588,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N95" s="6" t="n">
-        <v>80334112475.79723</v>
+      <c r="N95" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O95" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P95" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q95" s="4" t="n">
@@ -9463,7 +9627,7 @@
       </c>
       <c r="W95" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9490,7 +9654,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -9525,17 +9689,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N96" s="6" t="n">
-        <v>173980269803.8291</v>
+      <c r="N96" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O96" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P96" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q96" s="4" t="n">
@@ -9562,7 +9728,7 @@
       </c>
       <c r="W96" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9589,7 +9755,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -9624,17 +9790,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N97" s="6" t="n">
-        <v>90489877439.44135</v>
+      <c r="N97" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O97" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P97" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q97" s="4" t="n">
@@ -9661,7 +9829,7 @@
       </c>
       <c r="W97" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9688,7 +9856,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -9723,17 +9891,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N98" s="6" t="n">
-        <v>27058268376.48824</v>
+      <c r="N98" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O98" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P98" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q98" s="4" t="n">
@@ -9760,7 +9930,7 @@
       </c>
       <c r="W98" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9787,7 +9957,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -9822,17 +9992,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N99" s="6" t="n">
-        <v>13280058862.43732</v>
+      <c r="N99" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O99" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P99" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q99" s="4" t="n">
@@ -9859,7 +10031,7 @@
       </c>
       <c r="W99" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9886,7 +10058,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -9921,17 +10093,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N100" s="6" t="n">
-        <v>74113956796.00749</v>
+      <c r="N100" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O100" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P100" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q100" s="4" t="n">
@@ -9958,7 +10132,7 @@
       </c>
       <c r="W100" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -9985,7 +10159,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -10020,17 +10194,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N101" s="6" t="n">
-        <v>27220744551.05336</v>
+      <c r="N101" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O101" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P101" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q101" s="4" t="n">
@@ -10057,7 +10233,7 @@
       </c>
       <c r="W101" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10084,7 +10260,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -10120,11 +10296,11 @@
         </is>
       </c>
       <c r="N102" s="6" t="n">
-        <v>55398754393.85931</v>
+        <v>64923212314.32135</v>
       </c>
       <c r="O102" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P102" s="4" t="inlineStr">
@@ -10156,7 +10332,7 @@
       </c>
       <c r="W102" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10183,7 +10359,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -10218,17 +10394,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N103" s="6" t="n">
-        <v>82889591627.31059</v>
+      <c r="N103" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O103" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P103" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q103" s="4" t="n">
@@ -10255,7 +10433,7 @@
       </c>
       <c r="W103" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10282,7 +10460,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -10317,17 +10495,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N104" s="6" t="n">
-        <v>34617842683.75591</v>
+      <c r="N104" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O104" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P104" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q104" s="4" t="n">
@@ -10354,7 +10534,7 @@
       </c>
       <c r="W104" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10381,7 +10561,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -10416,17 +10596,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N105" s="6" t="n">
-        <v>753355563733.7185</v>
+      <c r="N105" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O105" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P105" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q105" s="4" t="n">
@@ -10453,7 +10635,7 @@
       </c>
       <c r="W105" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10480,7 +10662,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -10515,17 +10697,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N106" s="6" t="n">
-        <v>33465706661.96794</v>
+      <c r="N106" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O106" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P106" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q106" s="4" t="n">
@@ -10552,7 +10736,7 @@
       </c>
       <c r="W106" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10579,7 +10763,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -10614,17 +10798,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N107" s="6" t="n">
-        <v>64387268290.14609</v>
+      <c r="N107" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O107" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P107" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q107" s="4" t="n">
@@ -10651,7 +10837,7 @@
       </c>
       <c r="W107" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10678,7 +10864,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -10713,17 +10899,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N108" s="6" t="n">
-        <v>102683343166.8086</v>
+      <c r="N108" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O108" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P108" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q108" s="4" t="n">
@@ -10750,7 +10938,7 @@
       </c>
       <c r="W108" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10777,7 +10965,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -10812,17 +11000,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N109" s="6" t="n">
-        <v>22495725294.22522</v>
+      <c r="N109" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O109" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P109" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q109" s="4" t="n">
@@ -10849,7 +11039,7 @@
       </c>
       <c r="W109" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10876,7 +11066,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -10912,11 +11102,11 @@
         </is>
       </c>
       <c r="N110" s="6" t="n">
-        <v>83080671870.19131</v>
+        <v>78469340035.26892</v>
       </c>
       <c r="O110" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P110" s="4" t="inlineStr">
@@ -10948,7 +11138,7 @@
       </c>
       <c r="W110" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 8d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 10d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -10975,7 +11165,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -11010,17 +11200,19 @@
           <t>Consumer Disc</t>
         </is>
       </c>
-      <c r="N111" s="6" t="n">
-        <v>102991171934.07</v>
+      <c r="N111" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O111" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P111" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q111" s="4" t="n">
@@ -11047,7 +11239,7 @@
       </c>
       <c r="W111" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11074,7 +11266,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -11109,17 +11301,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N112" s="6" t="n">
-        <v>40401733537.30011</v>
+      <c r="N112" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O112" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P112" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q112" s="4" t="n">
@@ -11146,7 +11340,7 @@
       </c>
       <c r="W112" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11173,7 +11367,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -11208,17 +11402,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N113" s="6" t="n">
-        <v>47293341491.86511</v>
+      <c r="N113" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O113" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P113" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q113" s="4" t="n">
@@ -11245,7 +11441,7 @@
       </c>
       <c r="W113" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11272,7 +11468,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -11307,17 +11503,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N114" s="6" t="n">
-        <v>59169786195.87192</v>
+      <c r="N114" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O114" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P114" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q114" s="4" t="n">
@@ -11344,7 +11542,7 @@
       </c>
       <c r="W114" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11371,7 +11569,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -11406,17 +11604,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N115" s="6" t="n">
-        <v>73248713266.5041</v>
+      <c r="N115" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O115" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P115" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q115" s="4" t="n">
@@ -11443,7 +11643,7 @@
       </c>
       <c r="W115" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11470,7 +11670,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -11505,17 +11705,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N116" s="6" t="n">
-        <v>25503512602.75335</v>
+      <c r="N116" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O116" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P116" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q116" s="4" t="n">
@@ -11542,7 +11744,7 @@
       </c>
       <c r="W116" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11569,7 +11771,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -11604,17 +11806,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N117" s="6" t="n">
-        <v>546260754212.6935</v>
+      <c r="N117" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O117" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P117" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q117" s="4" t="n">
@@ -11641,7 +11845,7 @@
       </c>
       <c r="W117" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11668,7 +11872,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -11703,17 +11907,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N118" s="6" t="n">
-        <v>156639035387.289</v>
+      <c r="N118" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O118" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P118" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q118" s="4" t="n">
@@ -11740,7 +11946,7 @@
       </c>
       <c r="W118" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11767,7 +11973,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -11802,17 +12008,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N119" s="6" t="n">
-        <v>64150493251.06628</v>
+      <c r="N119" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O119" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P119" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q119" s="4" t="n">
@@ -11839,7 +12047,7 @@
       </c>
       <c r="W119" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11866,7 +12074,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -11901,17 +12109,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N120" s="6" t="n">
-        <v>37887853374.84371</v>
+      <c r="N120" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O120" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P120" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q120" s="4" t="n">
@@ -11938,7 +12148,7 @@
       </c>
       <c r="W120" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -11965,7 +12175,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -12000,17 +12210,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N121" s="6" t="n">
-        <v>23960727497.45567</v>
+      <c r="N121" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O121" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P121" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q121" s="4" t="n">
@@ -12037,7 +12249,7 @@
       </c>
       <c r="W121" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12064,7 +12276,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -12099,17 +12311,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N122" s="6" t="n">
-        <v>25846396357.69842</v>
+      <c r="N122" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O122" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P122" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q122" s="4" t="n">
@@ -12136,7 +12350,7 @@
       </c>
       <c r="W122" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12163,7 +12377,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -12198,17 +12412,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N123" s="6" t="n">
-        <v>16266720329.71902</v>
+      <c r="N123" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O123" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P123" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q123" s="4" t="n">
@@ -12235,7 +12451,7 @@
       </c>
       <c r="W123" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12262,7 +12478,7 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -12297,17 +12513,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N124" s="6" t="n">
-        <v>32129206511.4126</v>
+      <c r="N124" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O124" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P124" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q124" s="4" t="n">
@@ -12334,7 +12552,7 @@
       </c>
       <c r="W124" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 28d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12361,7 +12579,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -12396,17 +12614,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N125" s="6" t="n">
-        <v>37042475302.99583</v>
+      <c r="N125" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O125" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P125" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q125" s="4" t="n">
@@ -12433,7 +12653,7 @@
       </c>
       <c r="W125" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12680,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -12495,17 +12715,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N126" s="6" t="n">
-        <v>19399922723.90986</v>
+      <c r="N126" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O126" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P126" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q126" s="4" t="n">
@@ -12532,7 +12754,7 @@
       </c>
       <c r="W126" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12559,7 +12781,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -12594,17 +12816,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N127" s="6" t="n">
-        <v>98559842315.65967</v>
+      <c r="N127" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O127" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P127" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q127" s="4" t="n">
@@ -12631,7 +12855,7 @@
       </c>
       <c r="W127" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12658,7 +12882,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -12693,17 +12917,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N128" s="6" t="n">
-        <v>89557095464.32736</v>
+      <c r="N128" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O128" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P128" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q128" s="4" t="n">
@@ -12730,7 +12956,7 @@
       </c>
       <c r="W128" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12757,7 +12983,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -12792,17 +13018,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N129" s="6" t="n">
-        <v>21052321804.7523</v>
+      <c r="N129" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O129" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P129" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q129" s="4" t="n">
@@ -12829,7 +13057,7 @@
       </c>
       <c r="W129" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12856,7 +13084,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -12891,17 +13119,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N130" s="6" t="n">
-        <v>30338911841.94266</v>
+      <c r="N130" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O130" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P130" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q130" s="4" t="n">
@@ -12928,7 +13158,7 @@
       </c>
       <c r="W130" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -12955,7 +13185,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -12990,17 +13220,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N131" s="6" t="n">
-        <v>56532735426.60712</v>
+      <c r="N131" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O131" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P131" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q131" s="4" t="n">
@@ -13027,7 +13259,7 @@
       </c>
       <c r="W131" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13054,7 +13286,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -13089,17 +13321,19 @@
           <t>Consumer Disc</t>
         </is>
       </c>
-      <c r="N132" s="6" t="n">
-        <v>20945946985.81395</v>
+      <c r="N132" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O132" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P132" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q132" s="4" t="n">
@@ -13126,7 +13360,7 @@
       </c>
       <c r="W132" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13153,7 +13387,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -13188,17 +13422,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N133" s="6" t="n">
-        <v>109925892401.5142</v>
+      <c r="N133" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O133" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P133" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q133" s="4" t="n">
@@ -13225,7 +13461,7 @@
       </c>
       <c r="W133" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13252,7 +13488,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -13287,17 +13523,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N134" s="6" t="n">
-        <v>21423972391.2723</v>
+      <c r="N134" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O134" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P134" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q134" s="4" t="n">
@@ -13324,7 +13562,7 @@
       </c>
       <c r="W134" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13351,7 +13589,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -13386,17 +13624,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N135" s="6" t="n">
-        <v>27599422828.54258</v>
+      <c r="N135" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O135" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P135" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q135" s="4" t="n">
@@ -13423,7 +13663,7 @@
       </c>
       <c r="W135" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 1d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 3d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13450,7 +13690,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -13485,17 +13725,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N136" s="6" t="n">
-        <v>22227980135.64559</v>
+      <c r="N136" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O136" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P136" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q136" s="4" t="n">
@@ -13522,7 +13764,7 @@
       </c>
       <c r="W136" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13549,7 +13791,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -13584,17 +13826,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N137" s="6" t="n">
-        <v>56027339479.37971</v>
+      <c r="N137" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O137" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P137" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q137" s="4" t="n">
@@ -13621,7 +13865,7 @@
       </c>
       <c r="W137" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13648,7 +13892,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -13683,17 +13927,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N138" s="6" t="n">
-        <v>34087880601.02591</v>
+      <c r="N138" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O138" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P138" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q138" s="4" t="n">
@@ -13720,7 +13966,7 @@
       </c>
       <c r="W138" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13747,7 +13993,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -13782,17 +14028,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N139" s="6" t="n">
-        <v>48028608023.96908</v>
+      <c r="N139" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O139" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P139" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q139" s="4" t="n">
@@ -13819,7 +14067,7 @@
       </c>
       <c r="W139" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 2d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 4d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13846,7 +14094,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -13881,17 +14129,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N140" s="6" t="n">
-        <v>69390497307.31636</v>
+      <c r="N140" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O140" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P140" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q140" s="4" t="n">
@@ -13918,7 +14168,7 @@
       </c>
       <c r="W140" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -13945,7 +14195,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -13980,17 +14230,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N141" s="6" t="n">
-        <v>10799409266.63105</v>
+      <c r="N141" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O141" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P141" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q141" s="4" t="n">
@@ -14017,7 +14269,7 @@
       </c>
       <c r="W141" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14044,7 +14296,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -14079,17 +14331,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N142" s="6" t="n">
-        <v>22485368014.91627</v>
+      <c r="N142" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O142" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P142" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q142" s="4" t="n">
@@ -14116,7 +14370,7 @@
       </c>
       <c r="W142" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14143,7 +14397,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -14178,17 +14432,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N143" s="6" t="n">
-        <v>34689656544.60545</v>
+      <c r="N143" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O143" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P143" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q143" s="4" t="n">
@@ -14215,7 +14471,7 @@
       </c>
       <c r="W143" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14242,7 +14498,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -14277,17 +14533,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N144" s="6" t="n">
-        <v>28086653727.67912</v>
+      <c r="N144" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O144" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P144" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q144" s="4" t="n">
@@ -14314,7 +14572,7 @@
       </c>
       <c r="W144" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14341,7 +14599,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -14376,17 +14634,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N145" s="6" t="n">
-        <v>25072636247.77122</v>
+      <c r="N145" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O145" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P145" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q145" s="4" t="n">
@@ -14413,7 +14673,7 @@
       </c>
       <c r="W145" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14440,7 +14700,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -14475,17 +14735,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N146" s="6" t="n">
-        <v>96827785626.12506</v>
+      <c r="N146" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O146" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P146" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q146" s="4" t="n">
@@ -14512,7 +14774,7 @@
       </c>
       <c r="W146" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14539,7 +14801,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -14574,17 +14836,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N147" s="6" t="n">
-        <v>64017690131.78958</v>
+      <c r="N147" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O147" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P147" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q147" s="4" t="n">
@@ -14611,7 +14875,7 @@
       </c>
       <c r="W147" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14638,7 +14902,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -14673,17 +14937,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N148" s="6" t="n">
-        <v>9449307890.342999</v>
+      <c r="N148" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O148" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P148" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q148" s="4" t="n">
@@ -14710,7 +14976,7 @@
       </c>
       <c r="W148" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14737,7 +15003,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -14772,17 +15038,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N149" s="6" t="n">
-        <v>73943499425.51872</v>
+      <c r="N149" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O149" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P149" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q149" s="4" t="n">
@@ -14809,7 +15077,7 @@
       </c>
       <c r="W149" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14836,7 +15104,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -14871,17 +15139,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N150" s="6" t="n">
-        <v>14115621351.87959</v>
+      <c r="N150" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O150" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P150" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q150" s="4" t="n">
@@ -14908,7 +15178,7 @@
       </c>
       <c r="W150" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -14935,7 +15205,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -14970,17 +15240,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N151" s="6" t="n">
-        <v>825467539.8117318</v>
+      <c r="N151" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O151" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P151" s="4" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q151" s="4" t="n">
@@ -15007,7 +15279,7 @@
       </c>
       <c r="W151" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15034,7 +15306,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -15069,17 +15341,19 @@
           <t>Consumer Defensive</t>
         </is>
       </c>
-      <c r="N152" s="6" t="n">
-        <v>12947919779.15331</v>
+      <c r="N152" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O152" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P152" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q152" s="4" t="n">
@@ -15106,7 +15380,7 @@
       </c>
       <c r="W152" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15133,7 +15407,7 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -15168,17 +15442,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N153" s="6" t="n">
-        <v>14292230113.86092</v>
+      <c r="N153" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O153" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P153" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q153" s="4" t="n">
@@ -15205,7 +15481,7 @@
       </c>
       <c r="W153" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15232,7 +15508,7 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -15268,11 +15544,11 @@
         </is>
       </c>
       <c r="N154" s="6" t="n">
-        <v>204550243110.9356</v>
+        <v>139862085574.5275</v>
       </c>
       <c r="O154" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P154" s="4" t="inlineStr">
@@ -15304,7 +15580,7 @@
       </c>
       <c r="W154" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15331,7 +15607,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -15366,17 +15642,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N155" s="6" t="n">
-        <v>13645831365.88924</v>
+      <c r="N155" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O155" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P155" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q155" s="4" t="n">
@@ -15403,7 +15681,7 @@
       </c>
       <c r="W155" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15430,7 +15708,7 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -15465,17 +15743,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N156" s="6" t="n">
-        <v>87297136838.81131</v>
+      <c r="N156" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O156" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P156" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q156" s="4" t="n">
@@ -15502,7 +15782,7 @@
       </c>
       <c r="W156" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15529,7 +15809,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -15564,17 +15844,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N157" s="6" t="n">
-        <v>30718499642.34457</v>
+      <c r="N157" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O157" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P157" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q157" s="4" t="n">
@@ -15601,7 +15883,7 @@
       </c>
       <c r="W157" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 29d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15628,7 +15910,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -15663,17 +15945,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N158" s="6" t="n">
-        <v>111045253533.3641</v>
+      <c r="N158" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O158" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P158" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q158" s="4" t="n">
@@ -15700,7 +15984,7 @@
       </c>
       <c r="W158" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15727,7 +16011,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -15763,11 +16047,11 @@
         </is>
       </c>
       <c r="N159" s="6" t="n">
-        <v>5094481623274.441</v>
+        <v>4912471004503.345</v>
       </c>
       <c r="O159" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P159" s="4" t="inlineStr">
@@ -15799,7 +16083,7 @@
       </c>
       <c r="W159" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15826,7 +16110,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -15861,17 +16145,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N160" s="6" t="n">
-        <v>14537843856.07661</v>
+      <c r="N160" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O160" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P160" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q160" s="4" t="n">
@@ -15898,7 +16184,7 @@
       </c>
       <c r="W160" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -15925,7 +16211,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -15960,17 +16246,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N161" s="6" t="n">
-        <v>992887401325.0432</v>
+      <c r="N161" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O161" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P161" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q161" s="4" t="n">
@@ -15997,7 +16285,7 @@
       </c>
       <c r="W161" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16024,7 +16312,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -16059,17 +16347,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N162" s="6" t="n">
-        <v>82432790167.59808</v>
+      <c r="N162" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O162" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P162" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q162" s="4" t="n">
@@ -16096,7 +16386,7 @@
       </c>
       <c r="W162" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16123,7 +16413,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -16159,11 +16449,11 @@
         </is>
       </c>
       <c r="N163" s="6" t="n">
-        <v>2674853493963.549</v>
+        <v>2659500032721.515</v>
       </c>
       <c r="O163" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P163" s="4" t="inlineStr">
@@ -16195,7 +16485,7 @@
       </c>
       <c r="W163" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 5d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 7d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16222,7 +16512,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -16257,17 +16547,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N164" s="6" t="n">
-        <v>21902818280.68457</v>
+      <c r="N164" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O164" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P164" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q164" s="4" t="n">
@@ -16294,7 +16586,7 @@
       </c>
       <c r="W164" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16321,7 +16613,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -16356,17 +16648,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N165" s="6" t="n">
-        <v>53592004345.77758</v>
+      <c r="N165" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O165" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P165" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q165" s="4" t="n">
@@ -16393,7 +16687,7 @@
       </c>
       <c r="W165" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16420,7 +16714,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -16455,17 +16749,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N166" s="6" t="n">
-        <v>122913617306.017</v>
+      <c r="N166" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O166" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P166" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q166" s="4" t="n">
@@ -16492,7 +16788,7 @@
       </c>
       <c r="W166" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16519,7 +16815,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -16554,17 +16850,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N167" s="6" t="n">
-        <v>136238546003.0834</v>
+      <c r="N167" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O167" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P167" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q167" s="4" t="n">
@@ -16591,7 +16889,7 @@
       </c>
       <c r="W167" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16618,7 +16916,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -16653,17 +16951,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N168" s="6" t="n">
-        <v>296346634854.8615</v>
+      <c r="N168" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O168" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P168" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q168" s="4" t="n">
@@ -16690,7 +16990,7 @@
       </c>
       <c r="W168" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16717,7 +17017,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -16752,17 +17052,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N169" s="6" t="n">
-        <v>140993794935.8725</v>
+      <c r="N169" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O169" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P169" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q169" s="4" t="n">
@@ -16789,7 +17091,7 @@
       </c>
       <c r="W169" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16816,7 +17118,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -16851,17 +17153,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N170" s="6" t="n">
-        <v>3880610013548.706</v>
+      <c r="N170" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O170" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P170" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q170" s="4" t="n">
@@ -16888,7 +17192,7 @@
       </c>
       <c r="W170" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -16915,7 +17219,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -16950,17 +17254,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N171" s="6" t="n">
-        <v>3916516855912.108</v>
+      <c r="N171" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O171" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P171" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q171" s="4" t="n">
@@ -16987,7 +17293,7 @@
       </c>
       <c r="W171" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17014,7 +17320,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -17049,17 +17355,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N172" s="6" t="n">
-        <v>48283639645.51581</v>
+      <c r="N172" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O172" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P172" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q172" s="4" t="n">
@@ -17086,7 +17394,7 @@
       </c>
       <c r="W172" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17113,7 +17421,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -17148,17 +17456,19 @@
           <t>Staples</t>
         </is>
       </c>
-      <c r="N173" s="6" t="n">
-        <v>38627802301.14958</v>
+      <c r="N173" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O173" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P173" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q173" s="4" t="n">
@@ -17185,7 +17495,7 @@
       </c>
       <c r="W173" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17212,7 +17522,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -17247,17 +17557,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N174" s="6" t="n">
-        <v>843723217211.8292</v>
+      <c r="N174" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O174" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P174" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q174" s="4" t="n">
@@ -17284,7 +17596,7 @@
       </c>
       <c r="W174" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17311,7 +17623,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -17348,17 +17660,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N175" s="6" t="n">
-        <v>23453086212.00278</v>
+      <c r="N175" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O175" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P175" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q175" s="4" t="n">
@@ -17385,7 +17699,7 @@
       </c>
       <c r="W175" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 45d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 47d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17412,7 +17726,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -17447,17 +17761,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N176" s="6" t="n">
-        <v>247286267818.7022</v>
+      <c r="N176" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O176" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P176" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q176" s="4" t="n">
@@ -17484,7 +17800,7 @@
       </c>
       <c r="W176" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17511,7 +17827,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -17546,17 +17862,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N177" s="6" t="n">
-        <v>23329208255.60109</v>
+      <c r="N177" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O177" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P177" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q177" s="4" t="n">
@@ -17583,7 +17901,7 @@
       </c>
       <c r="W177" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17610,7 +17928,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -17645,17 +17963,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N178" s="6" t="n">
-        <v>120753575770.9667</v>
+      <c r="N178" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O178" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P178" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q178" s="4" t="n">
@@ -17682,7 +18002,7 @@
       </c>
       <c r="W178" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17709,7 +18029,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -17744,17 +18064,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N179" s="6" t="n">
-        <v>136772882559.5847</v>
+      <c r="N179" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O179" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P179" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q179" s="4" t="n">
@@ -17781,7 +18103,7 @@
       </c>
       <c r="W179" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17808,7 +18130,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -17843,17 +18165,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N180" s="6" t="n">
-        <v>353590021100.3874</v>
+      <c r="N180" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O180" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P180" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q180" s="4" t="n">
@@ -17880,7 +18204,7 @@
       </c>
       <c r="W180" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -17907,7 +18231,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -17942,17 +18266,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N181" s="6" t="n">
-        <v>182683784530.852</v>
+      <c r="N181" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O181" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P181" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q181" s="4" t="n">
@@ -17979,7 +18305,7 @@
       </c>
       <c r="W181" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18006,7 +18332,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -18042,11 +18368,11 @@
         </is>
       </c>
       <c r="N182" s="6" t="n">
-        <v>254976408779.9279</v>
+        <v>314267882987.9221</v>
       </c>
       <c r="O182" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P182" s="4" t="inlineStr">
@@ -18078,7 +18404,7 @@
       </c>
       <c r="W182" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18105,7 +18431,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -18140,17 +18466,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N183" s="6" t="n">
-        <v>217420254616.1736</v>
+      <c r="N183" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O183" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P183" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q183" s="4" t="n">
@@ -18177,7 +18505,7 @@
       </c>
       <c r="W183" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18204,7 +18532,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -18239,17 +18567,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N184" s="6" t="n">
-        <v>18264172487.74352</v>
+      <c r="N184" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O184" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P184" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q184" s="4" t="n">
@@ -18276,7 +18606,7 @@
       </c>
       <c r="W184" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18303,7 +18633,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -18338,17 +18668,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N185" s="6" t="n">
-        <v>202348504969.1966</v>
+      <c r="N185" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O185" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P185" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q185" s="4" t="n">
@@ -18375,7 +18707,7 @@
       </c>
       <c r="W185" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18402,7 +18734,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -18437,17 +18769,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N186" s="6" t="n">
-        <v>28569326345.83695</v>
+      <c r="N186" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O186" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P186" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q186" s="4" t="n">
@@ -18474,7 +18808,7 @@
       </c>
       <c r="W186" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18501,7 +18835,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -18536,17 +18870,19 @@
           <t>Basic Materials</t>
         </is>
       </c>
-      <c r="N187" s="6" t="n">
-        <v>113135786411.9562</v>
+      <c r="N187" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O187" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P187" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q187" s="4" t="n">
@@ -18573,7 +18909,7 @@
       </c>
       <c r="W187" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18600,7 +18936,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -18635,17 +18971,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N188" s="6" t="n">
-        <v>382472311023.9288</v>
+      <c r="N188" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O188" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P188" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q188" s="4" t="n">
@@ -18672,7 +19010,7 @@
       </c>
       <c r="W188" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18699,7 +19037,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -18734,17 +19072,19 @@
           <t>Real Estate</t>
         </is>
       </c>
-      <c r="N189" s="6" t="n">
-        <v>14047531026.96879</v>
+      <c r="N189" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O189" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P189" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q189" s="4" t="n">
@@ -18771,7 +19111,7 @@
       </c>
       <c r="W189" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18798,7 +19138,7 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -18833,17 +19173,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N190" s="6" t="n">
-        <v>281903196263.6478</v>
+      <c r="N190" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O190" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P190" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q190" s="4" t="n">
@@ -18870,7 +19212,7 @@
       </c>
       <c r="W190" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18897,7 +19239,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -18932,17 +19274,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N191" s="6" t="n">
-        <v>205352502645.7146</v>
+      <c r="N191" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O191" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P191" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q191" s="4" t="n">
@@ -18969,7 +19313,7 @@
       </c>
       <c r="W191" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 24d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 26d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -18996,7 +19340,7 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -19031,17 +19375,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N192" s="6" t="n">
-        <v>85467303076.69794</v>
+      <c r="N192" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O192" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P192" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q192" s="4" t="n">
@@ -19068,7 +19414,7 @@
       </c>
       <c r="W192" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19095,7 +19441,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -19130,17 +19476,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N193" s="6" t="n">
-        <v>82148568512.83273</v>
+      <c r="N193" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O193" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P193" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q193" s="4" t="n">
@@ -19167,7 +19515,7 @@
       </c>
       <c r="W193" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19194,7 +19542,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -19230,11 +19578,11 @@
         </is>
       </c>
       <c r="N194" s="6" t="n">
-        <v>315791182863.2249</v>
+        <v>405415174406.5037</v>
       </c>
       <c r="O194" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P194" s="4" t="inlineStr">
@@ -19266,7 +19614,7 @@
       </c>
       <c r="W194" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19293,7 +19641,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -19328,17 +19676,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N195" s="6" t="n">
-        <v>217070096839.7714</v>
+      <c r="N195" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O195" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P195" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q195" s="4" t="n">
@@ -19365,7 +19715,7 @@
       </c>
       <c r="W195" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19392,7 +19742,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -19427,17 +19777,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N196" s="6" t="n">
-        <v>18484171953.69656</v>
+      <c r="N196" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O196" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P196" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q196" s="4" t="n">
@@ -19464,7 +19816,7 @@
       </c>
       <c r="W196" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19491,7 +19843,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -19526,17 +19878,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N197" s="6" t="n">
-        <v>290201731938.0225</v>
+      <c r="N197" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O197" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P197" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q197" s="4" t="n">
@@ -19563,7 +19917,7 @@
       </c>
       <c r="W197" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19590,7 +19944,7 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -19625,17 +19979,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N198" s="6" t="n">
-        <v>7488589075.216432</v>
+      <c r="N198" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O198" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P198" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q198" s="4" t="n">
@@ -19662,7 +20018,7 @@
       </c>
       <c r="W198" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19689,7 +20045,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -19724,17 +20080,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N199" s="6" t="n">
-        <v>128647099802.9103</v>
+      <c r="N199" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O199" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P199" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q199" s="4" t="n">
@@ -19761,7 +20119,7 @@
       </c>
       <c r="W199" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19788,7 +20146,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -19823,17 +20181,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N200" s="6" t="n">
-        <v>74148095394.52744</v>
+      <c r="N200" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O200" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P200" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q200" s="4" t="n">
@@ -19860,7 +20220,7 @@
       </c>
       <c r="W200" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19887,7 +20247,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -19922,17 +20282,19 @@
           <t>Materials</t>
         </is>
       </c>
-      <c r="N201" s="6" t="n">
-        <v>11053504693.82843</v>
+      <c r="N201" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O201" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P201" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q201" s="4" t="n">
@@ -19959,7 +20321,7 @@
       </c>
       <c r="W201" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -19986,7 +20348,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -20023,17 +20385,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N202" s="6" t="n">
-        <v>21305905675.42725</v>
+      <c r="N202" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O202" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P202" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q202" s="4" t="n">
@@ -20060,7 +20424,7 @@
       </c>
       <c r="W202" s="4" t="inlineStr">
         <is>
-          <t>STRONG BUY · held 46d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>STRONG BUY · held 48d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20087,7 +20451,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -20122,17 +20486,19 @@
           <t>Communication</t>
         </is>
       </c>
-      <c r="N203" s="6" t="n">
-        <v>87096358995.60797</v>
+      <c r="N203" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O203" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P203" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q203" s="4" t="n">
@@ -20159,7 +20525,7 @@
       </c>
       <c r="W203" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20186,7 +20552,7 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -20221,17 +20587,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N204" s="6" t="n">
-        <v>178936937444.5307</v>
+      <c r="N204" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O204" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P204" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q204" s="4" t="n">
@@ -20258,7 +20626,7 @@
       </c>
       <c r="W204" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20285,7 +20653,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -20320,17 +20688,19 @@
           <t>Communication Services</t>
         </is>
       </c>
-      <c r="N205" s="6" t="n">
-        <v>140993794935.8725</v>
+      <c r="N205" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O205" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P205" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q205" s="4" t="n">
@@ -20357,7 +20727,7 @@
       </c>
       <c r="W205" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 41d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20384,7 +20754,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -20419,17 +20789,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N206" s="6" t="n">
-        <v>287938673780.7982</v>
+      <c r="N206" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O206" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P206" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q206" s="4" t="n">
@@ -20456,7 +20828,7 @@
       </c>
       <c r="W206" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20483,7 +20855,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -20518,17 +20890,19 @@
           <t>Consumer Cyclical</t>
         </is>
       </c>
-      <c r="N207" s="6" t="n">
-        <v>7059923578.936683</v>
+      <c r="N207" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O207" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P207" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q207" s="4" t="n">
@@ -20555,7 +20929,7 @@
       </c>
       <c r="W207" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 37d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 39d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20582,7 +20956,7 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -20618,11 +20992,11 @@
         </is>
       </c>
       <c r="N208" s="6" t="n">
-        <v>459726988530.8718</v>
+        <v>477639241496.4196</v>
       </c>
       <c r="O208" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P208" s="4" t="inlineStr">
@@ -20654,7 +21028,7 @@
       </c>
       <c r="W208" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20681,7 +21055,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -20716,17 +21090,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N209" s="6" t="n">
-        <v>40860154081.38228</v>
+      <c r="N209" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O209" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P209" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q209" s="4" t="n">
@@ -20753,7 +21129,7 @@
       </c>
       <c r="W209" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 36d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 38d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20780,7 +21156,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · R3 is still gathering evidence</t>
+          <t>Not rated yet · no R3 record for this date</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
@@ -20815,17 +21191,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N210" s="6" t="n">
-        <v>143383771605.5808</v>
+      <c r="N210" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O210" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P210" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q210" s="4" t="n">
@@ -20852,7 +21230,7 @@
       </c>
       <c r="W210" s="4" t="inlineStr">
         <is>
-          <t>BUY · held 31d · stop dynamic_risk_v2 · ENFORCED</t>
+          <t>BUY · held 33d · stop dynamic_risk_v2 · ENFORCED</t>
         </is>
       </c>
     </row>
@@ -20916,17 +21294,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N211" s="6" t="n">
-        <v>14541191703.75174</v>
+      <c r="N211" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O211" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P211" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q211" s="4" t="n">
@@ -21019,17 +21399,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N212" s="6" t="n">
-        <v>472824530511.796</v>
+      <c r="N212" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O212" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P212" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q212" s="4" t="n">
@@ -21120,17 +21502,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N213" s="6" t="n">
-        <v>56650011191.95325</v>
+      <c r="N213" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O213" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P213" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q213" s="4" t="n">
@@ -21222,11 +21606,11 @@
         </is>
       </c>
       <c r="N214" s="6" t="n">
-        <v>3894933077036.549</v>
+        <v>2925499309897.075</v>
       </c>
       <c r="O214" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P214" s="4" t="inlineStr">
@@ -21322,17 +21706,19 @@
           <t>Healthcare</t>
         </is>
       </c>
-      <c r="N215" s="6" t="n">
-        <v>125574078540.1959</v>
+      <c r="N215" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O215" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P215" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q215" s="4" t="n">
@@ -21424,11 +21810,11 @@
         </is>
       </c>
       <c r="N216" s="6" t="n">
-        <v>204550243110.9356</v>
+        <v>139862085574.5275</v>
       </c>
       <c r="O216" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="P216" s="4" t="inlineStr">
@@ -21526,17 +21912,19 @@
           <t>Energy</t>
         </is>
       </c>
-      <c r="N217" s="6" t="n">
-        <v>120725774433.4873</v>
+      <c r="N217" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O217" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P217" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q217" s="4" t="n">
@@ -21629,17 +22017,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N218" s="6" t="n">
-        <v>6105201468.341025</v>
+      <c r="N218" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O218" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P218" s="4" t="inlineStr">
         <is>
-          <t>Mid</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q218" s="4" t="n">
@@ -21732,17 +22122,19 @@
           <t>Technology</t>
         </is>
       </c>
-      <c r="N219" s="6" t="n">
-        <v>132068729514.6421</v>
+      <c r="N219" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O219" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P219" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q219" s="4" t="n">
@@ -21833,17 +22225,19 @@
           <t>Industrials</t>
         </is>
       </c>
-      <c r="N220" s="6" t="n">
-        <v>25503512602.75335</v>
+      <c r="N220" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O220" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P220" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q220" s="4" t="n">
@@ -21934,17 +22328,19 @@
           <t>Financial Services</t>
         </is>
       </c>
-      <c r="N221" s="6" t="n">
-        <v>85467303076.69794</v>
+      <c r="N221" s="4" t="inlineStr">
+        <is>
+          <t>MARKET_CAP_UNAVAILABLE</t>
+        </is>
       </c>
       <c r="O221" s="4" t="inlineStr">
         <is>
-          <t>2026-10-24</t>
+          <t>—</t>
         </is>
       </c>
       <c r="P221" s="4" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>—</t>
         </is>
       </c>
       <c r="Q221" s="4" t="n">
@@ -22154,7 +22550,7 @@
     <row r="1" ht="28" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>AEGIS USA · EXIT HISTORY · 2026-10-24</t>
+          <t>AEGIS USA · EXIT HISTORY · 2026-10-26</t>
         </is>
       </c>
     </row>

--- a/reports/telegram/aegis_history_usa.xlsx
+++ b/reports/telegram/aegis_history_usa.xlsx
@@ -546,7 +546,7 @@
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>⛔ STALE INPUT · recommendations_v3 STALE (3 day(s) old) · ensemble STALE (3 day(s) old) · feature_store STALE (97 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 0 candidate(s) reviewed today.</t>
+          <t>⛔ STALE INPUT · recommendations_v3 STALE (3 day(s) old) · ensemble STALE (3 day(s) old) · feature_store STALE (97 day(s) old) · CURRENT is built on decisions older than this report's as-of · treat NEW/ACTIVE with caution   ||   🤖 R3 SHADOW — RESEARCH ONLY, sits beside Action so you can see it next to the decision it comments on. R3 does NOT change Action, Confidence, Stop or Position. "Not rated yet" means R3 has no validated evidence on this name — it is the ABSENCE of a rating, NOT a Hold, a Buy, a mild negative, or a 50/50. A future "Caution" is a research flag and never means EXIT; a future "Supports" never means BUY. R3 becomes actionable only after out-of-sample validation, calibration, incremental-value evidence and explicit authorisation. 203 candidate(s) reviewed today.</t>
         </is>
       </c>
     </row>
@@ -690,7 +690,7 @@
       </c>
       <c r="E8" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F8" s="4" t="inlineStr">
@@ -793,7 +793,7 @@
       </c>
       <c r="E9" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F9" s="4" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F10" s="4" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="E11" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F11" s="4" t="inlineStr">
@@ -1102,7 +1102,7 @@
       </c>
       <c r="E12" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F12" s="4" t="inlineStr">
@@ -1203,7 +1203,7 @@
       </c>
       <c r="E13" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F13" s="4" t="inlineStr">
@@ -1306,7 +1306,7 @@
       </c>
       <c r="E14" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F14" s="4" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="E15" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F15" s="4" t="inlineStr">
@@ -1510,7 +1510,7 @@
       </c>
       <c r="E16" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F16" s="4" t="inlineStr">
@@ -1613,7 +1613,7 @@
       </c>
       <c r="E17" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F17" s="4" t="inlineStr">
@@ -1714,7 +1714,7 @@
       </c>
       <c r="E18" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F18" s="4" t="inlineStr">
@@ -1817,7 +1817,7 @@
       </c>
       <c r="E19" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F19" s="4" t="inlineStr">
@@ -1920,7 +1920,7 @@
       </c>
       <c r="E20" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F20" s="4" t="inlineStr">
@@ -2021,7 +2021,7 @@
       </c>
       <c r="E21" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F21" s="4" t="inlineStr">
@@ -2124,7 +2124,7 @@
       </c>
       <c r="E22" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F22" s="4" t="inlineStr">
@@ -2227,7 +2227,7 @@
       </c>
       <c r="E23" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F23" s="4" t="inlineStr">
@@ -2328,7 +2328,7 @@
       </c>
       <c r="E24" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F24" s="4" t="inlineStr">
@@ -2431,7 +2431,7 @@
       </c>
       <c r="E25" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F25" s="4" t="inlineStr">
@@ -2534,7 +2534,7 @@
       </c>
       <c r="E26" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F26" s="4" t="inlineStr">
@@ -2637,7 +2637,7 @@
       </c>
       <c r="E27" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F27" s="4" t="inlineStr">
@@ -2740,7 +2740,7 @@
       </c>
       <c r="E28" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F28" s="4" t="inlineStr">
@@ -2843,7 +2843,7 @@
       </c>
       <c r="E29" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F29" s="4" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="E30" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F30" s="4" t="inlineStr">
@@ -3049,7 +3049,7 @@
       </c>
       <c r="E31" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F31" s="4" t="inlineStr">
@@ -3150,7 +3150,7 @@
       </c>
       <c r="E32" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F32" s="4" t="inlineStr">
@@ -3253,7 +3253,7 @@
       </c>
       <c r="E33" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F33" s="4" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E34" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F34" s="4" t="inlineStr">
@@ -3457,7 +3457,7 @@
       </c>
       <c r="E35" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F35" s="4" t="inlineStr">
@@ -3560,7 +3560,7 @@
       </c>
       <c r="E36" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F36" s="4" t="inlineStr">
@@ -3663,7 +3663,7 @@
       </c>
       <c r="E37" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F37" s="4" t="inlineStr">
@@ -3766,7 +3766,7 @@
       </c>
       <c r="E38" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F38" s="4" t="inlineStr">
@@ -3869,7 +3869,7 @@
       </c>
       <c r="E39" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F39" s="4" t="inlineStr">
@@ -3970,7 +3970,7 @@
       </c>
       <c r="E40" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F40" s="4" t="inlineStr">
@@ -4073,7 +4073,7 @@
       </c>
       <c r="E41" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F41" s="4" t="inlineStr">
@@ -4176,7 +4176,7 @@
       </c>
       <c r="E42" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F42" s="4" t="inlineStr">
@@ -4281,7 +4281,7 @@
       </c>
       <c r="E43" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F43" s="4" t="inlineStr">
@@ -4384,7 +4384,7 @@
       </c>
       <c r="E44" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F44" s="4" t="inlineStr">
@@ -4487,7 +4487,7 @@
       </c>
       <c r="E45" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F45" s="4" t="inlineStr">
@@ -4588,7 +4588,7 @@
       </c>
       <c r="E46" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F46" s="4" t="inlineStr">
@@ -4691,7 +4691,7 @@
       </c>
       <c r="E47" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F47" s="4" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="E48" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F48" s="4" t="inlineStr">
@@ -4897,7 +4897,7 @@
       </c>
       <c r="E49" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F49" s="4" t="inlineStr">
@@ -5000,7 +5000,7 @@
       </c>
       <c r="E50" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F50" s="4" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="E51" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F51" s="4" t="inlineStr">
@@ -5204,7 +5204,7 @@
       </c>
       <c r="E52" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F52" s="4" t="inlineStr">
@@ -5305,7 +5305,7 @@
       </c>
       <c r="E53" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F53" s="4" t="inlineStr">
@@ -5408,7 +5408,7 @@
       </c>
       <c r="E54" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F54" s="4" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="E55" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F55" s="4" t="inlineStr">
@@ -5612,7 +5612,7 @@
       </c>
       <c r="E56" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F56" s="4" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="E57" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F57" s="4" t="inlineStr">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="E58" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F58" s="4" t="inlineStr">
@@ -5917,7 +5917,7 @@
       </c>
       <c r="E59" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F59" s="4" t="inlineStr">
@@ -6020,7 +6020,7 @@
       </c>
       <c r="E60" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F60" s="4" t="inlineStr">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E61" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F61" s="4" t="inlineStr">
@@ -6222,7 +6222,7 @@
       </c>
       <c r="E62" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F62" s="4" t="inlineStr">
@@ -6323,7 +6323,7 @@
       </c>
       <c r="E63" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F63" s="4" t="inlineStr">
@@ -6426,7 +6426,7 @@
       </c>
       <c r="E64" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F64" s="4" t="inlineStr">
@@ -6527,7 +6527,7 @@
       </c>
       <c r="E65" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F65" s="4" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="E66" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F66" s="4" t="inlineStr">
@@ -6731,7 +6731,7 @@
       </c>
       <c r="E67" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F67" s="4" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="E68" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F68" s="4" t="inlineStr">
@@ -6933,7 +6933,7 @@
       </c>
       <c r="E69" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F69" s="4" t="inlineStr">
@@ -7034,7 +7034,7 @@
       </c>
       <c r="E70" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F70" s="4" t="inlineStr">
@@ -7135,7 +7135,7 @@
       </c>
       <c r="E71" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F71" s="4" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="E72" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F72" s="4" t="inlineStr">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="E73" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F73" s="4" t="inlineStr">
@@ -7436,7 +7436,7 @@
       </c>
       <c r="E74" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F74" s="4" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="E75" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F75" s="4" t="inlineStr">
@@ -7638,7 +7638,7 @@
       </c>
       <c r="E76" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F76" s="4" t="inlineStr">
@@ -7737,7 +7737,7 @@
       </c>
       <c r="E77" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F77" s="4" t="inlineStr">
@@ -7838,7 +7838,7 @@
       </c>
       <c r="E78" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F78" s="4" t="inlineStr">
@@ -7939,7 +7939,7 @@
       </c>
       <c r="E79" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F79" s="4" t="inlineStr">
@@ -8038,7 +8038,7 @@
       </c>
       <c r="E80" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F80" s="4" t="inlineStr">
@@ -8139,7 +8139,7 @@
       </c>
       <c r="E81" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F81" s="4" t="inlineStr">
@@ -8240,7 +8240,7 @@
       </c>
       <c r="E82" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F82" s="4" t="inlineStr">
@@ -8341,7 +8341,7 @@
       </c>
       <c r="E83" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F83" s="4" t="inlineStr">
@@ -8442,7 +8442,7 @@
       </c>
       <c r="E84" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F84" s="4" t="inlineStr">
@@ -8543,7 +8543,7 @@
       </c>
       <c r="E85" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F85" s="4" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="E86" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F86" s="4" t="inlineStr">
@@ -8745,7 +8745,7 @@
       </c>
       <c r="E87" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F87" s="4" t="inlineStr">
@@ -8846,7 +8846,7 @@
       </c>
       <c r="E88" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F88" s="4" t="inlineStr">
@@ -8947,7 +8947,7 @@
       </c>
       <c r="E89" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F89" s="4" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="E90" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F90" s="4" t="inlineStr">
@@ -9149,7 +9149,7 @@
       </c>
       <c r="E91" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F91" s="4" t="inlineStr">
@@ -9250,7 +9250,7 @@
       </c>
       <c r="E92" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F92" s="4" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="E93" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F93" s="4" t="inlineStr">
@@ -9452,7 +9452,7 @@
       </c>
       <c r="E94" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F94" s="4" t="inlineStr">
@@ -9553,7 +9553,7 @@
       </c>
       <c r="E95" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F95" s="4" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="E96" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F96" s="4" t="inlineStr">
@@ -9755,7 +9755,7 @@
       </c>
       <c r="E97" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F97" s="4" t="inlineStr">
@@ -9856,7 +9856,7 @@
       </c>
       <c r="E98" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F98" s="4" t="inlineStr">
@@ -9957,7 +9957,7 @@
       </c>
       <c r="E99" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F99" s="4" t="inlineStr">
@@ -10058,7 +10058,7 @@
       </c>
       <c r="E100" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F100" s="4" t="inlineStr">
@@ -10159,7 +10159,7 @@
       </c>
       <c r="E101" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F101" s="4" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="E102" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F102" s="4" t="inlineStr">
@@ -10359,7 +10359,7 @@
       </c>
       <c r="E103" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F103" s="4" t="inlineStr">
@@ -10460,7 +10460,7 @@
       </c>
       <c r="E104" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F104" s="4" t="inlineStr">
@@ -10561,7 +10561,7 @@
       </c>
       <c r="E105" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F105" s="4" t="inlineStr">
@@ -10662,7 +10662,7 @@
       </c>
       <c r="E106" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F106" s="4" t="inlineStr">
@@ -10763,7 +10763,7 @@
       </c>
       <c r="E107" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F107" s="4" t="inlineStr">
@@ -10864,7 +10864,7 @@
       </c>
       <c r="E108" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F108" s="4" t="inlineStr">
@@ -10965,7 +10965,7 @@
       </c>
       <c r="E109" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F109" s="4" t="inlineStr">
@@ -11066,7 +11066,7 @@
       </c>
       <c r="E110" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F110" s="4" t="inlineStr">
@@ -11165,7 +11165,7 @@
       </c>
       <c r="E111" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F111" s="4" t="inlineStr">
@@ -11266,7 +11266,7 @@
       </c>
       <c r="E112" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F112" s="4" t="inlineStr">
@@ -11367,7 +11367,7 @@
       </c>
       <c r="E113" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F113" s="4" t="inlineStr">
@@ -11468,7 +11468,7 @@
       </c>
       <c r="E114" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F114" s="4" t="inlineStr">
@@ -11569,7 +11569,7 @@
       </c>
       <c r="E115" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F115" s="4" t="inlineStr">
@@ -11670,7 +11670,7 @@
       </c>
       <c r="E116" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F116" s="4" t="inlineStr">
@@ -11771,7 +11771,7 @@
       </c>
       <c r="E117" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F117" s="4" t="inlineStr">
@@ -11872,7 +11872,7 @@
       </c>
       <c r="E118" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F118" s="4" t="inlineStr">
@@ -11973,7 +11973,7 @@
       </c>
       <c r="E119" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F119" s="4" t="inlineStr">
@@ -12074,7 +12074,7 @@
       </c>
       <c r="E120" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F120" s="4" t="inlineStr">
@@ -12175,7 +12175,7 @@
       </c>
       <c r="E121" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F121" s="4" t="inlineStr">
@@ -12276,7 +12276,7 @@
       </c>
       <c r="E122" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F122" s="4" t="inlineStr">
@@ -12377,7 +12377,7 @@
       </c>
       <c r="E123" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F123" s="4" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="E124" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F124" s="4" t="inlineStr">
@@ -12579,7 +12579,7 @@
       </c>
       <c r="E125" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F125" s="4" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="E126" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F126" s="4" t="inlineStr">
@@ -12781,7 +12781,7 @@
       </c>
       <c r="E127" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F127" s="4" t="inlineStr">
@@ -12882,7 +12882,7 @@
       </c>
       <c r="E128" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F128" s="4" t="inlineStr">
@@ -12983,7 +12983,7 @@
       </c>
       <c r="E129" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F129" s="4" t="inlineStr">
@@ -13084,7 +13084,7 @@
       </c>
       <c r="E130" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F130" s="4" t="inlineStr">
@@ -13185,7 +13185,7 @@
       </c>
       <c r="E131" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F131" s="4" t="inlineStr">
@@ -13286,7 +13286,7 @@
       </c>
       <c r="E132" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F132" s="4" t="inlineStr">
@@ -13387,7 +13387,7 @@
       </c>
       <c r="E133" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F133" s="4" t="inlineStr">
@@ -13488,7 +13488,7 @@
       </c>
       <c r="E134" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F134" s="4" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="E135" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F135" s="4" t="inlineStr">
@@ -13690,7 +13690,7 @@
       </c>
       <c r="E136" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F136" s="4" t="inlineStr">
@@ -13791,7 +13791,7 @@
       </c>
       <c r="E137" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F137" s="4" t="inlineStr">
@@ -13892,7 +13892,7 @@
       </c>
       <c r="E138" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F138" s="4" t="inlineStr">
@@ -13993,7 +13993,7 @@
       </c>
       <c r="E139" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F139" s="4" t="inlineStr">
@@ -14094,7 +14094,7 @@
       </c>
       <c r="E140" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F140" s="4" t="inlineStr">
@@ -14195,7 +14195,7 @@
       </c>
       <c r="E141" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F141" s="4" t="inlineStr">
@@ -14296,7 +14296,7 @@
       </c>
       <c r="E142" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F142" s="4" t="inlineStr">
@@ -14397,7 +14397,7 @@
       </c>
       <c r="E143" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F143" s="4" t="inlineStr">
@@ -14498,7 +14498,7 @@
       </c>
       <c r="E144" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F144" s="4" t="inlineStr">
@@ -14599,7 +14599,7 @@
       </c>
       <c r="E145" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F145" s="4" t="inlineStr">
@@ -14700,7 +14700,7 @@
       </c>
       <c r="E146" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F146" s="4" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="E147" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F147" s="4" t="inlineStr">
@@ -14902,7 +14902,7 @@
       </c>
       <c r="E148" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F148" s="4" t="inlineStr">
@@ -15003,7 +15003,7 @@
       </c>
       <c r="E149" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F149" s="4" t="inlineStr">
@@ -15104,7 +15104,7 @@
       </c>
       <c r="E150" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F150" s="4" t="inlineStr">
@@ -15205,7 +15205,7 @@
       </c>
       <c r="E151" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F151" s="4" t="inlineStr">
@@ -15306,7 +15306,7 @@
       </c>
       <c r="E152" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F152" s="4" t="inlineStr">
@@ -15407,7 +15407,7 @@
       </c>
       <c r="E153" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F153" s="4" t="inlineStr">
@@ -15508,7 +15508,7 @@
       </c>
       <c r="E154" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F154" s="4" t="inlineStr">
@@ -15607,7 +15607,7 @@
       </c>
       <c r="E155" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F155" s="4" t="inlineStr">
@@ -15708,7 +15708,7 @@
       </c>
       <c r="E156" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F156" s="4" t="inlineStr">
@@ -15809,7 +15809,7 @@
       </c>
       <c r="E157" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F157" s="4" t="inlineStr">
@@ -15910,7 +15910,7 @@
       </c>
       <c r="E158" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F158" s="4" t="inlineStr">
@@ -16011,7 +16011,7 @@
       </c>
       <c r="E159" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F159" s="4" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="E160" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F160" s="4" t="inlineStr">
@@ -16211,7 +16211,7 @@
       </c>
       <c r="E161" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F161" s="4" t="inlineStr">
@@ -16312,7 +16312,7 @@
       </c>
       <c r="E162" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F162" s="4" t="inlineStr">
@@ -16413,7 +16413,7 @@
       </c>
       <c r="E163" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F163" s="4" t="inlineStr">
@@ -16512,7 +16512,7 @@
       </c>
       <c r="E164" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F164" s="4" t="inlineStr">
@@ -16613,7 +16613,7 @@
       </c>
       <c r="E165" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F165" s="4" t="inlineStr">
@@ -16714,7 +16714,7 @@
       </c>
       <c r="E166" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F166" s="4" t="inlineStr">
@@ -16815,7 +16815,7 @@
       </c>
       <c r="E167" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F167" s="4" t="inlineStr">
@@ -16916,7 +16916,7 @@
       </c>
       <c r="E168" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F168" s="4" t="inlineStr">
@@ -17017,7 +17017,7 @@
       </c>
       <c r="E169" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F169" s="4" t="inlineStr">
@@ -17118,7 +17118,7 @@
       </c>
       <c r="E170" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F170" s="4" t="inlineStr">
@@ -17219,7 +17219,7 @@
       </c>
       <c r="E171" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F171" s="4" t="inlineStr">
@@ -17320,7 +17320,7 @@
       </c>
       <c r="E172" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F172" s="4" t="inlineStr">
@@ -17421,7 +17421,7 @@
       </c>
       <c r="E173" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F173" s="4" t="inlineStr">
@@ -17522,7 +17522,7 @@
       </c>
       <c r="E174" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F174" s="4" t="inlineStr">
@@ -17623,7 +17623,7 @@
       </c>
       <c r="E175" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F175" s="4" t="inlineStr">
@@ -17726,7 +17726,7 @@
       </c>
       <c r="E176" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F176" s="4" t="inlineStr">
@@ -17827,7 +17827,7 @@
       </c>
       <c r="E177" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F177" s="4" t="inlineStr">
@@ -17928,7 +17928,7 @@
       </c>
       <c r="E178" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F178" s="4" t="inlineStr">
@@ -18029,7 +18029,7 @@
       </c>
       <c r="E179" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F179" s="4" t="inlineStr">
@@ -18130,7 +18130,7 @@
       </c>
       <c r="E180" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F180" s="4" t="inlineStr">
@@ -18231,7 +18231,7 @@
       </c>
       <c r="E181" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F181" s="4" t="inlineStr">
@@ -18332,7 +18332,7 @@
       </c>
       <c r="E182" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F182" s="4" t="inlineStr">
@@ -18431,7 +18431,7 @@
       </c>
       <c r="E183" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F183" s="4" t="inlineStr">
@@ -18532,7 +18532,7 @@
       </c>
       <c r="E184" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F184" s="4" t="inlineStr">
@@ -18633,7 +18633,7 @@
       </c>
       <c r="E185" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F185" s="4" t="inlineStr">
@@ -18734,7 +18734,7 @@
       </c>
       <c r="E186" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F186" s="4" t="inlineStr">
@@ -18835,7 +18835,7 @@
       </c>
       <c r="E187" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F187" s="4" t="inlineStr">
@@ -18936,7 +18936,7 @@
       </c>
       <c r="E188" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F188" s="4" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="E189" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F189" s="4" t="inlineStr">
@@ -19138,7 +19138,7 @@
       </c>
       <c r="E190" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F190" s="4" t="inlineStr">
@@ -19239,7 +19239,7 @@
       </c>
       <c r="E191" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F191" s="4" t="inlineStr">
@@ -19340,7 +19340,7 @@
       </c>
       <c r="E192" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F192" s="4" t="inlineStr">
@@ -19441,7 +19441,7 @@
       </c>
       <c r="E193" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F193" s="4" t="inlineStr">
@@ -19542,7 +19542,7 @@
       </c>
       <c r="E194" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F194" s="4" t="inlineStr">
@@ -19641,7 +19641,7 @@
       </c>
       <c r="E195" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F195" s="4" t="inlineStr">
@@ -19742,7 +19742,7 @@
       </c>
       <c r="E196" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F196" s="4" t="inlineStr">
@@ -19843,7 +19843,7 @@
       </c>
       <c r="E197" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F197" s="4" t="inlineStr">
@@ -19944,7 +19944,7 @@
       </c>
       <c r="E198" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F198" s="4" t="inlineStr">
@@ -20045,7 +20045,7 @@
       </c>
       <c r="E199" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F199" s="4" t="inlineStr">
@@ -20146,7 +20146,7 @@
       </c>
       <c r="E200" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F200" s="4" t="inlineStr">
@@ -20247,7 +20247,7 @@
       </c>
       <c r="E201" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F201" s="4" t="inlineStr">
@@ -20348,7 +20348,7 @@
       </c>
       <c r="E202" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F202" s="4" t="inlineStr">
@@ -20451,7 +20451,7 @@
       </c>
       <c r="E203" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F203" s="4" t="inlineStr">
@@ -20552,7 +20552,7 @@
       </c>
       <c r="E204" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F204" s="4" t="inlineStr">
@@ -20653,7 +20653,7 @@
       </c>
       <c r="E205" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F205" s="4" t="inlineStr">
@@ -20754,7 +20754,7 @@
       </c>
       <c r="E206" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F206" s="4" t="inlineStr">
@@ -20855,7 +20855,7 @@
       </c>
       <c r="E207" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F207" s="4" t="inlineStr">
@@ -20956,7 +20956,7 @@
       </c>
       <c r="E208" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F208" s="4" t="inlineStr">
@@ -21055,7 +21055,7 @@
       </c>
       <c r="E209" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F209" s="4" t="inlineStr">
@@ -21156,7 +21156,7 @@
       </c>
       <c r="E210" s="4" t="inlineStr">
         <is>
-          <t>Not rated yet · no R3 record for this date</t>
+          <t>Not rated yet · R3 is still gathering evidence</t>
         </is>
       </c>
       <c r="F210" s="4" t="inlineStr">
